--- a/data/affiliate/picks.xlsx
+++ b/data/affiliate/picks.xlsx
@@ -697,21 +697,23 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ASUS DUAL GeForce RTX 5060 8GB GDDR7</t>
+          <t>INNO3D GeForce RTX 5060 ICHILL X3 WHITE 8GB GDDR7</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>14990</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>16500</v>
-      </c>
+        <v>16990</v>
+      </c>
+      <c r="F2" s="3" t="n"/>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n"/>
+          <t>https://shopee.co.th/product/74778579/45361620338</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/th-11134207-81zte-mp0m4brh648y60</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Shopee</t>
@@ -739,19 +741,25 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>MSI GeForce RTX 5060 VENTUS 2X 8G</t>
+          <t>GIGABYTE GeForce RTX 5070 AERO OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>13990</v>
-      </c>
-      <c r="F3" s="3" t="n"/>
+        <v>31200</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>80000</v>
+      </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n"/>
+          <t>https://shopee.co.th/product/133460598/45410842093</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/sg-11134201-822xs-mogaiu4vc2rv54</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Shopee</t>
@@ -788,7 +796,7 @@
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H4" s="5" t="n"/>
@@ -832,7 +840,7 @@
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -872,7 +880,7 @@
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
@@ -916,7 +924,7 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -952,7 +960,7 @@
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H8" s="8" t="n"/>
@@ -983,19 +991,23 @@
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>เคส MacBook Air M4</t>
+          <t>elago MagSafe Side Mount Holder ยึดมือถือกับ MacBook</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>590</v>
+        <v>1390</v>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="n"/>
+          <t>https://shopee.co.th/product/381301308/27707726524</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/th-11134207-7r98q-lyuzdp3rmvu19b</t>
+        </is>
+      </c>
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="11" t="n"/>
       <c r="K9" s="12" t="n">
@@ -1003,7 +1015,7 @@
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>ป้องกันรอย</t>
+          <t>อุปกรณ์เสริม MacBook Air M4 16GB</t>
         </is>
       </c>
     </row>
@@ -1021,19 +1033,23 @@
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>เคส MacBook Air M4 32GB</t>
+          <t>elago MagSafe Side Mount Holder ยึดมือถือกับ MacBook</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>620</v>
+        <v>1390</v>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="n"/>
+          <t>https://shopee.co.th/product/381301308/27707726524</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/th-11134207-7r98q-lyuzdp3rmvu19b</t>
+        </is>
+      </c>
       <c r="I10" s="11" t="n"/>
       <c r="J10" s="11" t="n"/>
       <c r="K10" s="12" t="n">
@@ -1041,7 +1057,7 @@
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>ป้องกันรอย</t>
+          <t>อุปกรณ์เสริม MacBook Air M4 32GB</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1084,7 @@
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H11" s="11" t="n"/>
@@ -1106,7 +1122,7 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
@@ -1140,7 +1156,7 @@
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H13" s="11" t="n"/>
@@ -1174,7 +1190,7 @@
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H14" s="11" t="n"/>
@@ -1208,7 +1224,7 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H15" s="11" t="n"/>
@@ -1237,19 +1253,25 @@
       <c r="C16" s="14" t="n"/>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>แผงโซล่าเซลล์ 550W Mono</t>
+          <t>CELUO แผงโซล่าเซลล์ 18V/500W พร้อมสายเชื่อมต่อ</t>
         </is>
       </c>
       <c r="E16" s="15" t="n">
-        <v>4990</v>
-      </c>
-      <c r="F16" s="15" t="n"/>
+        <v>189</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>999</v>
+      </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="n"/>
+          <t>https://shopee.co.th/product/1001948638/53005644906</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/th-11134207-81ztd-mk4p2vjmkhkzbc</t>
+        </is>
+      </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Shopee</t>
@@ -1277,19 +1299,25 @@
       <c r="C17" s="17" t="n"/>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>EV Charger 7kW Wallbox Type 2</t>
+          <t>ROMADA C03 EV Charger Type2 3.5kW 16A จอ LCD</t>
         </is>
       </c>
       <c r="E17" s="18" t="n">
-        <v>12900</v>
-      </c>
-      <c r="F17" s="18" t="n"/>
+        <v>2520</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>5040</v>
+      </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="n"/>
+          <t>https://shopee.co.th/product/1791120553/49208184442</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/cn-11134207-820l4-mmle2s3pjuvc6a</t>
+        </is>
+      </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
           <t>Shopee</t>
@@ -1317,19 +1345,25 @@
       <c r="C18" s="20" t="n"/>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>ทองคำแท่ง 1 บาท ออโรร่า</t>
+          <t>SHINING GOLD ทองคำแท้ 96.5% น้ำหนัก 0.5 กรัม</t>
         </is>
       </c>
       <c r="E18" s="21" t="n">
-        <v>52000</v>
-      </c>
-      <c r="F18" s="21" t="n"/>
+        <v>2769</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>6559</v>
+      </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="n"/>
+          <t>https://shopee.co.th/product/345889393/20475717603</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/th-11134207-7ras9-m517zanf92n1a5</t>
+        </is>
+      </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
           <t>Shopee</t>
@@ -1353,19 +1387,23 @@
       <c r="C19" s="23" t="n"/>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>ASUS DUAL GeForce RTX 5060 8GB</t>
+          <t>INNO3D GeForce RTX 5060 ICHILL X3 WHITE 8GB GDDR7</t>
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>14990</v>
+        <v>16990</v>
       </c>
       <c r="F19" s="24" t="n"/>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H19" s="23" t="n"/>
+          <t>https://shopee.co.th/product/74778579/45361620338</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/th-11134207-81zte-mp0m4brh648y60</t>
+        </is>
+      </c>
       <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Shopee</t>
@@ -1389,19 +1427,23 @@
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>MSI GeForce RTX 5060 VENTUS 2X 8G</t>
+          <t>INNO3D GeForce RTX 5060 ICHILL X3 WHITE 8GB GDDR7</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>13990</v>
+        <v>16990</v>
       </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="n"/>
+          <t>https://shopee.co.th/product/74778579/45361620338</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/th-11134207-81zte-mp0m4brh648y60</t>
+        </is>
+      </c>
       <c r="I20" s="11" t="n"/>
       <c r="J20" s="11" t="n"/>
       <c r="K20" s="12" t="n">
@@ -1436,7 +1478,7 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
+          <t>https://shopee.co.th/product/ใส่ลิงก์จริง</t>
         </is>
       </c>
       <c r="H21" s="11" t="n"/>
@@ -1465,19 +1507,25 @@
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>MSI GeForce RTX 5070 Ti Gaming X Slim</t>
+          <t>GIGABYTE GeForce RTX 5070 AERO OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>35990</v>
-      </c>
-      <c r="F22" s="12" t="n"/>
+        <v>31200</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>80000</v>
+      </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/ใส่ลิงก์จริง</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="n"/>
+          <t>https://shopee.co.th/product/133460598/45410842093</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.co.th/file/sg-11134201-822xs-mogaiu4vc2rv54</t>
+        </is>
+      </c>
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="11" t="n"/>
       <c r="K22" s="12" t="n">
@@ -1485,7 +1533,7 @@
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>VRAM 16GB Pro batch gen</t>
+          <t>VRAM 12GB Pro batch gen</t>
         </is>
       </c>
     </row>

--- a/data/affiliate/picks.xlsx
+++ b/data/affiliate/picks.xlsx
@@ -694,7 +694,11 @@
           <t>item</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>5060|5060ti|4060|4060ti|3060|3060ti|3070|3070ti</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>INNO3D GeForce RTX 5060 ICHILL X3 WHITE 8GB GDDR7</t>
@@ -738,7 +742,11 @@
           <t>item</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>5070|5070ti|4070|4070s|4070ti|3080|3080ti|3070</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>GIGABYTE GeForce RTX 5070 AERO OC 12GB GDDR7</t>
@@ -1563,7 +1571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1575,6 +1583,8 @@
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1623,6 +1633,16 @@
           <t>GPU tier</t>
         </is>
       </c>
+      <c r="N1" s="26" t="inlineStr">
+        <is>
+          <t>ids (ai_calculator)</t>
+        </is>
+      </c>
+      <c r="O1" s="26" t="inlineStr">
+        <is>
+          <t>GPU name + VRAM</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
@@ -1632,12 +1652,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>item + ids</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AI Calculator — GPU strip</t>
+          <t>AI Calculator — GPU strip (กรองด้วย gpu.id → ดู Ref col N)</t>
         </is>
       </c>
       <c r="E2" s="28" t="inlineStr">
@@ -1666,6 +1686,16 @@
           <t>RTX 5060 8 GB — เริ่มต้น</t>
         </is>
       </c>
+      <c r="N2" s="27" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>RTX 5090  · VRAM 32GB</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="28" t="inlineStr">
@@ -1680,7 +1710,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AI Calculator — CPU strip (กรองด้วย ids)</t>
+          <t>AI Calculator — CPU strip (กรองด้วย cpu.id → ดู Ref col E)</t>
         </is>
       </c>
       <c r="E3" s="31" t="inlineStr">
@@ -1709,6 +1739,16 @@
           <t>RTX 5060 Ti 16 GB — จริงจัง</t>
         </is>
       </c>
+      <c r="N3" s="31" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="O3" s="32" t="inlineStr">
+        <is>
+          <t>RTX 5080  · VRAM 16GB</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="29" t="inlineStr">
@@ -1752,6 +1792,16 @@
           <t>RTX 5070 Ti / 5080 — Pro</t>
         </is>
       </c>
+      <c r="N4" s="27" t="inlineStr">
+        <is>
+          <t>5070ti</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>RTX 5070 Ti · VRAM 16GB</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="33" t="inlineStr">
@@ -1787,6 +1837,16 @@
           <t>MacBook Pro M4 Pro 48 GB</t>
         </is>
       </c>
+      <c r="N5" s="31" t="inlineStr">
+        <is>
+          <t>5070</t>
+        </is>
+      </c>
+      <c r="O5" s="32" t="inlineStr">
+        <is>
+          <t>RTX 5070  · VRAM 12GB</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
@@ -1822,6 +1882,16 @@
           <t>MacBook Pro M4 Max 36 GB</t>
         </is>
       </c>
+      <c r="N6" s="27" t="inlineStr">
+        <is>
+          <t>5060ti</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>RTX 5060 Ti 16GB · VRAM 16GB</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
@@ -1857,6 +1927,16 @@
           <t>MacBook Pro M4 Max 128 GB</t>
         </is>
       </c>
+      <c r="N7" s="31" t="inlineStr">
+        <is>
+          <t>4090</t>
+        </is>
+      </c>
+      <c r="O7" s="32" t="inlineStr">
+        <is>
+          <t>RTX 4090  · VRAM 24GB</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
@@ -1892,6 +1972,16 @@
           <t>Mac Studio</t>
         </is>
       </c>
+      <c r="N8" s="27" t="inlineStr">
+        <is>
+          <t>4080s</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>RTX 4080 Super · VRAM 16GB</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="E9" s="31" t="inlineStr">
@@ -1904,6 +1994,16 @@
           <t>Intel Core i9-14900K</t>
         </is>
       </c>
+      <c r="N9" s="31" t="inlineStr">
+        <is>
+          <t>4080</t>
+        </is>
+      </c>
+      <c r="O9" s="32" t="inlineStr">
+        <is>
+          <t>RTX 4080  · VRAM 16GB</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="E10" s="28" t="inlineStr">
@@ -1916,6 +2016,16 @@
           <t>Intel Core i7-14700K</t>
         </is>
       </c>
+      <c r="N10" s="27" t="inlineStr">
+        <is>
+          <t>4070tis</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>RTX 4070 Ti Super · VRAM 16GB</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="E11" s="31" t="inlineStr">
@@ -1928,6 +2038,16 @@
           <t>Intel Core i5-14600K</t>
         </is>
       </c>
+      <c r="N11" s="31" t="inlineStr">
+        <is>
+          <t>4070ti</t>
+        </is>
+      </c>
+      <c r="O11" s="32" t="inlineStr">
+        <is>
+          <t>RTX 4070 Ti · VRAM 12GB</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="E12" s="28" t="inlineStr">
@@ -1940,6 +2060,16 @@
           <t>Intel Core i9-13900K</t>
         </is>
       </c>
+      <c r="N12" s="27" t="inlineStr">
+        <is>
+          <t>4070s</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>RTX 4070 Super · VRAM 12GB</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="E13" s="31" t="inlineStr">
@@ -1952,6 +2082,16 @@
           <t>Intel Core i7-13700K</t>
         </is>
       </c>
+      <c r="N13" s="31" t="inlineStr">
+        <is>
+          <t>4070</t>
+        </is>
+      </c>
+      <c r="O13" s="32" t="inlineStr">
+        <is>
+          <t>RTX 4070  · VRAM 12GB</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="E14" s="28" t="inlineStr">
@@ -1964,6 +2104,16 @@
           <t>Intel Core i5-13600K</t>
         </is>
       </c>
+      <c r="N14" s="27" t="inlineStr">
+        <is>
+          <t>4060ti16</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>RTX 4060 Ti 16GB · VRAM 16GB</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="E15" s="31" t="inlineStr">
@@ -1976,6 +2126,16 @@
           <t>Intel Core i9-12900K</t>
         </is>
       </c>
+      <c r="N15" s="31" t="inlineStr">
+        <is>
+          <t>4060ti</t>
+        </is>
+      </c>
+      <c r="O15" s="32" t="inlineStr">
+        <is>
+          <t>RTX 4060 Ti 8GB · VRAM 8GB</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="E16" s="28" t="inlineStr">
@@ -1986,6 +2146,136 @@
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Intel Core i7-12700K</t>
+        </is>
+      </c>
+      <c r="N16" s="27" t="inlineStr">
+        <is>
+          <t>4060</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>RTX 4060  · VRAM 8GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="N17" s="31" t="inlineStr">
+        <is>
+          <t>3090ti</t>
+        </is>
+      </c>
+      <c r="O17" s="32" t="inlineStr">
+        <is>
+          <t>RTX 3090 Ti · VRAM 24GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="N18" s="27" t="inlineStr">
+        <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>RTX 3090  · VRAM 24GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="N19" s="31" t="inlineStr">
+        <is>
+          <t>3080ti</t>
+        </is>
+      </c>
+      <c r="O19" s="32" t="inlineStr">
+        <is>
+          <t>RTX 3080 Ti · VRAM 12GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="N20" s="27" t="inlineStr">
+        <is>
+          <t>3080_12</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>RTX 3080 12GB · VRAM 12GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="N21" s="31" t="inlineStr">
+        <is>
+          <t>3080</t>
+        </is>
+      </c>
+      <c r="O21" s="32" t="inlineStr">
+        <is>
+          <t>RTX 3080 10GB · VRAM 10GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="N22" s="27" t="inlineStr">
+        <is>
+          <t>3070ti</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>RTX 3070 Ti · VRAM 8GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="N23" s="31" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="O23" s="32" t="inlineStr">
+        <is>
+          <t>RTX 3070  · VRAM 8GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="N24" s="27" t="inlineStr">
+        <is>
+          <t>3060ti</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>RTX 3060 Ti · VRAM 8GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="N25" s="31" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="O25" s="32" t="inlineStr">
+        <is>
+          <t>RTX 3060 12GB · VRAM 12GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="N26" s="27" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>RTX 3050 8GB · VRAM 8GB</t>
         </is>
       </c>
     </row>

--- a/data/affiliate/picks.xlsx
+++ b/data/affiliate/picks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/GitHub/compair-website/data/affiliate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64202FD2-74FA-5943-9B2A-6BB3C6BAD5A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62163156-7BF3-B64E-935F-38D6E78DE91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="276">
   <si>
     <t>section</t>
   </si>
@@ -755,10 +755,100 @@
     <t>RTX 3050 8GB · VRAM 8GB</t>
   </si>
   <si>
-    <t>https://down-th.img.susercontent.com/file/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
-  </si>
-  <si>
-    <t>https://down-th.img.susercontent.com/file/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+    <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+  </si>
+  <si>
+    <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+  </si>
+  <si>
+    <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+  </si>
+  <si>
+    <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+  </si>
+  <si>
+    <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+  </si>
+  <si>
+    <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+  </si>
+  <si>
+    <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+  </si>
+  <si>
+    <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+  </si>
+  <si>
+    <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
   </si>
 </sst>
 </file>
@@ -2040,7 +2130,7 @@
       <c r="G24" t="s">
         <v>73</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="44" t="s">
         <v>245</v>
       </c>
       <c r="I24" t="s">
@@ -2066,6 +2156,9 @@
       <c r="G25" t="s">
         <v>75</v>
       </c>
+      <c r="H25" t="s">
+        <v>246</v>
+      </c>
       <c r="I25" t="s">
         <v>18</v>
       </c>
@@ -2089,6 +2182,9 @@
       <c r="G26" t="s">
         <v>77</v>
       </c>
+      <c r="H26" t="s">
+        <v>247</v>
+      </c>
       <c r="I26" t="s">
         <v>18</v>
       </c>
@@ -2112,6 +2208,9 @@
       <c r="G27" t="s">
         <v>79</v>
       </c>
+      <c r="H27" t="s">
+        <v>248</v>
+      </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
@@ -2135,6 +2234,9 @@
       <c r="G28" t="s">
         <v>81</v>
       </c>
+      <c r="H28" t="s">
+        <v>249</v>
+      </c>
       <c r="I28" t="s">
         <v>18</v>
       </c>
@@ -2155,8 +2257,11 @@
       <c r="E29">
         <v>180000</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="44" t="s">
         <v>83</v>
+      </c>
+      <c r="H29" t="s">
+        <v>250</v>
       </c>
       <c r="I29" t="s">
         <v>18</v>
@@ -2181,6 +2286,9 @@
       <c r="G30" t="s">
         <v>84</v>
       </c>
+      <c r="H30" t="s">
+        <v>251</v>
+      </c>
       <c r="I30" t="s">
         <v>18</v>
       </c>
@@ -2204,6 +2312,9 @@
       <c r="G31" t="s">
         <v>86</v>
       </c>
+      <c r="H31" t="s">
+        <v>252</v>
+      </c>
       <c r="I31" t="s">
         <v>18</v>
       </c>
@@ -2227,6 +2338,9 @@
       <c r="G32" t="s">
         <v>88</v>
       </c>
+      <c r="H32" t="s">
+        <v>252</v>
+      </c>
       <c r="I32" t="s">
         <v>18</v>
       </c>
@@ -2250,6 +2364,9 @@
       <c r="G33" t="s">
         <v>90</v>
       </c>
+      <c r="H33" t="s">
+        <v>253</v>
+      </c>
       <c r="I33" t="s">
         <v>18</v>
       </c>
@@ -2273,6 +2390,9 @@
       <c r="G34" t="s">
         <v>92</v>
       </c>
+      <c r="H34" t="s">
+        <v>254</v>
+      </c>
       <c r="I34" t="s">
         <v>18</v>
       </c>
@@ -2296,6 +2416,9 @@
       <c r="G35" t="s">
         <v>94</v>
       </c>
+      <c r="H35" t="s">
+        <v>255</v>
+      </c>
       <c r="I35" t="s">
         <v>18</v>
       </c>
@@ -2319,6 +2442,9 @@
       <c r="G36" t="s">
         <v>96</v>
       </c>
+      <c r="H36" t="s">
+        <v>256</v>
+      </c>
       <c r="I36" t="s">
         <v>18</v>
       </c>
@@ -2342,6 +2468,9 @@
       <c r="G37" t="s">
         <v>98</v>
       </c>
+      <c r="H37" t="s">
+        <v>257</v>
+      </c>
       <c r="I37" t="s">
         <v>18</v>
       </c>
@@ -2365,6 +2494,9 @@
       <c r="G38" t="s">
         <v>100</v>
       </c>
+      <c r="H38" t="s">
+        <v>258</v>
+      </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
@@ -2388,6 +2520,9 @@
       <c r="G39" t="s">
         <v>102</v>
       </c>
+      <c r="H39" t="s">
+        <v>259</v>
+      </c>
       <c r="I39" t="s">
         <v>18</v>
       </c>
@@ -2411,6 +2546,9 @@
       <c r="G40" t="s">
         <v>104</v>
       </c>
+      <c r="H40" t="s">
+        <v>260</v>
+      </c>
       <c r="I40" t="s">
         <v>18</v>
       </c>
@@ -2434,6 +2572,9 @@
       <c r="G41" t="s">
         <v>106</v>
       </c>
+      <c r="H41" t="s">
+        <v>261</v>
+      </c>
       <c r="I41" t="s">
         <v>18</v>
       </c>
@@ -2457,6 +2598,9 @@
       <c r="G42" t="s">
         <v>108</v>
       </c>
+      <c r="H42" t="s">
+        <v>262</v>
+      </c>
       <c r="I42" t="s">
         <v>18</v>
       </c>
@@ -2480,6 +2624,9 @@
       <c r="G43" t="s">
         <v>110</v>
       </c>
+      <c r="H43" t="s">
+        <v>263</v>
+      </c>
       <c r="I43" t="s">
         <v>18</v>
       </c>
@@ -2503,6 +2650,9 @@
       <c r="G44" t="s">
         <v>112</v>
       </c>
+      <c r="H44" t="s">
+        <v>264</v>
+      </c>
       <c r="I44" t="s">
         <v>18</v>
       </c>
@@ -2526,6 +2676,9 @@
       <c r="G45" t="s">
         <v>114</v>
       </c>
+      <c r="H45" t="s">
+        <v>265</v>
+      </c>
       <c r="I45" t="s">
         <v>18</v>
       </c>
@@ -2549,6 +2702,9 @@
       <c r="G46" t="s">
         <v>116</v>
       </c>
+      <c r="H46" t="s">
+        <v>266</v>
+      </c>
       <c r="I46" t="s">
         <v>18</v>
       </c>
@@ -2572,6 +2728,9 @@
       <c r="G47" t="s">
         <v>118</v>
       </c>
+      <c r="H47" t="s">
+        <v>267</v>
+      </c>
       <c r="I47" t="s">
         <v>18</v>
       </c>
@@ -2595,6 +2754,9 @@
       <c r="G48" t="s">
         <v>120</v>
       </c>
+      <c r="H48" t="s">
+        <v>268</v>
+      </c>
       <c r="I48" t="s">
         <v>18</v>
       </c>
@@ -2618,6 +2780,9 @@
       <c r="G49" t="s">
         <v>122</v>
       </c>
+      <c r="H49" t="s">
+        <v>269</v>
+      </c>
       <c r="I49" t="s">
         <v>18</v>
       </c>
@@ -2641,6 +2806,9 @@
       <c r="G50" t="s">
         <v>124</v>
       </c>
+      <c r="H50" s="44" t="s">
+        <v>270</v>
+      </c>
       <c r="I50" t="s">
         <v>18</v>
       </c>
@@ -2664,6 +2832,9 @@
       <c r="G51" t="s">
         <v>126</v>
       </c>
+      <c r="H51" t="s">
+        <v>271</v>
+      </c>
       <c r="I51" t="s">
         <v>18</v>
       </c>
@@ -2687,6 +2858,9 @@
       <c r="G52" t="s">
         <v>128</v>
       </c>
+      <c r="H52" t="s">
+        <v>272</v>
+      </c>
       <c r="I52" t="s">
         <v>18</v>
       </c>
@@ -2710,6 +2884,9 @@
       <c r="G53" t="s">
         <v>130</v>
       </c>
+      <c r="H53" t="s">
+        <v>273</v>
+      </c>
       <c r="I53" t="s">
         <v>18</v>
       </c>
@@ -2733,6 +2910,9 @@
       <c r="G54" t="s">
         <v>132</v>
       </c>
+      <c r="H54" t="s">
+        <v>273</v>
+      </c>
       <c r="I54" t="s">
         <v>18</v>
       </c>
@@ -2756,6 +2936,9 @@
       <c r="G55" t="s">
         <v>134</v>
       </c>
+      <c r="H55" t="s">
+        <v>274</v>
+      </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
@@ -2776,8 +2959,11 @@
       <c r="E56">
         <v>209000</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G56" s="44" t="s">
         <v>136</v>
+      </c>
+      <c r="H56" t="s">
+        <v>275</v>
       </c>
       <c r="I56" t="s">
         <v>18</v>
@@ -2799,6 +2985,11 @@
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G56" r:id="rId1" xr:uid="{51B4B247-5F7B-F340-8707-F8B6B881741F}"/>
+    <hyperlink ref="G29" r:id="rId2" xr:uid="{F62BFD74-43D4-C948-BF68-5ABBA550E7E0}"/>
+    <hyperlink ref="H50" r:id="rId3" xr:uid="{0776B790-E8F9-B348-81E9-896A77354059}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/affiliate/picks.xlsx
+++ b/data/affiliate/picks.xlsx
@@ -1333,7 +1333,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ai_calculator</t>
+          <t>ai_calculator_cpu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1343,20 +1343,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
+          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>169700</v>
+        <v>22700</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
+          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1364,24 +1364,19 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>mcwinner</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ai_calculator</t>
+          <t>ai_calculator_cpu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1391,20 +1386,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>301100</v>
+        <v>26500</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
+          <t>https://s.shopee.co.th/2g9IIXOei9</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1412,21 +1407,19 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ai_calculator</t>
+          <t>ai_calculator_cpu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,20 +1429,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>236900</v>
+        <v>10500</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaAsBag8T</t>
+          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1457,21 +1450,19 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>382</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ai_calculator</t>
+          <t>ai_calculator_cpu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1481,20 +1472,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>288900</v>
+        <v>33000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LduHGca9O</t>
+          <t>https://s.shopee.co.th/30m8h9NO2F</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1502,21 +1493,19 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ai_calculator</t>
+          <t>ai_calculator_cpu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1526,20 +1515,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
+          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>195500</v>
+        <v>29900</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
+          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1547,24 +1536,19 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>atSine Tech</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ai_calculator</t>
+          <t>ai_calculator_cpu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1574,20 +1558,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
+          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>180700</v>
+        <v>24200</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1113sedqpM</t>
+          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1595,21 +1579,19 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ai_calculator</t>
+          <t>ai_calculator_cpu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1619,20 +1601,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
+          <t>CPU AMD AM5 RYZEN 9 9950X3D (NEXT) - A0168684</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>180000</v>
+        <v>32200</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
+          <t>https://s.shopee.co.th/3qLFggKDLS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1640,18 +1622,13 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -1665,22 +1642,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>337700</v>
+        <v>169700</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gODU2f7VK</t>
+          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1695,7 +1677,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>I KNOW YOU</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -1713,22 +1695,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>204900</v>
+        <v>301100</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhdgLeUAN</t>
+          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1743,7 +1730,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -1758,22 +1745,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>193900</v>
+        <v>236900</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlN5QgOBI</t>
+          <t>https://s.shopee.co.th/1qaAsBag8T</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1803,22 +1795,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
+          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205600</v>
+        <v>288900</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4nHjfkqL</t>
+          <t>https://s.shopee.co.th/1LduHGca9O</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1833,7 +1830,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -1848,22 +1845,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
+          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>193400</v>
+        <v>195500</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18WgoherG</t>
+          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1878,8 +1880,11 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1893,22 +1898,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>189900</v>
+        <v>180700</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
+          <t>https://s.shopee.co.th/1113sedqpM</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1923,7 +1933,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -1938,22 +1948,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>198500</v>
+        <v>180000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XCe0OciG</t>
+          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1968,8 +1983,11 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1983,22 +2001,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
+          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>189000</v>
+        <v>337700</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
+          <t>https://s.shopee.co.th/gODU2f7VK</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2013,8 +2036,11 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>I KNOW YOU</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2028,22 +2054,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>192900</v>
+        <v>204900</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
+          <t>https://s.shopee.co.th/qhdgLeUAN</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2058,7 +2089,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -2073,22 +2104,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>187900</v>
+        <v>193900</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
+          <t>https://s.shopee.co.th/LlN5QgOBI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2103,7 +2139,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -2118,22 +2154,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
+          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>198500</v>
+        <v>205600</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
+          <t>https://s.shopee.co.th/W4nHjfkqL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2148,11 +2189,8 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>3</v>
+          <t>Advice Official Shop</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2166,22 +2204,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>195500</v>
+        <v>193400</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
+          <t>https://s.shopee.co.th/18WgoherG</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2196,7 +2239,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -2211,22 +2254,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
+          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>459500</v>
+        <v>189900</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40efSASQkA</t>
+          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2256,22 +2304,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>186900</v>
+        <v>198500</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
+          <t>https://s.shopee.co.th/50XCe0OciG</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2301,22 +2354,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
+          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>186900</v>
+        <v>189000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
+          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2346,22 +2404,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
+          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185500</v>
+        <v>192900</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLFFrT45B</t>
+          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2391,22 +2454,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
+          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>269500</v>
+        <v>187900</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOyewUy66</t>
+          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2436,22 +2504,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>195000</v>
+        <v>198500</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
+          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2468,6 +2541,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2481,9 +2557,14 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
+          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2491,12 +2572,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8GKWEm4</t>
+          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2526,22 +2607,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
+          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>179900</v>
+        <v>459500</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
+          <t>https://s.shopee.co.th/40efSASQkA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2571,22 +2657,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
+          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185500</v>
+        <v>186900</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2616,22 +2707,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
+          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>198500</v>
+        <v>186900</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSi41Ws75</t>
+          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2661,22 +2757,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>192900</v>
+        <v>185500</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXxouETJ2</t>
+          <t>https://s.shopee.co.th/3qLFFrT45B</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2706,22 +2807,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
+          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>188500</v>
+        <v>269500</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prO1DDpy5</t>
+          <t>https://s.shopee.co.th/3LOyewUy66</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2751,22 +2857,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
+          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>215000</v>
+        <v>195000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
+          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2796,22 +2907,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
+          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228800</v>
+        <v>195500</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
+          <t>https://s.shopee.co.th/30m8GKWEm4</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2826,7 +2942,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -2841,22 +2957,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
+          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>209000</v>
+        <v>179900</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70IH1gH0ey</t>
+          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2871,7 +2992,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>shoppingpc dotnet</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -2886,17 +3007,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>9000</v>
+        <v>185500</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbhDzGNK1</t>
+          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2911,17 +3042,14 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2929,23 +3057,27 @@
           <t>item</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>22700</v>
+        <v>198500</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
+          <t>https://s.shopee.co.th/2qSi41Ws75</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2953,19 +3085,21 @@
           <t>Shopee</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ขายดี</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>mcwinner</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>19</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2973,23 +3107,27 @@
           <t>item</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>26500</v>
+        <v>192900</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9IIXOei9</t>
+          <t>https://s.shopee.co.th/7fXxouETJ2</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2997,19 +3135,21 @@
           <t>Shopee</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ขายดี</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>6</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3017,23 +3157,27 @@
           <t>item</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10500</v>
+        <v>188500</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+          <t>https://s.shopee.co.th/7prO1DDpy5</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3041,19 +3185,21 @@
           <t>Shopee</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ขายดี</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>382</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3061,23 +3207,27 @@
           <t>item</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>33000</v>
+        <v>215000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3085,19 +3235,21 @@
           <t>Shopee</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ขายดี</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>6</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3105,23 +3257,27 @@
           <t>item</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>29900</v>
+        <v>228800</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3129,19 +3285,21 @@
           <t>Shopee</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ขายดี</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>atSine Tech</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>2</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3149,23 +3307,27 @@
           <t>item</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
+          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>24200</v>
+        <v>209000</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
+          <t>https://s.shopee.co.th/70IH1gH0ey</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3173,19 +3335,21 @@
           <t>Shopee</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ขายดี</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>4</v>
+          <t>shoppingpc dotnet</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3193,23 +3357,22 @@
           <t>item</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CPU AMD AM5 RYZEN 9 9950X3D (NEXT) - A0168684</t>
+          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>32200</v>
+        <v>9000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLFggKDLS</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+          <t>https://s.shopee.co.th/7AbhDzGNK1</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3217,13 +3380,18 @@
           <t>Shopee</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ขายดี</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EZGGTECH</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/affiliate/picks.xlsx
+++ b/data/affiliate/picks.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1333,7 +1333,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1341,22 +1341,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
+          <t>VGA การ์ดจอ PNY GeForce RTX 5080 16GB ARGB Overclocked Triple Fan DLSS 4 GDDR7</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>22700</v>
+        <v>51900</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
+          <t>https://s.shopee.co.th/9fJ7913vKx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mo4863r6po1v3b.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1366,17 +1371,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>mcwinner</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1384,22 +1389,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>GBT GF RTX 5080 GAMING OC 16G (Rev1.0)	GV-N5080GAMOC-16GD</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>26500</v>
+        <v>57600</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9IIXOei9</t>
+          <t>https://s.shopee.co.th/6AjEyaHFRI</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-mazph6oiow1i7d.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1409,17 +1419,14 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>6</v>
+          <t>Hp_by_iqink</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1427,22 +1434,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>ZOTAC GAMING GEFORCE RTX5080 SOLID CORE OC 16GB 256BIT GDDR7(P288-1N765-300Z8)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10500</v>
+        <v>56000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+          <t>https://s.shopee.co.th/60PomHHsmH</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8a9twwj7iemf8.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1452,17 +1464,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>TECHNOCOM.OFFICIAL</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>382</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1470,22 +1482,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>ASUS PRIME GEFORCE RTX5080 OC 16G GDDR7 (90YV0LX0-M0NA00)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>33000</v>
+        <v>63000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+          <t>https://s.shopee.co.th/6VM5NCFylO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m846xz01ff8u95.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1495,17 +1512,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>TECHNOCOM.OFFICIAL</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1513,22 +1530,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>29900</v>
+        <v>52900</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+          <t>https://s.shopee.co.th/6L2fAtGc6N</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmv7butau96u14.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1538,17 +1560,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>atSine Tech</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1556,22 +1575,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G GAMING TRIO OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>24200</v>
+        <v>62600</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
+          <t>https://s.shopee.co.th/5VTYBMJmnE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-moy490f3fuofce.webp</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1581,17 +1605,14 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>4</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1599,22 +1620,27 @@
           <t>item</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CPU AMD AM5 RYZEN 9 9950X3D (NEXT) - A0168684</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7 +  PSU ASUS 1200W ROG THOR 1200P3 80+PLATINUM MIKU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>32200</v>
+        <v>111000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLFggKDLS</t>
+          <t>https://s.shopee.co.th/5LA7z3KQ8D</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mmjrx4g2i8zn0b.webp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1624,11 +1650,8 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>11</v>
+          <t>D.P COMPUTER Hi End</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1644,25 +1667,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>169700</v>
+        <v>89900</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
+          <t>https://s.shopee.co.th/5q6OZyIW7K</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mpkfshwxt3ij71.webp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1670,18 +1693,10 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
+          <t>D.P COMPUTER Hi End</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1697,25 +1712,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5080 SOLID CORE OC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>301100</v>
+        <v>52200</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
+          <t>https://s.shopee.co.th/5fmyNfJ9SJ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mm1mtsp7op3402.webp</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1723,14 +1738,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>M.B Computer Store</t>
         </is>
       </c>
     </row>
@@ -1747,25 +1757,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 X3 OC - 16GB GDDR7 - A0182764</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>236900</v>
+        <v>56500</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaAsBag8T</t>
+          <t>https://s.shopee.co.th/7VEcZ2CAjg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpukkz1kncp821.webp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1773,14 +1783,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -1797,25 +1802,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL FROSTBITE OC - 16GB GDDR7 - A0182767</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>288900</v>
+        <v>71700</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LduHGca9O</t>
+          <t>https://s.shopee.co.th/7KvCMjCo4f</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mpukedl8v8ch88.webp</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1823,14 +1828,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -1847,25 +1847,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 WINDFORCE OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>195500</v>
+        <v>52900</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
+          <t>https://s.shopee.co.th/7prSxeAu3m</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkd8n452amth61.webp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1873,18 +1873,13 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -1900,25 +1895,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
+          <t>VGA การ์ดจอ ZOTAC GAMING GeForce RTX 5080 GAMING SOLID CORE OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>180700</v>
+        <v>52400</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1113sedqpM</t>
+          <t>https://s.shopee.co.th/7fY2lLBXOl</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mki0hzdcdlvk9a.webp</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1926,15 +1921,13 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1950,25 +1943,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 (PRIME-RTX5080-16G)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>180000</v>
+        <v>67600</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
+          <t>https://s.shopee.co.th/6pyvloEi5c</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4j8l8twxuce.webp</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1976,18 +1969,10 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>2</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2003,25 +1988,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>337700</v>
+        <v>55900</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gODU2f7VK</t>
+          <t>https://s.shopee.co.th/6ffVZVFLQb</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mmv7325j5mgxbb.webp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2029,18 +2014,10 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>I KNOW YOU</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2056,25 +2033,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>ASUS ROG ASTRAL RTX5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>204900</v>
+        <v>113000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhdgLeUAN</t>
+          <t>https://s.shopee.co.th/7AbmAQDRPi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mjxxy5kvxjied7.webp</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2082,14 +2059,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -2106,25 +2078,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>193900</v>
+        <v>71900</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlN5QgOBI</t>
+          <t>https://s.shopee.co.th/70ILy7E4kh</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mjjcxbr8kqo03d.webp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2132,14 +2104,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -2156,25 +2123,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC - 16GB GDDR7 (N50803-16D7X-17603930)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205600</v>
+        <v>59000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4nHjfkqL</t>
+          <t>https://s.shopee.co.th/3ViTngROr2</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbdla2gs3l9wca.webp</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2182,15 +2149,13 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2206,25 +2171,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
+          <t>MSI VGA GEFORCE RTX 5080 SHADOW 3X OC - 16GB GDDR7 - A0167047</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>193400</v>
+        <v>58000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18WgoherG</t>
+          <t>https://s.shopee.co.th/3LP3bNS2C1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rask-m9r5cxk7f42o1c.webp</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2232,14 +2197,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -2256,25 +2216,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 XTREME WATERFORCE - 16GB GDDR7 (REV. 1.0) - A0166365</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>189900</v>
+        <v>74200</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
+          <t>https://s.shopee.co.th/3qLKCIQ8B8</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-mai21hqfq6icd6.webp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2282,14 +2242,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -2306,25 +2261,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 AORUS MASTER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>198500</v>
+        <v>60700</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XCe0OciG</t>
+          <t>https://s.shopee.co.th/3g1tzzQlW7</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mky5qpeaknwi66.webp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2332,14 +2287,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -2356,25 +2306,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
+          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>189000</v>
+        <v>9000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
+          <t>https://s.shopee.co.th/2qSn0STwCy</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2382,15 +2332,13 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>EZGGTECH</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2406,25 +2354,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>192900</v>
+        <v>67900</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
+          <t>https://s.shopee.co.th/2g9Mo9UZXx</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4xoa7sr9r50.webp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2432,14 +2380,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2456,25 +2399,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC WHITE - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>187900</v>
+        <v>55900</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
+          <t>https://s.shopee.co.th/3B5dP4SfX4</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mqbi0037km4r5f.webp</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2482,14 +2425,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2506,25 +2444,25 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
+          <t>GALAX RTX5080 HOF GAMING BLACK EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>198500</v>
+        <v>87000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
+          <t>https://s.shopee.co.th/30mDClTIs3</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mi2smox3b8qo49.webp</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2532,18 +2470,10 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L41" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2559,35 +2489,30 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>195500</v>
+        <v>69500</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
+          <t>https://s.shopee.co.th/4qDrO8MK9Q</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9pqc1bk39ipd8.webp</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>Shopee</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2609,25 +2534,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G VENTUS 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>459500</v>
+        <v>64100</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40efSASQkA</t>
+          <t>https://s.shopee.co.th/4fuRBpMxUP</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmjx8u2c385h1b.webp</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2635,14 +2560,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2579,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 AERO OC - 16GB GDDR7 (REV. 1.0) - A0166362</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>186900</v>
+        <v>66200</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
+          <t>https://s.shopee.co.th/5AqhmkL3TW</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m9r5fxjheinlbf.webp</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2685,15 +2605,13 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2709,25 +2627,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 AORUS MASTER - 16GB GDDR7 (REV. 1.0) - A0166364</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>186900</v>
+        <v>70500</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
+          <t>https://s.shopee.co.th/50XHaRLgoV</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e59iq7j2a769.webp</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2735,14 +2653,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -2759,25 +2672,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 WHITE OC EDITION</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185500</v>
+        <v>79900</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLFFrT45B</t>
+          <t>https://s.shopee.co.th/4AyAauOrVM</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlljzbvrqccib8.webp</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2785,14 +2698,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -2809,25 +2717,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
+          <t>(มีโค้ดลด2000฿) RTX 5060 5060Ti 5060 ti 2060Super 3060 3060Ti 3070 3070Ti 4060 4060Ti 4070 4070Ti 4080 4090 5080 5090</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>269500</v>
+        <v>5000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOyewUy66</t>
+          <t>https://s.shopee.co.th/40ekObPUqL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2835,15 +2743,13 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>EZGGTECH</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="48">
@@ -2859,25 +2765,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
+          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>195000</v>
+        <v>21400</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
+          <t>https://s.shopee.co.th/4Vb0zWNapS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2885,14 +2791,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>3CCamera.th</t>
         </is>
       </c>
     </row>
@@ -2909,25 +2810,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Intel Core Ultra 9 285K + RTX 5080 | DDR5 64GB 6400MHz / SSD 2TB | โทนขาว / ชุดแต่ง Lian Li</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>195500</v>
+        <v>155700</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8GKWEm4</t>
+          <t>https://s.shopee.co.th/4LHanDOEAR</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfkgr2oabvux4c.webp</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2935,14 +2836,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -2959,35 +2855,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
+          <t>GIGABYTE RTX5080 AORUS XTREME WATERFORECE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>179900</v>
+        <v>89500</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
+          <t>https://s.shopee.co.th/qhicmbYGm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prhvzpau3yd2.webp</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>Shopee</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3009,35 +2900,30 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185500</v>
+        <v>66900</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+          <t>https://s.shopee.co.th/gOIQTcBbl</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9pqq1xfnr3i22.webp</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>Shopee</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3059,25 +2945,25 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>198500</v>
+        <v>75300</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSi41Ws75</t>
+          <t>https://s.shopee.co.th/1BKZ1OaHas</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mmwzh1437egx8f.webp</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3085,14 +2971,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -3109,25 +2990,25 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
+          <t>MSI VGA GEFORCE RTX 5080 VENTUS 3X OC - 16GB GDDR7 - A0167046</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>192900</v>
+        <v>60500</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXxouETJ2</t>
+          <t>https://s.shopee.co.th/1118p5auvr</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasf-m9r4yrpdj75afe.webp</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3135,14 +3016,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -3159,25 +3035,25 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 GAMING OC - 16GB GDDR7 (REV. 1.0) - A0166361</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>188500</v>
+        <v>65500</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prO1DDpy5</t>
+          <t>https://s.shopee.co.th/BS1pYe5ci</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9e55v65yvbda7.webp</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3185,14 +3061,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3080,25 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 ICHILL X3 V2 - 16GB GDDR7 C50803-16D7X-176069R</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>215000</v>
+        <v>64900</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
+          <t>https://s.shopee.co.th/18bdFeixh</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-modebjzln30gb5.webp</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3235,14 +3106,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -3259,25 +3125,25 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | RAM 64GB 6400MHz / SSD 2TB | โทนขาว / HYTE Y70 Touch</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228800</v>
+        <v>145900</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
+          <t>https://s.shopee.co.th/W4sEAcowo</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq8r6vopg3rg36.webp</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3285,14 +3151,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -3309,25 +3170,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
+          <t>ROG Zephyrus G18 G815LW-S9112W Asus U9-275HX32 G 1TB RTX5080 W11 3YOSS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>209000</v>
+        <v>125000</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70IH1gH0ey</t>
+          <t>https://s.shopee.co.th/LlS1rdSHn</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-me5o4gxp31mrb5.webp</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3335,14 +3196,9 @@
           <t>Shopee</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>shoppingpc dotnet</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -3359,39 +3215,3888 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>130900</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BD6DEWTZA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq90ma8arc3x60.webp</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MSI RTX5080 SHADOW 3X OC 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>67800</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20tg0vX6u9</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9prwjnh3cy749.webp</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5080 WINFOREC OC SFF 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>68500</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VpwbqVCtG</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prnu5bv9wxb3.webp</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 MASTER 16G - 16GB GDDR7 (GV-N5080AORUS M-16GD)</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>67900</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LWWPXVqEF</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbbxwlx4z7uc43.webp</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GALAX VGA GEFORCE RTX 5080 HOF GAMING BLACK - 16GB GDDR7 - A0172861</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>68400</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VxPQ0Z0v6</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-824je-me9vcwg1o3cw45.webp</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO OC - 16GB GDDR7 - A0180200</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>55500</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LdzDhZeG5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-82609-mmd4ly6nd341a5.webp</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 XTREME WATERFORCE 16G - 16GB GDDR7 (GV-N5080AORUSX W-16GD)</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>73800</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qaFocXkFC</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mbbxc0wleh6p7b.webp</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 16GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>130900</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gGpcJYNaB</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mq8stcq5cx6of7.webp</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MSI STEALTH A16 AI PLUS Ryzen AI 9 HX 370/RTX 5080 RAM64/2TB - ID26060441</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>113400</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fQZxB7jNY</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpuc7ehxc9ho8a.webp</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>10X Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Original 380W 20V 19A อะแดปเตอร์ชาร์จสําหรับ ASUS ROG Strix scar 16 2025 G635LW RTX5080 ADP-380AB B</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pk09U762b</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824jc-mep4jcmcgnphd5.webp</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>junyue999.th</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5080 AORUS MASTER ICE 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>82500</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/903QLn6She</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-map4vxrow1ao8a.webp</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>INNO3D RTX5080 X3 OC 16GB BLACK GDDR7</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>66900</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AMqY65pMh</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8d39ntj3z7289.webp</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC WHITE - 16GB GDDR7 (N50803-16D7X-17605211)</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>59000</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/80At9xAGjU</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbdmsesr8qk199.webp</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL X3 V2 OC - 16GB GDDR7 - A0182766</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>61800</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8AUJMG9dOX</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mpujxufur8y4aa.webp</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7 - A0166369</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>55500</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8KnjYZ903a</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0k-mc7mmx5y9omf72.webp</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>78500</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V79ks8Mid</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-me6x1j4ufmyqba.webp</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 WINDFORCE OC - 16GB GDDR7 (REV. 1.0) - A0166360</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>60300</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zvxXd2efw</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7ras8-m9r4yq4hudlb71.webp</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7 WHITE</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>69200</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAFNjw21Kz</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9pqwzx9tkvi06.webp</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GIGABYTE GAMING RTX5080 16 GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>75900</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AKYnwF1O02</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5zvhd595sc69a.webp</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 WINDFORCE OC SFF 16G - 16GB GDDR7 (GV-N5080WF3OC-16GD)</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>58800</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AUsE8Y0kf5</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbc1uyc222bab6.webp</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] MSI GAMING TRIO RTX5080 16 GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>72900</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KgGkP5C1s</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m5qng58cco0t25.webp</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RTX5080/16GB GALAX 1-CLICK (OC/D7) - A0166352</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>59600</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uzgwi4Ygv</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m81gt7mb1w4u18.webp</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 HOF GAMING BLACK EDITION - 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>70600</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fJ7913vLy</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdpq3ctyx2ta3e.webp</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5080 OC WHITE 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>89500</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pcXLK3I11</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-misduj582yo30b.webp</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ZOTAC RTX5080 SOLID GAMING OC 16GB GDDR7 WHITE</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>64900</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60PomHHsnI</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-mapdn0hs6q9gfb.webp</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>GALAX RTX5080 HOF GAMING 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>87000</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AjEyaHFSL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mi2scd35wirsed.webp</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GIGABYTE AERO RTX5080 16GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>78500</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6L2fAtGc7O</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mki1wyjsh14yd6.webp</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ZOTAC GAMING RTX5080 SOLID CORE OC 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VM5NCFymR</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mloguv0dy97323.webp</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5080 SOLID CORE OC - 16GB GDDR7 (ZT-B50800J2-10P)</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>59000</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5LA7z3KQ9E</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbvy43nc50gsdd.webp</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ASUS TUF RTX5080 GAMING OC 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>81000</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VTYBMJmoH</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m9pk6xb8lmjk47.webp</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>INNO3D RTX5080 X3 OC WHITE 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>68300</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5fmyNfJ9TK</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8d2yz7814ax90.webp</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7 (GV-N5080AERO OC-16GD)</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>67000</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q6OZyIW8N</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbbyjj2rglflce.webp</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE AORUS RTX5080 MASTER 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>80900</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KvCMjCo5g</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml4sii5ubnym20.webp</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ROG ASTRAL RTX5080 16GB OC GDDR7 BLACK</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>85500</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VEcZ2CAkj</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq632jnzevwuf9.webp</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ROG ASTRAL RTX5080 16 GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>88500</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fY2lLBXPm</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5p939h7ybw69b.webp</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>MSI RTX5080 VENTUS X3 OC PLUS 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>63000</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7prSxeAu4p</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mnkzq2y21x51b3.webp</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ASUS PRIME RTX5080 OC 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>74300</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6ffVZVFLRc</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9pl3a6dymlq34.webp</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G SHADOW 3X OC - 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>60500</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6pyvloEi6f</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m807f87tz7xq68.webp</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 GAMING OC 16G - 16GB GDDR7 (GV-N5080GAMING OC-16GD)</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>63500</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70ILy7E4li</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0o-mbbz0v0mfsdt28.webp</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC - 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>61400</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7AbmAQDRQl</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0g-mb65w0t41ai927.webp</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5080 16GB GDDR7 OC EDITION (TUF-RTX5080-O16G-GAMING)</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>71700</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LP3bNS2D2</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mb7lu03gdf7ace.webp</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>63900</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViTngROs5</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9qqhz75s2cu0e.webp</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์ประกอบ HYTE Y40 RTX5080 BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>155900</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g1tzzQlX8</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m5v66xgrzeuv7b.webp</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์ประกอบ HTYE Y60 RTX5080 OC GDDR7 BLACK</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>159000</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qLKCIQ8CB</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m63p4ze31cil46.webp</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
           <t>5090</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/7AbhDzGNK1</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>ขายดี</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>EZGGTECH</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>169700</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>301100</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>236900</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qaAsBag8T</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>288900</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LduHGca9O</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>195500</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>180700</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1113sedqpM</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>337700</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gODU2f7VK</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>I KNOW YOU</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>204900</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/qhdgLeUAN</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>193900</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LlN5QgOBI</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>205600</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W4nHjfkqL</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>193400</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/18WgoherG</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>189900</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>198500</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50XCe0OciG</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>189000</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>192900</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>187900</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>198500</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>195500</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>459500</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40efSASQkA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>186900</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>186900</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>185500</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qLFFrT45B</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>269500</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOyewUy66</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>195000</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>195500</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30m8GKWEm4</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>179900</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>185500</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>198500</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qSi41Ws75</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>192900</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXxouETJ2</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>188500</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7prO1DDpy5</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>215000</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>228800</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>209000</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70IH1gH0ey</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>shoppingpc dotnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>22700</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>mcwinner</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>26500</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g9IIXOei9</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>33000</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>29900</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>atSine Tech</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>24200</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CPU AMD AM5 RYZEN 9 9950X3D (NEXT) - A0168684</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>32200</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qLFggKDLS</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/affiliate/picks.xlsx
+++ b/data/affiliate/picks.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N142"/>
+  <dimension ref="A1:N240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1343,25 +1343,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ PNY GeForce RTX 5080 16GB ARGB Overclocked Triple Fan DLSS 4 GDDR7</t>
+          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>51900</v>
+        <v>9000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7913vKx</t>
+          <t>https://s.shopee.co.th/8pk0FdV2MF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mo4863r6po1v3b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EZGGTECH</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1391,25 +1391,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GBT GF RTX 5080 GAMING OC 16G (Rev1.0)	GV-N5080GAMOC-16GD</t>
+          <t>(15,990฿) GALAX RTX 5070 12G RGB🌈 ของใหม่ มือ1</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>57600</v>
+        <v>9600</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjEyaHFRI</t>
+          <t>https://s.shopee.co.th/8KnjeiWwNA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-mazph6oiow1i7d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mfcwvayul2x892.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1419,8 +1419,11 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Hp_by_iqink</t>
-        </is>
+          <t>การ์ดจอมือสอง อุปกรณ์คอม</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1436,25 +1439,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING GEFORCE RTX5080 SOLID CORE OC 16GB 256BIT GDDR7(P288-1N765-300Z8)</t>
+          <t>VGA ZOTAC GAMING GEFORCE RTX 5070 SOLID OC 12GB GDDR7 (ZT-B50700J-10P) (รับประกัน3ปี)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>56000</v>
+        <v>26200</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PomHHsmH</t>
+          <t>https://s.shopee.co.th/8V79r1WJ2D</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8a9twwj7iemf8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-me8br9vvoe11c5.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1464,11 +1467,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
+          <t>pansonics</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20">
@@ -1484,25 +1487,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ASUS PRIME GEFORCE RTX5080 OC 16G GDDR7 (90YV0LX0-M0NA00)</t>
+          <t>VGA GALAX GEFORCE RTX 5070 EX Gamer 1-Click OC 12GB GDDR7 192-bit (รับประกัน3ปี)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>63000</v>
+        <v>28900</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5NCFylO</t>
+          <t>https://s.shopee.co.th/80AtG6YD38</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m846xz01ff8u95.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mkknnqo1ueww40.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1512,11 +1515,11 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
+          <t>pansonics</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1532,25 +1535,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7</t>
+          <t>VGA ASUS PRIME GEFORCE RTX 5070 WHITE OC  EDITION 12GB GDDR7 (รับประกัน3ปี)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>52900</v>
+        <v>31500</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fAtGc6N</t>
+          <t>https://s.shopee.co.th/8AUJSPXZiB</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmv7butau96u14.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfupu0o5b7kf65.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1560,8 +1563,11 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
-        </is>
+          <t>pansonics</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1577,25 +1583,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G GAMING TRIO OC - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G SHADOW 3X OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>62600</v>
+        <v>23900</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYBMJmnE</t>
+          <t>https://s.shopee.co.th/AKYo2OPKJc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-moy490f3fuofce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mlygum4567er09.webp</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1607,6 +1613,9 @@
         <is>
           <t>แอดบอล คอมพิวเตอร์</t>
         </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1622,25 +1631,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7 +  PSU ASUS 1200W ROG THOR 1200P3 80+PLATINUM MIKU</t>
+          <t>VGA (การ์ดแสดงผล) ASUS DUAL GEFORCE RTX 5070 12GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>111000</v>
+        <v>23900</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA7z3KQ8D</t>
+          <t>https://s.shopee.co.th/AUsEEhOgyf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mmjrx4g2i8zn0b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlj56pbe4c1t6c.webp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1650,7 +1659,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>D.P COMPUTER Hi End</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -1667,25 +1676,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 12GB GDDR7 (PRIME-RTX5070-12G)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>89900</v>
+        <v>27500</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6OZyIW7K</t>
+          <t>https://s.shopee.co.th/9zvxdmQaza</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mpkfshwxt3ij71.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mhgdx8jz03cwa4.webp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1695,7 +1704,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>D.P COMPUTER Hi End</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -1712,25 +1721,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5080 SOLID CORE OC</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 12GB GDDR7 OC EDITION (PRIME-RTX5070-O12G)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>52200</v>
+        <v>28900</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyNfJ9SJ</t>
+          <t>https://s.shopee.co.th/AAFNq5Pxed</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mm1mtsp7op3402.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mm74uk247pc1bd.webp</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1740,7 +1749,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>M.B Computer Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -1757,25 +1766,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 X3 OC - 16GB GDDR7 - A0182764</t>
+          <t>VGA (การ์ดแสดงผล) PNY GEFORCE RTX 5070 ARGB EPIC-X RGB OVERCLOCKED TRIPLE FAN - 12GB GDDR7 VCG507012TFXXPB1-O</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>56500</v>
+        <v>29000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcZ2CAjg</t>
+          <t>https://s.shopee.co.th/9fJ7FARrfY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpukkz1kncp821.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mkgpazghoefa01.webp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1785,7 +1794,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -1802,25 +1811,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL FROSTBITE OC - 16GB GDDR7 - A0182767</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 TI 16GB GDDR7</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>71700</v>
+        <v>39000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCMjCo4f</t>
+          <t>https://s.shopee.co.th/9pcXRTREKb</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mpukedl8v8ch88.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mm1j7jihgoap88.webp</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1830,7 +1839,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -1847,25 +1856,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 WINDFORCE OC SFF 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5070 GAMINGPRO - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>52900</v>
+        <v>25900</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prSxeAu3m</t>
+          <t>https://s.shopee.co.th/9KgGqYT8LW</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkd8n452amth61.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mm73lr6fcc8wde.webp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1875,11 +1884,8 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>10</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1895,25 +1901,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ ZOTAC GAMING GeForce RTX 5080 GAMING SOLID CORE OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) VGA COLORFUL GEFORCE RTX 5070 TI BATTLE AX - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>52400</v>
+        <v>40000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2lLBXOl</t>
+          <t>https://s.shopee.co.th/9Uzh2rSV0Z</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mki0hzdcdlvk9a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mkgrq7veafpg48.webp</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1923,11 +1929,8 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>4</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1943,25 +1946,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 (PRIME-RTX5080-16G)</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 GAMING OC 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>67600</v>
+        <v>28500</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvloEi5c</t>
+          <t>https://s.shopee.co.th/6L2fH2eYQy</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4j8l8twxuce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mhgh1lfdj6de72.webp</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1988,25 +1991,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G GAMING TRIO OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>55900</v>
+        <v>34500</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVZVFLQb</t>
+          <t>https://s.shopee.co.th/6VM5TLdv61</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mmv7325j5mgxbb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mlj63he5z9j5eb.webp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2018,6 +2021,9 @@
         <is>
           <t>แอดบอล คอมพิวเตอร์</t>
         </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2033,25 +2039,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 TI X3 - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>113000</v>
+        <v>39900</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmAQDRPi</t>
+          <t>https://s.shopee.co.th/60PosQfp6w</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mjxxy5kvxjied7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mnb3ffe2756p85.webp</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2061,7 +2067,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2078,25 +2084,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 EX GAMER 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 TWIN X2 OC WHITE - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>71900</v>
+        <v>27900</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70ILy7E4kh</t>
+          <t>https://s.shopee.co.th/6AjF4jfBlz</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mjjcxbr8kqo03d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mm74le80axhg26.webp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2106,7 +2112,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2123,25 +2129,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC - 16GB GDDR7 (N50803-16D7X-17603930)</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G SHADOW 2X OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>59000</v>
+        <v>25500</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTngROr2</t>
+          <t>https://s.shopee.co.th/5fmyToh5mu</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbdla2gs3l9wca.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlyf8z1anrbc9a.webp</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2151,11 +2157,8 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2171,25 +2174,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MSI VGA GEFORCE RTX 5080 SHADOW 3X OC - 16GB GDDR7 - A0167047</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 TI EX GAMER 1-CLICK OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>58000</v>
+        <v>39900</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3bNS2C1</t>
+          <t>https://s.shopee.co.th/5q6Og7gSRx</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rask-m9r5cxk7f42o1c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mn5rk2rprw1u22.webp</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2199,7 +2202,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2216,25 +2219,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 XTREME WATERFORCE - 16GB GDDR7 (REV. 1.0) - A0166365</t>
+          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5070 12GB GDDR7 OC EDITION (TUF-RTX5070-O12G-GAMING)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>74200</v>
+        <v>29400</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKCIQ8B8</t>
+          <t>https://s.shopee.co.th/5LA85CiMSs</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-mai21hqfq6icd6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mhge8e0c0utj90.webp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2244,7 +2247,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2261,25 +2264,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 AORUS MASTER 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G INSPIRE 3X OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60700</v>
+        <v>31900</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1tzzQlW7</t>
+          <t>https://s.shopee.co.th/5VTYHVhj7v</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mky5qpeaknwi66.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mn33svflo9ok19.webp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2289,7 +2292,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2306,25 +2309,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 TI 16G SHADOW 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9000</v>
+        <v>39900</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSn0STwCy</t>
+          <t>https://s.shopee.co.th/7fY2rUZTjM</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mofl9m7g2m1bfe.webp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2334,11 +2337,8 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2354,25 +2354,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 AERO OC 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>67900</v>
+        <v>28900</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9Mo9UZXx</t>
+          <t>https://s.shopee.co.th/7prT3nYqOP</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4xoa7sr9r50.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlj4jn7p52bn89.webp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2399,25 +2399,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC WHITE - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5070 TI GAMINGPRO - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>55900</v>
+        <v>40000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5dP4SfX4</t>
+          <t>https://s.shopee.co.th/7KvCSsakPK</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mqbi0037km4r5f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mn5s9hngkwzo32.webp</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2444,25 +2444,25 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 HOF GAMING BLACK EDITION 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 WHITE OC EDITION 12GB GDDR7</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>87000</v>
+        <v>28000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30mDClTIs3</t>
+          <t>https://s.shopee.co.th/7VEcfBa74N</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mi2smox3b8qo49.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mlj8li0hw7pgca.webp</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 1-CLICK OC WHITE - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>69500</v>
+        <v>27500</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDrO8MK9Q</t>
+          <t>https://s.shopee.co.th/70IM4Gc15I</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9pqc1bk39ipd8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134201-81ztk-mhg4bj1gpse8cf.webp</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2534,25 +2534,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G VENTUS 3X OC - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 TWIN X2 - 12GB GDDR7 (N50702-12D7-195064N)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>64100</v>
+        <v>25500</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuRBpMxUP</t>
+          <t>https://s.shopee.co.th/7AbmGZbNkL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmjx8u2c385h1b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mlj48zqab1twc0.webp</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2579,25 +2579,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 AERO OC - 16GB GDDR7 (REV. 1.0) - A0166362</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG STRIX GEFORCE RTX 5070 TI 16GB GDDR7</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>66200</v>
+        <v>47500</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqhmkL3TW</t>
+          <t>https://s.shopee.co.th/6ffVfedHlG</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m9r5fxjheinlbf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mm748jdbevwgb8.webp</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2607,11 +2607,8 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>3</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2627,25 +2624,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VGA GIGABYTE GEFORCE RTX 5080 AORUS MASTER - 16GB GDDR7 (REV. 1.0) - A0166364</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 EAGLE OC ICE SFF 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70500</v>
+        <v>29000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XHaRLgoV</t>
+          <t>https://s.shopee.co.th/6pyvrxceQJ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e59iq7j2a769.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mlj6cvh6afpcfc.webp</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2655,7 +2652,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2672,25 +2669,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 WHITE OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 EAGLE OC SFF 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>79900</v>
+        <v>24900</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4AyAauOrVM</t>
+          <t>https://s.shopee.co.th/3g1u68ohqi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlljzbvrqccib8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mlj49goxj4sg7b.webp</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2700,7 +2697,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2717,25 +2714,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(มีโค้ดลด2000฿) RTX 5060 5060Ti 5060 ti 2060Super 3060 3060Ti 3070 3070Ti 4060 4060Ti 4070 4070Ti 4080 4090 5080 5090</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 EX GAMER 1-CLICK OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5000</v>
+        <v>26500</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40ekObPUqL</t>
+          <t>https://s.shopee.co.th/3qLKIRo4Vl</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mhfxc8du1vkad3.webp</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2745,11 +2742,8 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>23</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -2765,25 +2759,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 TI 16G VENTUS 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>21400</v>
+        <v>39900</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vb0zWNapS</t>
+          <t>https://s.shopee.co.th/3LP3hWpyWg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkgq0zywyzgk9b.webp</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2793,7 +2787,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>3CCamera.th</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2810,25 +2804,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Intel Core Ultra 9 285K + RTX 5080 | DDR5 64GB 6400MHz / SSD 2TB | โทนขาว / ชุดแต่ง Lian Li</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5070 TWIN EDGE - 12GB GDDR7 (ZT-B50700E-10P)</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>155700</v>
+        <v>22000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHanDOEAR</t>
+          <t>https://s.shopee.co.th/3ViTtppLBj</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfkgr2oabvux4c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mhggp8eo347a7a.webp</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2838,7 +2832,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2855,25 +2849,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 AORUS XTREME WATERFORECE 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 TI 1-CLICK OC 2X - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>89500</v>
+        <v>39900</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhicmbYGm</t>
+          <t>https://s.shopee.co.th/30mDIurFCe</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prhvzpau3yd2.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mjqqmfpm9fd0ef.webp</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2883,8 +2877,11 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2900,25 +2897,25 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7 WHITE</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 EX GAMER 1-CLICK OC WHITE - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>66900</v>
+        <v>28600</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gOIQTcBbl</t>
+          <t>https://s.shopee.co.th/3B5dVDqbrh</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9pqq1xfnr3i22.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mkgpmmnbvkee06.webp</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2928,7 +2925,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2945,25 +2942,25 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 WINDFORCE OC SFF 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>75300</v>
+        <v>27000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKZ1OaHas</t>
+          <t>https://s.shopee.co.th/2g9MuIsVsc</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mmwzh1437egx8f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mhgg3kczd3wj7a.webp</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2973,7 +2970,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -2990,25 +2987,25 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MSI VGA GEFORCE RTX 5080 VENTUS 3X OC - 16GB GDDR7 - A0167046</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG STRIX GEFORCE RTX 5070 12GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>60500</v>
+        <v>34600</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1118p5auvr</t>
+          <t>https://s.shopee.co.th/2qSn6brsXf</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasf-m9r4yrpdj75afe.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mhgdehhugembdd.webp</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3018,7 +3015,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3035,25 +3032,25 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VGA GIGABYTE GEFORCE RTX 5080 GAMING OC - 16GB GDDR7 (REV. 1.0) - A0166361</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G VANGUARD SOC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65500</v>
+        <v>29000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BS1pYe5ci</t>
+          <t>https://s.shopee.co.th/50XHgajd96</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9e55v65yvbda7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mlj7htauark48d.webp</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3063,7 +3060,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3080,25 +3077,25 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 ICHILL X3 V2 - 16GB GDDR7 C50803-16D7X-176069R</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5070 INFINITY 3 - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>64900</v>
+        <v>24900</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18bdFeixh</t>
+          <t>https://s.shopee.co.th/5Aqhstizo9</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-modebjzln30gb5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlj6vysxk9vs85.webp</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3108,7 +3105,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3125,25 +3122,25 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | RAM 64GB 6400MHz / SSD 2TB | โทนขาว / HYTE Y70 Touch</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 TI GAMING OC 16G - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>145900</v>
+        <v>38900</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4sEAcowo</t>
+          <t>https://s.shopee.co.th/4fuRHyktp4</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq8r6vopg3rg36.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-merzaz171ts0c9.webp</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3153,8 +3150,11 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3170,25 +3170,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ROG Zephyrus G18 G815LW-S9112W Asus U9-275HX32 G 1TB RTX5080 W11 3YOSS</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 1-CLICK OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>125000</v>
+        <v>27900</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlS1rdSHn</t>
+          <t>https://s.shopee.co.th/4qDrUHkGU7</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-me5o4gxp31mrb5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mhfx1sjd3rpna9.webp</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>NOTEBOOK  CORP</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G VENTUS 2X OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>130900</v>
+        <v>27500</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD6DEWTZA</t>
+          <t>https://s.shopee.co.th/4LHatMmAV2</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq90ma8arc3x60.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zti-mkgs6ubokcg4e6.webp</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3260,25 +3260,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MSI RTX5080 SHADOW 3X OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5070 MASTER 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>67800</v>
+        <v>32900</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20tg0vX6u9</t>
+          <t>https://s.shopee.co.th/4Vb15flXA5</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9prwjnh3cy749.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mlj51w24z1u08f.webp</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3305,25 +3305,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 WINFOREC OC SFF 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 X3 OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>68500</v>
+        <v>25500</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2VpwbqVCtG</t>
+          <t>https://s.shopee.co.th/40ekUknRB0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prnu5bv9wxb3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlj485n39xcf69.webp</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3350,25 +3350,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 MASTER 16G - 16GB GDDR7 (GV-N5080AORUS M-16GD)</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5070 TI OC EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>67900</v>
+        <v>41500</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2LWWPXVqEF</t>
+          <t>https://s.shopee.co.th/4AyAh3mnq3</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbbxwlx4z7uc43.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mn5rzhzup53a0c.webp</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3395,25 +3395,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GALAX VGA GEFORCE RTX 5080 HOF GAMING BLACK - 16GB GDDR7 - A0172861</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 TI HOF GAMING - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>68400</v>
+        <v>48500</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxPQ0Z0v6</t>
+          <t>https://s.shopee.co.th/1118vEyrGS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134275-824je-me9vcwg1o3cw45.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlygemsgbev722.webp</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3440,25 +3440,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO OC - 16GB GDDR7 - A0180200</t>
+          <t>ชุดคอมประกอบ AMD Ryzen 7 7800X3D 5.0GHz/B650M/DDR5 32GB (16X2) 5200/M.2 512GB/PSU750W/ RTX 5070</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>55500</v>
+        <v>65700</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LdzDhZeG5</t>
+          <t>https://s.shopee.co.th/1BKZ7XyDvV</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134275-82609-mmd4ly6nd341a5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mp9d847uhgjm80.webp</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3485,25 +3485,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 XTREME WATERFORCE 16G - 16GB GDDR7 (GV-N5080AORUSX W-16GD)</t>
+          <t>ชุดคอมประกอบ AMD Ryzen 7 7900X3D 5.6GHz/B650M/DDR5 32GB (16X2) 5200/M.2 512GB/PSU750W/ RTX 5070</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>73800</v>
+        <v>65700</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaFocXkFC</t>
+          <t>https://s.shopee.co.th/gOIWd07wQ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mbbxc0wleh6p7b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mpgo7nupupzj78.webp</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3530,25 +3530,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 16GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>ชุดคอมประกอบ INTEL CORE I7 12700KF 5.0 GHz/B760M/DDR4 32GB (16X2) 3200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>130900</v>
+        <v>47400</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGpcJYNaB</t>
+          <t>https://s.shopee.co.th/qhiivzUbT</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mq8stcq5cx6of7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mp11k4bg9bt924.webp</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3575,25 +3575,25 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MSI STEALTH A16 AI PLUS Ryzen AI 9 HX 370/RTX 5080 RAM64/2TB - ID26060441</t>
+          <t>ชุดคอมประกอบ AMD RYZEN 5 7500F 5.0 GHz/A620M/DDR5 32GB (16X2) 5200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>113400</v>
+        <v>52000</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fQZxB7jNY</t>
+          <t>https://s.shopee.co.th/LlS811OcO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpuc7ehxc9ho8a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mpaacvrbqh36c5.webp</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>10X Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3620,25 +3620,25 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Original 380W 20V 19A อะแดปเตอร์ชาร์จสําหรับ ASUS ROG Strix scar 16 2025 G635LW RTX5080 ADP-380AB B</t>
+          <t>ชุดคอมประกอบ INTEL CORE I7 12700 4.9 GHz/B660M/DDR4 32GB (16X2) 3200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6400</v>
+        <v>52700</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pk09U762b</t>
+          <t>https://s.shopee.co.th/W4sKK0lHR</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824jc-mep4jcmcgnphd5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mq8m96d4luyz2c.webp</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3648,11 +3648,8 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>junyue999.th</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>3</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -3668,25 +3665,25 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 AORUS MASTER ICE 16GB GDDR7</t>
+          <t>ชุดคอมประกอบ INTEL I7 14700K 5.6 GHz/B760M /DDR4 32GB (16X2) BUS 3200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>82500</v>
+        <v>62500</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/903QLn6She</t>
+          <t>https://s.shopee.co.th/18bjP2fIM</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-map4vxrow1ao8a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mpdp2grbr4su76.webp</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3696,11 +3693,8 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>1</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -3716,25 +3710,25 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>INNO3D RTX5080 X3 OC 16GB BLACK GDDR7</t>
+          <t>ชุดคอมประกอบ INTEL I7 14700F 5.4 GHz/B760M WIFI/DDR5 32GB (16X2) BUS 6000/M.2 1TB/850W/เลือกเคสได้ RTX 5070</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>66900</v>
+        <v>62900</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AMqY65pMh</t>
+          <t>https://s.shopee.co.th/BS1vi21xP</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8d39ntj3z7289.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mkkgsvb7j4ee42.webp</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3744,7 +3738,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3761,25 +3755,25 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC WHITE - 16GB GDDR7 (N50803-16D7X-17605211)</t>
+          <t>ชุดคอมประกอบ AMD Ryzen 7 5800X 4.7 GHz/B550/DDR4 32GB (16X2) 3200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>59000</v>
+        <v>54800</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/80At9xAGjU</t>
+          <t>https://s.shopee.co.th/2LWWVgtmYq</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbdmsesr8qk199.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mpvht7ozql1pdf.webp</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3789,7 +3783,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3806,25 +3800,25 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL X3 V2 OC - 16GB GDDR7 - A0182766</t>
+          <t>ชุดคอมประกอบ INTEL CORE I5 14500 5.0 GHz/B760M/DDR4 32GB (16X2) 3200/M.2 1TB/750W/เลือกเคสได้ RTX 5070</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>61800</v>
+        <v>48400</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8AUJMG9dOX</t>
+          <t>https://s.shopee.co.th/2Vpwhzt9Dt</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mpujxufur8y4aa.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mp0mdj79btoi6a.webp</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3834,7 +3828,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -3851,25 +3845,25 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7 - A0166369</t>
+          <t>ชุดคอมประกอบ INTEL CORE I5 13500 4.8 GHz/B760M/DDR4 32GB (16X2) 3200/M.2 1TB/750W/เลือกเคสได้ RTX 5070</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>55500</v>
+        <v>47000</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8KnjYZ903a</t>
+          <t>https://s.shopee.co.th/20tg74v3Eo</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0k-mc7mmx5y9omf72.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mp0jaoe0uznk6b.webp</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3879,11 +3873,8 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>3</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -3899,25 +3890,25 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+          <t>BOSSPC / INTEL CORE ULTRA 5 225F / 32GB DDR5 BUS6000 RGB / RTX 5070 12GB / M.2 1TB</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>78500</v>
+        <v>77500</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8V79ks8Mid</t>
+          <t>https://s.shopee.co.th/2BD6JNuPtr</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-me6x1j4ufmyqba.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mnnrlzy11m9v63.webp</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3927,11 +3918,8 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>1</v>
+          <t>BOSSPC</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -3947,25 +3935,25 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 WINDFORCE OC - 16GB GDDR7 (REV. 1.0) - A0166360</t>
+          <t>TwithIT การ์ดจอ VGA Graphic Card GPU GTX 1060/1050Ti/1650 RTX 3050/3060/4060/5060/5060Ti/5070</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>60300</v>
+        <v>3500</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9zvxXd2efw</t>
+          <t>https://s.shopee.co.th/1gGpiSwJum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7ras8-m9r4yq4hudlb71.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mpzcowidfwnf22.webp</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3975,11 +3963,11 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>TwithTech</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -3995,25 +3983,25 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 EX GAMER 16GB GDDR7 WHITE</t>
+          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>69200</v>
+        <v>21400</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAFNjw21Kz</t>
+          <t>https://s.shopee.co.th/1qaFulvgZp</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9pqwzx9tkvi06.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4023,7 +4011,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>3CCamera.th</t>
         </is>
       </c>
     </row>
@@ -4040,25 +4028,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>GIGABYTE GAMING RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>Alphacool Water Block เข้ากันได้กับ RTX 5080 / 5070 Ti INNO3D และ MSI ASIC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>75900</v>
+        <v>14900</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKYnwF1O02</t>
+          <t>https://s.shopee.co.th/1LdzJqxaak</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5zvhd595sc69a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-820l4-mm01f4p4ojd49c.webp</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4068,7 +4056,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>133lnxgoshop.th</t>
         </is>
       </c>
     </row>
@@ -4085,25 +4073,25 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 WINDFORCE OC SFF 16G - 16GB GDDR7 (GV-N5080WF3OC-16GD)</t>
+          <t>VGA ZOTAC GEFORCE RTX 5070 GAMING TWIN EDGE OC - 12GB GDDR7 มือสอง</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>58800</v>
+        <v>24600</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AUsE8Y0kf5</t>
+          <t>https://s.shopee.co.th/1VxPW9wxFn</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbc1uyc222bab6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mq00fruhkkxs6b.webp</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4113,7 +4101,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>M&amp;N Computer</t>
         </is>
       </c>
     </row>
@@ -4130,25 +4118,25 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] MSI GAMING TRIO RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>Geforce RTX 5070 OC 12GB GDDR7 Snow Fox DLSS 4 Esports Design Live AI กราฟิกการ์ดสําหรับเล่นเกมอิสระ</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>72900</v>
+        <v>90500</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9KgGkP5C1s</t>
+          <t>https://s.shopee.co.th/9AMqeFTlhI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m5qng58cco0t25.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7renx-m8d3bdfuxnswe8.webp</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4158,11 +4146,8 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
+          <t>PC Accessories Shop</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -4178,25 +4163,25 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RTX5080/16GB GALAX 1-CLICK (OC/D7) - A0166352</t>
+          <t>คอมประกอบครบชุด SPCOMZING RYZEN5 5600 / M.2 500GB / RTX 5070 12GB / B550M / 32GB DDR4 / จอ 24นิ้ว</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>59600</v>
+        <v>26700</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9Uzgwi4Ygv</t>
+          <t>https://s.shopee.co.th/903QRwUP2H</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m81gt7mb1w4u18.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mp20d8fdwykh66.webp</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4206,11 +4191,8 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>11</v>
+          <t>SPCOMZING</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -4226,25 +4208,25 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 HOF GAMING BLACK EDITION - 16GB GDDR7</t>
+          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT VOID OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>70600</v>
+        <v>46000</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7913vLy</t>
+          <t>https://s.shopee.co.th/8pk0FdV2NG</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdpq3ctyx2ta3e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mln8wxv1kao1df.webp</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4254,7 +4236,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -4271,25 +4253,25 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5080 OC WHITE 16GB GDDR7</t>
+          <t>GALAX RTX5070 EX GAMER 12GB GDDR7</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>89500</v>
+        <v>35000</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9pcXLK3I11</t>
+          <t>https://s.shopee.co.th/8fQa3KVfiF</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-misduj582yo30b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-ml3do6g159fm84.webp</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4316,25 +4298,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5080 SOLID GAMING OC 16GB GDDR7 WHITE</t>
+          <t>GIGABYTE RTX5070 AERO OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>64900</v>
+        <v>37900</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PomHHsnI</t>
+          <t>https://s.shopee.co.th/8V79r1WJ3E</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-mapdn0hs6q9gfb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-ml3b0ujyyigw9f.webp</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4361,25 +4343,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 HOF GAMING 16GB GDDR7</t>
+          <t>ZOTAC GAMING RTX5070 TWIN EDGE 12GB GDDR7</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>87000</v>
+        <v>31000</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjEyaHFSL</t>
+          <t>https://s.shopee.co.th/8KnjeiWwOD</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mi2scd35wirsed.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-ma9clcgr2jrn46.webp</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4406,25 +4388,25 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GIGABYTE AERO RTX5080 16GB GDDR7 OC EDITION</t>
+          <t>INNO3D RTX5070 TWIN X2 OC 12GB WHITE GDDR7</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>78500</v>
+        <v>33600</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fAtGc7O</t>
+          <t>https://s.shopee.co.th/8AUJSPXZjC</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mki1wyjsh14yd6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8fpz7z7z3m167.webp</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4436,9 +4418,6 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L84" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -4454,25 +4433,25 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5080 SOLID CORE OC 16GB GDDR7</t>
+          <t>MSI RTX5070 GAMING TRIO OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>62500</v>
+        <v>36300</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5NCFymR</t>
+          <t>https://s.shopee.co.th/80AtG6YD4B</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mloguv0dy97323.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8fplkpwu26459.webp</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4499,25 +4478,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5080 SOLID CORE OC - 16GB GDDR7 (ZT-B50800J2-10P)</t>
+          <t>GALAX RTX5070 1-CLICK 12GB OC GDDR7</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>59000</v>
+        <v>32800</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA7z3KQ9E</t>
+          <t>https://s.shopee.co.th/AUsEEhOgzg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbvy43nc50gsdd.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m7t43sao8g0oc9.webp</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4527,7 +4506,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -4544,25 +4523,25 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ASUS TUF RTX5080 GAMING OC 16GB GDDR7</t>
+          <t>MSI RTX5070 VANGUARD SOC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>81000</v>
+        <v>42900</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYBMJmoH</t>
+          <t>https://s.shopee.co.th/AKYo2OPKKf</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m9pk6xb8lmjk47.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m7t7pn5x4rli2a.webp</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4589,25 +4568,25 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>INNO3D RTX5080 X3 OC WHITE 16GB GDDR7</t>
+          <t>ASUS PRIME RTX5070 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>68300</v>
+        <v>34900</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyNfJ9TK</t>
+          <t>https://s.shopee.co.th/AAFNq5Pxfe</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8d2yz7814ax90.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fw1olmz4kue9.webp</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4634,25 +4613,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7 (GV-N5080AERO OC-16GD)</t>
+          <t>ZOTAC RTX5070 SOLID GAMING OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>67000</v>
+        <v>32500</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6OZyIW8N</t>
+          <t>https://s.shopee.co.th/9zvxdmQb0d</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbbyjj2rglflce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fob1nq1jpl67.webp</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4662,7 +4641,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -4679,25 +4658,25 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE AORUS RTX5080 MASTER 16GB GDDR7</t>
+          <t>MSI RTX5070 SHADOW 2X OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>80900</v>
+        <v>29500</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCMjCo5g</t>
+          <t>https://s.shopee.co.th/9pcXRTRELc</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml4sii5ubnym20.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8u1tn79jysufe.webp</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4709,9 +4688,6 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L90" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4727,25 +4703,25 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5080 16GB OC GDDR7 BLACK</t>
+          <t>GALAX RTX5070 1-Click OC 12GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>85500</v>
+        <v>33000</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcZ2CAkj</t>
+          <t>https://s.shopee.co.th/9fJ7FARrgb</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq632jnzevwuf9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fuipfj90xad4.webp</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4772,25 +4748,25 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT LIGHT OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>88500</v>
+        <v>46000</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2lLBXPm</t>
+          <t>https://s.shopee.co.th/9Uzh2rSV1a</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5p939h7ybw69b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlnatrpoxouad3.webp</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4802,9 +4778,6 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L92" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4820,25 +4793,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>MSI RTX5080 VENTUS X3 OC PLUS 16GB GDDR7</t>
+          <t>GIGABYTE RTX5070 EAGLE OC ICE SFF 12GB GDDR7</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>63000</v>
+        <v>34900</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prSxeAu4p</t>
+          <t>https://s.shopee.co.th/9KgGqYT8MZ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mnkzq2y21x51b3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8frvyv07ej3f1.webp</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4865,25 +4838,25 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ASUS PRIME RTX5080 OC 16GB GDDR7</t>
+          <t>ASUS DUAL RTX5070 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>74300</v>
+        <v>35500</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVZVFLRc</t>
+          <t>https://s.shopee.co.th/6VM5TLdv72</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9pl3a6dymlq34.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mk0r90rueww2f6.webp</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4910,25 +4883,25 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G SHADOW 3X OC - 16GB GDDR7</t>
+          <t>ASUS PRIME RTX5070 OC 12GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>60500</v>
+        <v>38600</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvloEi6f</t>
+          <t>https://s.shopee.co.th/6L2fH2eYS1</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m807f87tz7xq68.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3a2dz58n4028.webp</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4938,11 +4911,8 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -4958,25 +4928,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 GAMING OC 16G - 16GB GDDR7 (GV-N5080GAMING OC-16GD)</t>
+          <t>MSI VENTUS 3X RTX5070 12GB OC GDDR7</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>63500</v>
+        <v>41000</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70ILy7E4li</t>
+          <t>https://s.shopee.co.th/6AjF4jfBn0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0o-mbbz0v0mfsdt28.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mj41n0bwbe2qfb.webp</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4986,7 +4956,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -5003,25 +4973,25 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC - 16GB GDDR7</t>
+          <t>ZOTAC RTX5070 AMP WHITE 12GB GDDR7</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>61400</v>
+        <v>35800</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmAQDRQl</t>
+          <t>https://s.shopee.co.th/60PosQfp7z</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0g-mb65w0t41ai927.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml3ci5g59l3998.webp</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5031,7 +5001,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -5048,25 +5018,25 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5080 16GB GDDR7 OC EDITION (TUF-RTX5080-O16G-GAMING)</t>
+          <t>GIGABYTE RTX5070 AORUS MASTER 12GB GDDR7</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>71700</v>
+        <v>40800</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3bNS2D2</t>
+          <t>https://s.shopee.co.th/5q6Og7gSSy</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mb7lu03gdf7ace.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m8u12jihcu0e4a.webp</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5076,7 +5046,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -5093,25 +5063,25 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+          <t>INNO3D RTX5070 TWIN X2 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>63900</v>
+        <v>37500</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTngROs5</t>
+          <t>https://s.shopee.co.th/5fmyToh5nx</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9qqhz75s2cu0e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fqk2rbkneka7.webp</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5121,11 +5091,8 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L99" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -5141,25 +5108,25 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ HYTE Y40 RTX5080 BLACK/WHITE</t>
+          <t>INNO3D RTX5070 TWIN X2 12GB GDDR7 BLACK</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>155900</v>
+        <v>32500</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1tzzQlX8</t>
+          <t>https://s.shopee.co.th/5VTYHVhj8w</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m5v66xgrzeuv7b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t4k8v92src0c.webp</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5186,25 +5153,25 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ HTYE Y60 RTX5080 OC GDDR7 BLACK</t>
+          <t>ASUS TUF RTX5070 GAMING OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>159000</v>
+        <v>38600</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKCIQ8CB</t>
+          <t>https://s.shopee.co.th/5LA85CiMTv</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m63p4ze31cil46.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3amujwk64if2.webp</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5231,25 +5198,25 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
+          <t>GIGABYTE RTX5070 WINDFORCE SFF OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>169700</v>
+        <v>35500</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
+          <t>https://s.shopee.co.th/7prT3nYqPQ</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8frlxq4oo3224.webp</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5259,11 +5226,8 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L102" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -5279,25 +5243,25 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
+          <t>MSI RTX5070 VENTUS 2X OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>301100</v>
+        <v>29500</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
+          <t>https://s.shopee.co.th/7fY2rUZTkP</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8u1lrmsiteo80.webp</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5307,7 +5271,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -5324,25 +5288,25 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>GIGABYTE RTX5070 GAMING OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>236900</v>
+        <v>36500</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaAsBag8T</t>
+          <t>https://s.shopee.co.th/7VEcfBa75O</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8fr2ccuzg5855.webp</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5352,7 +5316,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -5369,25 +5333,25 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
+          <t>MSI RTX5070 GAMING TRIO 12GB GDDR7</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>288900</v>
+        <v>43600</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LduHGca9O</t>
+          <t>https://s.shopee.co.th/7KvCSsakQN</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t79lqa4x7caf.webp</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5414,25 +5378,25 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
+          <t>คอมพิวเตอร์ประกอบ MSI SUPRIM GAMING X BLACK EDITION i7-10700 +32GB    + RTX 3070 / VENTUS RTX5070 3X</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>195500</v>
+        <v>27500</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
+          <t>https://s.shopee.co.th/7AbmGZbNlM</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7r98y-lyvt0wibg8fd67.webp</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5444,9 +5408,6 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L106" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -5462,25 +5423,25 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5070 SOLID OC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>180700</v>
+        <v>26800</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1113sedqpM</t>
+          <t>https://s.shopee.co.th/70IM4Gc16L</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mm1mzdmzk4qo34.webp</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5490,7 +5451,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>M.B Computer Store</t>
         </is>
       </c>
     </row>
@@ -5507,25 +5468,25 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5070 Twin Edge OC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>180000</v>
+        <v>25600</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
+          <t>https://s.shopee.co.th/6pyvrxceRK</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mm1mwhbo2kg438.webp</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5535,11 +5496,8 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
-        </is>
-      </c>
-      <c r="L108" t="n">
-        <v>2</v>
+          <t>M.B Computer Store</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -5555,25 +5513,25 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
+          <t>Nextcomputer CORE ULTRA 9 285K RAM 32GB I M2 1024GB I RTX5070 หรือ VGA เลือกได้</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>337700</v>
+        <v>66900</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gODU2f7VK</t>
+          <t>https://s.shopee.co.th/6ffVfedHmJ</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mki994u99atha7.webp</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5583,11 +5541,11 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>I KNOW YOU</t>
+          <t>Nextcomputer</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
@@ -5603,25 +5561,25 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>Nextcomputer Hight End I9 14900F I RAM 32G I RTX5070 I POWER 750W</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>204900</v>
+        <v>89900</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhdgLeUAN</t>
+          <t>https://s.shopee.co.th/3qLKIRo4Wm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mkic1lczkqva5e.webp</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5631,7 +5589,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>Nextcomputer</t>
         </is>
       </c>
     </row>
@@ -5648,25 +5606,25 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>Nextcomputer RTX5070 l I5 14400f l RAM 32GB I B760M DDR5</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>193900</v>
+        <v>54900</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlN5QgOBI</t>
+          <t>https://s.shopee.co.th/3g1u68ohrl</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasf-m8vbh6rczv2hde.webp</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5676,7 +5634,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>Nextcomputer</t>
         </is>
       </c>
     </row>
@@ -5693,25 +5651,25 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
+          <t>Asus TUF Gaming A16 (FA608UP-QT024W) Ryzen 7 260/16GB/512GB M.2 SSD/GeForce RTX 5070 8GB/16" WQXGA/Windows 11 Home/Jaege</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>205600</v>
+        <v>71700</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4nHjfkqL</t>
+          <t>https://s.shopee.co.th/3ViTtppLCk</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-moryg8c7hh5958.webp</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5721,7 +5679,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -5738,25 +5696,25 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
+          <t>Predator Helios Neo 16S AI PHN16S-71-95J9_Abyssal black  U9-275HX 32G 1TB RTX5070 W11 BK (Game Pass) (AI)</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>193400</v>
+        <v>84000</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18WgoherG</t>
+          <t>https://s.shopee.co.th/3LP3hWpyXj</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mgvzdc0r48p4eb.webp</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5766,7 +5724,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -5783,25 +5741,25 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
+          <t>Asus ROG Strix G16 (G614PP-TS138W) Ryzen 9 8940HX /16GB/1TB M.2 SSD/GeForce RTX 5070 8GB/16"/Windows 11 Home/Eclipse Gr</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>189900</v>
+        <v>86900</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
+          <t>https://s.shopee.co.th/3B5dVDqbsi</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mos4vczzwg0cec.webp</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5811,7 +5769,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -5828,25 +5786,25 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
+          <t>VGA การ์ดจอ PNY GeForce RTX 5080 16GB ARGB Overclocked Triple Fan DLSS 4 GDDR7</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>198500</v>
+        <v>51900</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XCe0OciG</t>
+          <t>https://s.shopee.co.th/9fJ7913vKx</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mo4863r6po1v3b.webp</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5856,8 +5814,11 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -5873,25 +5834,25 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
+          <t>GBT GF RTX 5080 GAMING OC 16G (Rev1.0)	GV-N5080GAMOC-16GD</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>189000</v>
+        <v>57600</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
+          <t>https://s.shopee.co.th/6AjEyaHFRI</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-mazph6oiow1i7d.webp</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5901,7 +5862,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Hp_by_iqink</t>
         </is>
       </c>
     </row>
@@ -5918,25 +5879,25 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
+          <t>ZOTAC GAMING GEFORCE RTX5080 SOLID CORE OC 16GB 256BIT GDDR7(P288-1N765-300Z8)</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>192900</v>
+        <v>56000</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
+          <t>https://s.shopee.co.th/60PomHHsmH</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8a9twwj7iemf8.webp</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5946,8 +5907,11 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="118">
@@ -5963,25 +5927,25 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
+          <t>ASUS PRIME GEFORCE RTX5080 OC 16G GDDR7 (90YV0LX0-M0NA00)</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>187900</v>
+        <v>63000</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
+          <t>https://s.shopee.co.th/6VM5NCFylO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m846xz01ff8u95.webp</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5991,8 +5955,11 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="119">
@@ -6008,25 +5975,25 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>198500</v>
+        <v>52900</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
+          <t>https://s.shopee.co.th/6L2fAtGc6N</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmv7butau96u14.webp</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6036,11 +6003,8 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L119" t="n">
-        <v>3</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -6056,25 +6020,25 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G GAMING TRIO OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>195500</v>
+        <v>62600</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
+          <t>https://s.shopee.co.th/5VTYBMJmnE</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-moy490f3fuofce.webp</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6084,7 +6048,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -6101,25 +6065,25 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7 +  PSU ASUS 1200W ROG THOR 1200P3 80+PLATINUM MIKU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>459500</v>
+        <v>111000</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40efSASQkA</t>
+          <t>https://s.shopee.co.th/5LA7z3KQ8D</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mmjrx4g2i8zn0b.webp</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6129,7 +6093,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>D.P COMPUTER Hi End</t>
         </is>
       </c>
     </row>
@@ -6146,25 +6110,25 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>186900</v>
+        <v>89900</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
+          <t>https://s.shopee.co.th/5q6OZyIW7K</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mpkfshwxt3ij71.webp</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6174,7 +6138,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>D.P COMPUTER Hi End</t>
         </is>
       </c>
     </row>
@@ -6191,25 +6155,25 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5080 SOLID CORE OC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>186900</v>
+        <v>52200</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
+          <t>https://s.shopee.co.th/5fmyNfJ9SJ</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mm1mtsp7op3402.webp</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6219,7 +6183,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>M.B Computer Store</t>
         </is>
       </c>
     </row>
@@ -6236,25 +6200,25 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 X3 OC - 16GB GDDR7 - A0182764</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185500</v>
+        <v>56500</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLFFrT45B</t>
+          <t>https://s.shopee.co.th/7VEcZ2CAjg</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpukkz1kncp821.webp</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6264,7 +6228,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6281,25 +6245,25 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL FROSTBITE OC - 16GB GDDR7 - A0182767</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>269500</v>
+        <v>71700</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOyewUy66</t>
+          <t>https://s.shopee.co.th/7KvCMjCo4f</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mpukedl8v8ch88.webp</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6309,7 +6273,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6326,25 +6290,25 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 WINDFORCE OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>195000</v>
+        <v>52900</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
+          <t>https://s.shopee.co.th/7prSxeAu3m</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkd8n452amth61.webp</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6354,8 +6318,11 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="127">
@@ -6371,25 +6338,25 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
+          <t>VGA การ์ดจอ ZOTAC GAMING GeForce RTX 5080 GAMING SOLID CORE OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>195500</v>
+        <v>52400</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8GKWEm4</t>
+          <t>https://s.shopee.co.th/7fY2lLBXOl</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mki0hzdcdlvk9a.webp</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6399,8 +6366,11 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="128">
@@ -6416,25 +6386,25 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 (PRIME-RTX5080-16G)</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>179900</v>
+        <v>67600</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
+          <t>https://s.shopee.co.th/6pyvloEi5c</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4j8l8twxuce.webp</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6444,7 +6414,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -6461,25 +6431,25 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185500</v>
+        <v>55900</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+          <t>https://s.shopee.co.th/6ffVZVFLQb</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mmv7325j5mgxbb.webp</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6489,7 +6459,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -6506,25 +6476,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>198500</v>
+        <v>113000</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSi41Ws75</t>
+          <t>https://s.shopee.co.th/7AbmAQDRPi</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mjxxy5kvxjied7.webp</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6551,25 +6521,25 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>192900</v>
+        <v>71900</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXxouETJ2</t>
+          <t>https://s.shopee.co.th/70ILy7E4kh</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mjjcxbr8kqo03d.webp</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6596,25 +6566,25 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC - 16GB GDDR7 (N50803-16D7X-17603930)</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>188500</v>
+        <v>59000</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prO1DDpy5</t>
+          <t>https://s.shopee.co.th/3ViTngROr2</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbdla2gs3l9wca.webp</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6624,8 +6594,11 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -6641,25 +6614,25 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
+          <t>MSI VGA GEFORCE RTX 5080 SHADOW 3X OC - 16GB GDDR7 - A0167047</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>215000</v>
+        <v>58000</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
+          <t>https://s.shopee.co.th/3LP3bNS2C1</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rask-m9r5cxk7f42o1c.webp</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6669,7 +6642,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6686,25 +6659,25 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 XTREME WATERFORCE - 16GB GDDR7 (REV. 1.0) - A0166365</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228800</v>
+        <v>74200</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
+          <t>https://s.shopee.co.th/3qLKCIQ8B8</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-mai21hqfq6icd6.webp</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6714,7 +6687,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6731,25 +6704,25 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 AORUS MASTER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>209000</v>
+        <v>60700</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70IH1gH0ey</t>
+          <t>https://s.shopee.co.th/3g1tzzQlW7</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mky5qpeaknwi66.webp</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6759,14 +6732,14 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>shoppingpc dotnet</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6776,25 +6749,25 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
+          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>22700</v>
+        <v>9000</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
+          <t>https://s.shopee.co.th/2qSn0STwCy</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6804,17 +6777,17 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>mcwinner</t>
+          <t>EZGGTECH</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6824,25 +6797,25 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>26500</v>
+        <v>67900</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9IIXOei9</t>
+          <t>https://s.shopee.co.th/2g9Mo9UZXx</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4xoa7sr9r50.webp</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6852,17 +6825,14 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>6</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6872,25 +6842,25 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC WHITE - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>10500</v>
+        <v>55900</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+          <t>https://s.shopee.co.th/3B5dP4SfX4</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mqbi0037km4r5f.webp</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6900,17 +6870,14 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>382</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6920,25 +6887,25 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>GALAX RTX5080 HOF GAMING BLACK EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>33000</v>
+        <v>87000</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+          <t>https://s.shopee.co.th/30mDClTIs3</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mi2smox3b8qo49.webp</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6948,17 +6915,14 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>6</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6968,25 +6932,25 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>29900</v>
+        <v>69500</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+          <t>https://s.shopee.co.th/4qDrO8MK9Q</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9pqc1bk39ipd8.webp</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6996,17 +6960,14 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>atSine Tech</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>2</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7016,25 +6977,25 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G VENTUS 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>24200</v>
+        <v>64100</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
+          <t>https://s.shopee.co.th/4fuRBpMxUP</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmjx8u2c385h1b.webp</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7044,58 +7005,4540 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>4</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 AERO OC - 16GB GDDR7 (REV. 1.0) - A0166362</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>66200</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AqhmkL3TW</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m9r5fxjheinlbf.webp</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 AORUS MASTER - 16GB GDDR7 (REV. 1.0) - A0166364</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>70500</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50XHaRLgoV</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e59iq7j2a769.webp</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 WHITE OC EDITION</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>79900</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AyAauOrVM</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlljzbvrqccib8.webp</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>(มีโค้ดลด2000฿) RTX 5060 5060Ti 5060 ti 2060Super 3060 3060Ti 3070 3070Ti 4060 4060Ti 4070 4070Ti 4080 4090 5080 5090</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40ekObPUqL</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>EZGGTECH</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>21400</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vb0zWNapS</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>3CCamera.th</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Intel Core Ultra 9 285K + RTX 5080 | DDR5 64GB 6400MHz / SSD 2TB | โทนขาว / ชุดแต่ง Lian Li</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>155700</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LHanDOEAR</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfkgr2oabvux4c.webp</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5080 AORUS XTREME WATERFORECE 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>89500</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/qhicmbYGm</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prhvzpau3yd2.webp</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7 WHITE</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>66900</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gOIQTcBbl</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9pqq1xfnr3i22.webp</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>75300</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BKZ1OaHas</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mmwzh1437egx8f.webp</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>MSI VGA GEFORCE RTX 5080 VENTUS 3X OC - 16GB GDDR7 - A0167046</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>60500</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1118p5auvr</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasf-m9r4yrpdj75afe.webp</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 GAMING OC - 16GB GDDR7 (REV. 1.0) - A0166361</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>65500</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/BS1pYe5ci</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9e55v65yvbda7.webp</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 ICHILL X3 V2 - 16GB GDDR7 C50803-16D7X-176069R</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>64900</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/18bdFeixh</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-modebjzln30gb5.webp</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | RAM 64GB 6400MHz / SSD 2TB | โทนขาว / HYTE Y70 Touch</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>145900</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W4sEAcowo</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq8r6vopg3rg36.webp</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ROG Zephyrus G18 G815LW-S9112W Asus U9-275HX32 G 1TB RTX5080 W11 3YOSS</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>125000</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LlS1rdSHn</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-me5o4gxp31mrb5.webp</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>NOTEBOOK  CORP</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>130900</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BD6DEWTZA</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq90ma8arc3x60.webp</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>MSI RTX5080 SHADOW 3X OC 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>67800</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20tg0vX6u9</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9prwjnh3cy749.webp</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5080 WINFOREC OC SFF 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>68500</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VpwbqVCtG</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prnu5bv9wxb3.webp</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 MASTER 16G - 16GB GDDR7 (GV-N5080AORUS M-16GD)</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>67900</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LWWPXVqEF</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbbxwlx4z7uc43.webp</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>GALAX VGA GEFORCE RTX 5080 HOF GAMING BLACK - 16GB GDDR7 - A0172861</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>68400</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VxPQ0Z0v6</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-824je-me9vcwg1o3cw45.webp</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO OC - 16GB GDDR7 - A0180200</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>55500</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LdzDhZeG5</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-82609-mmd4ly6nd341a5.webp</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 XTREME WATERFORCE 16G - 16GB GDDR7 (GV-N5080AORUSX W-16GD)</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>73800</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qaFocXkFC</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mbbxc0wleh6p7b.webp</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 16GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>130900</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gGpcJYNaB</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mq8stcq5cx6of7.webp</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>MSI STEALTH A16 AI PLUS Ryzen AI 9 HX 370/RTX 5080 RAM64/2TB - ID26060441</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>113400</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fQZxB7jNY</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpuc7ehxc9ho8a.webp</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>10X Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Original 380W 20V 19A อะแดปเตอร์ชาร์จสําหรับ ASUS ROG Strix scar 16 2025 G635LW RTX5080 ADP-380AB B</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pk09U762b</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824jc-mep4jcmcgnphd5.webp</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>junyue999.th</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5080 AORUS MASTER ICE 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>82500</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/903QLn6She</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-map4vxrow1ao8a.webp</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>INNO3D RTX5080 X3 OC 16GB BLACK GDDR7</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>66900</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AMqY65pMh</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8d39ntj3z7289.webp</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC WHITE - 16GB GDDR7 (N50803-16D7X-17605211)</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>59000</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/80At9xAGjU</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbdmsesr8qk199.webp</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL X3 V2 OC - 16GB GDDR7 - A0182766</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>61800</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8AUJMG9dOX</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mpujxufur8y4aa.webp</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7 - A0166369</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>55500</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8KnjYZ903a</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0k-mc7mmx5y9omf72.webp</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>78500</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V79ks8Mid</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-me6x1j4ufmyqba.webp</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 WINDFORCE OC - 16GB GDDR7 (REV. 1.0) - A0166360</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>60300</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zvxXd2efw</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7ras8-m9r4yq4hudlb71.webp</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7 WHITE</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>69200</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAFNjw21Kz</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9pqwzx9tkvi06.webp</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>GIGABYTE GAMING RTX5080 16 GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>75900</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AKYnwF1O02</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5zvhd595sc69a.webp</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 WINDFORCE OC SFF 16G - 16GB GDDR7 (GV-N5080WF3OC-16GD)</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>58800</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AUsE8Y0kf5</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbc1uyc222bab6.webp</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] MSI GAMING TRIO RTX5080 16 GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>72900</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KgGkP5C1s</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m5qng58cco0t25.webp</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>RTX5080/16GB GALAX 1-CLICK (OC/D7) - A0166352</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>59600</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uzgwi4Ygv</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m81gt7mb1w4u18.webp</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 HOF GAMING BLACK EDITION - 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>70600</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fJ7913vLy</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdpq3ctyx2ta3e.webp</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5080 OC WHITE 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>89500</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pcXLK3I11</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-misduj582yo30b.webp</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ZOTAC RTX5080 SOLID GAMING OC 16GB GDDR7 WHITE</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>64900</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60PomHHsnI</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-mapdn0hs6q9gfb.webp</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>GALAX RTX5080 HOF GAMING 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>87000</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AjEyaHFSL</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mi2scd35wirsed.webp</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>GIGABYTE AERO RTX5080 16GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>78500</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6L2fAtGc7O</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mki1wyjsh14yd6.webp</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ZOTAC GAMING RTX5080 SOLID CORE OC 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VM5NCFymR</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mloguv0dy97323.webp</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5080 SOLID CORE OC - 16GB GDDR7 (ZT-B50800J2-10P)</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>59000</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5LA7z3KQ9E</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbvy43nc50gsdd.webp</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ASUS TUF RTX5080 GAMING OC 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>81000</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VTYBMJmoH</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m9pk6xb8lmjk47.webp</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>INNO3D RTX5080 X3 OC WHITE 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>68300</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5fmyNfJ9TK</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8d2yz7814ax90.webp</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7 (GV-N5080AERO OC-16GD)</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>67000</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q6OZyIW8N</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbbyjj2rglflce.webp</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE AORUS RTX5080 MASTER 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>80900</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KvCMjCo5g</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml4sii5ubnym20.webp</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ROG ASTRAL RTX5080 16GB OC GDDR7 BLACK</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>85500</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VEcZ2CAkj</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq632jnzevwuf9.webp</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ROG ASTRAL RTX5080 16 GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>88500</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fY2lLBXPm</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5p939h7ybw69b.webp</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>MSI RTX5080 VENTUS X3 OC PLUS 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>63000</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7prSxeAu4p</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mnkzq2y21x51b3.webp</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ASUS PRIME RTX5080 OC 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>74300</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6ffVZVFLRc</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9pl3a6dymlq34.webp</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G SHADOW 3X OC - 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>60500</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6pyvloEi6f</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m807f87tz7xq68.webp</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 GAMING OC 16G - 16GB GDDR7 (GV-N5080GAMING OC-16GD)</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>63500</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70ILy7E4li</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0o-mbbz0v0mfsdt28.webp</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC - 16GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>61400</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7AbmAQDRQl</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0g-mb65w0t41ai927.webp</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5080 16GB GDDR7 OC EDITION (TUF-RTX5080-O16G-GAMING)</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>71700</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LP3bNS2D2</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mb7lu03gdf7ace.webp</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>63900</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViTngROs5</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9qqhz75s2cu0e.webp</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์ประกอบ HYTE Y40 RTX5080 BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>155900</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g1tzzQlX8</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m5v66xgrzeuv7b.webp</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์ประกอบ HTYE Y60 RTX5080 OC GDDR7 BLACK</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>159000</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qLKCIQ8CB</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m63p4ze31cil46.webp</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>169700</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>301100</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>236900</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qaAsBag8T</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>288900</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LduHGca9O</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>195500</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>180700</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1113sedqpM</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>337700</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gODU2f7VK</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>I KNOW YOU</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>204900</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/qhdgLeUAN</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>193900</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LlN5QgOBI</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>205600</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W4nHjfkqL</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>193400</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/18WgoherG</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>189900</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>198500</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50XCe0OciG</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>189000</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>192900</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>187900</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>198500</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>195500</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>459500</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40efSASQkA</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>186900</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>186900</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>185500</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qLFFrT45B</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>269500</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOyewUy66</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>195000</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>195500</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30m8GKWEm4</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>179900</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>185500</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>198500</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qSi41Ws75</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>192900</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXxouETJ2</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>188500</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7prO1DDpy5</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>215000</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>228800</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>209000</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70IH1gH0ey</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>shoppingpc dotnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
           <t>ai_calculator_cpu</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>r9_7950x</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>22700</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>mcwinner</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>26500</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g9IIXOei9</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>33000</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>29900</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>atSine Tech</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>24200</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
         <is>
           <t>CPU AMD AM5 RYZEN 9 9950X3D (NEXT) - A0168684</t>
         </is>
       </c>
-      <c r="E142" t="n">
+      <c r="E240" t="n">
         <v>32200</v>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G240" t="inlineStr">
         <is>
           <t>https://s.shopee.co.th/3qLFggKDLS</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H240" t="inlineStr">
         <is>
           <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
         <is>
           <t>Advice Official Shop</t>
         </is>
       </c>
-      <c r="L142" t="n">
+      <c r="L240" t="n">
         <v>11</v>
       </c>
     </row>

--- a/data/affiliate/picks.xlsx
+++ b/data/affiliate/picks.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N240"/>
+  <dimension ref="A1:N238"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3988,20 +3988,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
+          <t>VGA ZOTAC GEFORCE RTX 5070 GAMING TWIN EDGE OC - 12GB GDDR7 มือสอง</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>21400</v>
+        <v>24600</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaFulvgZp</t>
+          <t>https://s.shopee.co.th/1VxPW9wxFn</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mq00fruhkkxs6b.webp</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>3CCamera.th</t>
+          <t>M&amp;N Computer</t>
         </is>
       </c>
     </row>
@@ -4033,20 +4033,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Alphacool Water Block เข้ากันได้กับ RTX 5080 / 5070 Ti INNO3D และ MSI ASIC</t>
+          <t>Geforce RTX 5070 OC 12GB GDDR7 Snow Fox DLSS 4 Esports Design Live AI กราฟิกการ์ดสําหรับเล่นเกมอิสระ</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>14900</v>
+        <v>90500</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LdzJqxaak</t>
+          <t>https://s.shopee.co.th/9AMqeFTlhI</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/cn-11134207-820l4-mm01f4p4ojd49c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7renx-m8d3bdfuxnswe8.webp</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>133lnxgoshop.th</t>
+          <t>PC Accessories Shop</t>
         </is>
       </c>
     </row>
@@ -4078,20 +4078,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VGA ZOTAC GEFORCE RTX 5070 GAMING TWIN EDGE OC - 12GB GDDR7 มือสอง</t>
+          <t>คอมประกอบครบชุด SPCOMZING RYZEN5 5600 / M.2 500GB / RTX 5070 12GB / B550M / 32GB DDR4 / จอ 24นิ้ว</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>24600</v>
+        <v>26700</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxPW9wxFn</t>
+          <t>https://s.shopee.co.th/903QRwUP2H</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mq00fruhkkxs6b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mp20d8fdwykh66.webp</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>M&amp;N Computer</t>
+          <t>SPCOMZING</t>
         </is>
       </c>
     </row>
@@ -4123,20 +4123,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Geforce RTX 5070 OC 12GB GDDR7 Snow Fox DLSS 4 Esports Design Live AI กราฟิกการ์ดสําหรับเล่นเกมอิสระ</t>
+          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT VOID OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>90500</v>
+        <v>46000</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AMqeFTlhI</t>
+          <t>https://s.shopee.co.th/8pk0FdV2NG</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7renx-m8d3bdfuxnswe8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mln8wxv1kao1df.webp</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>PC Accessories Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -4168,20 +4168,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>คอมประกอบครบชุด SPCOMZING RYZEN5 5600 / M.2 500GB / RTX 5070 12GB / B550M / 32GB DDR4 / จอ 24นิ้ว</t>
+          <t>GALAX RTX5070 EX GAMER 12GB GDDR7</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>26700</v>
+        <v>35000</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/903QRwUP2H</t>
+          <t>https://s.shopee.co.th/8fQa3KVfiF</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mp20d8fdwykh66.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-ml3do6g159fm84.webp</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>SPCOMZING</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -4213,20 +4213,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT VOID OC 12GB GDDR7</t>
+          <t>GIGABYTE RTX5070 AERO OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>46000</v>
+        <v>37900</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pk0FdV2NG</t>
+          <t>https://s.shopee.co.th/8V79r1WJ3E</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mln8wxv1kao1df.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-ml3b0ujyyigw9f.webp</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4258,20 +4258,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>GALAX RTX5070 EX GAMER 12GB GDDR7</t>
+          <t>ZOTAC GAMING RTX5070 TWIN EDGE 12GB GDDR7</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>35000</v>
+        <v>31000</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fQa3KVfiF</t>
+          <t>https://s.shopee.co.th/8KnjeiWwOD</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-ml3do6g159fm84.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-ma9clcgr2jrn46.webp</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4303,20 +4303,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 AERO OC 12GB GDDR7</t>
+          <t>INNO3D RTX5070 TWIN X2 OC 12GB WHITE GDDR7</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>37900</v>
+        <v>33600</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8V79r1WJ3E</t>
+          <t>https://s.shopee.co.th/8AUJSPXZjC</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-ml3b0ujyyigw9f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8fpz7z7z3m167.webp</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4348,20 +4348,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5070 TWIN EDGE 12GB GDDR7</t>
+          <t>MSI RTX5070 GAMING TRIO OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>31000</v>
+        <v>36300</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8KnjeiWwOD</t>
+          <t>https://s.shopee.co.th/80AtG6YD4B</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-ma9clcgr2jrn46.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8fplkpwu26459.webp</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4393,20 +4393,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>INNO3D RTX5070 TWIN X2 OC 12GB WHITE GDDR7</t>
+          <t>GALAX RTX5070 1-CLICK 12GB OC GDDR7</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>33600</v>
+        <v>32800</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8AUJSPXZjC</t>
+          <t>https://s.shopee.co.th/AUsEEhOgzg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8fpz7z7z3m167.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m7t43sao8g0oc9.webp</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4438,20 +4438,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MSI RTX5070 GAMING TRIO OC 12GB GDDR7</t>
+          <t>MSI RTX5070 VANGUARD SOC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>36300</v>
+        <v>42900</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/80AtG6YD4B</t>
+          <t>https://s.shopee.co.th/AKYo2OPKKf</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8fplkpwu26459.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m7t7pn5x4rli2a.webp</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4483,20 +4483,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>GALAX RTX5070 1-CLICK 12GB OC GDDR7</t>
+          <t>ASUS PRIME RTX5070 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>32800</v>
+        <v>34900</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AUsEEhOgzg</t>
+          <t>https://s.shopee.co.th/AAFNq5Pxfe</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m7t43sao8g0oc9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fw1olmz4kue9.webp</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4528,20 +4528,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MSI RTX5070 VANGUARD SOC 12GB GDDR7</t>
+          <t>ZOTAC RTX5070 SOLID GAMING OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>42900</v>
+        <v>32500</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKYo2OPKKf</t>
+          <t>https://s.shopee.co.th/9zvxdmQb0d</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m7t7pn5x4rli2a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fob1nq1jpl67.webp</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4573,20 +4573,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ASUS PRIME RTX5070 OC 12GB GDDR7</t>
+          <t>MSI RTX5070 SHADOW 2X OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>34900</v>
+        <v>29500</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAFNq5Pxfe</t>
+          <t>https://s.shopee.co.th/9pcXRTRELc</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fw1olmz4kue9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8u1tn79jysufe.webp</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4618,20 +4618,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5070 SOLID GAMING OC 12GB GDDR7</t>
+          <t>GALAX RTX5070 1-Click OC 12GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>32500</v>
+        <v>33000</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9zvxdmQb0d</t>
+          <t>https://s.shopee.co.th/9fJ7FARrgb</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fob1nq1jpl67.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fuipfj90xad4.webp</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4663,20 +4663,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MSI RTX5070 SHADOW 2X OC 12GB GDDR7</t>
+          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT LIGHT OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>29500</v>
+        <v>46000</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9pcXRTRELc</t>
+          <t>https://s.shopee.co.th/9Uzh2rSV1a</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8u1tn79jysufe.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlnatrpoxouad3.webp</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4708,20 +4708,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GALAX RTX5070 1-Click OC 12GB GDDR7 WHITE</t>
+          <t>GIGABYTE RTX5070 EAGLE OC ICE SFF 12GB GDDR7</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>33000</v>
+        <v>34900</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7FARrgb</t>
+          <t>https://s.shopee.co.th/9KgGqYT8MZ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fuipfj90xad4.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8frvyv07ej3f1.webp</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4753,20 +4753,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT LIGHT OC 12GB GDDR7</t>
+          <t>ASUS DUAL RTX5070 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>46000</v>
+        <v>35500</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9Uzh2rSV1a</t>
+          <t>https://s.shopee.co.th/6VM5TLdv72</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlnatrpoxouad3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mk0r90rueww2f6.webp</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4798,20 +4798,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 EAGLE OC ICE SFF 12GB GDDR7</t>
+          <t>ASUS PRIME RTX5070 OC 12GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>34900</v>
+        <v>38600</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9KgGqYT8MZ</t>
+          <t>https://s.shopee.co.th/6L2fH2eYS1</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8frvyv07ej3f1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3a2dz58n4028.webp</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4843,20 +4843,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ASUS DUAL RTX5070 OC 12GB GDDR7</t>
+          <t>MSI VENTUS 3X RTX5070 12GB OC GDDR7</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>35500</v>
+        <v>41000</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5TLdv72</t>
+          <t>https://s.shopee.co.th/6AjF4jfBn0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mk0r90rueww2f6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mj41n0bwbe2qfb.webp</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4888,20 +4888,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ASUS PRIME RTX5070 OC 12GB GDDR7 WHITE</t>
+          <t>ZOTAC RTX5070 AMP WHITE 12GB GDDR7</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>38600</v>
+        <v>35800</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fH2eYS1</t>
+          <t>https://s.shopee.co.th/60PosQfp7z</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3a2dz58n4028.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml3ci5g59l3998.webp</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4933,20 +4933,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MSI VENTUS 3X RTX5070 12GB OC GDDR7</t>
+          <t>GIGABYTE RTX5070 AORUS MASTER 12GB GDDR7</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>41000</v>
+        <v>40800</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjF4jfBn0</t>
+          <t>https://s.shopee.co.th/5q6Og7gSSy</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mj41n0bwbe2qfb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m8u12jihcu0e4a.webp</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4978,20 +4978,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5070 AMP WHITE 12GB GDDR7</t>
+          <t>INNO3D RTX5070 TWIN X2 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>35800</v>
+        <v>37500</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PosQfp7z</t>
+          <t>https://s.shopee.co.th/5fmyToh5nx</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml3ci5g59l3998.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fqk2rbkneka7.webp</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5023,20 +5023,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 AORUS MASTER 12GB GDDR7</t>
+          <t>INNO3D RTX5070 TWIN X2 12GB GDDR7 BLACK</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>40800</v>
+        <v>32500</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6Og7gSSy</t>
+          <t>https://s.shopee.co.th/5VTYHVhj8w</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m8u12jihcu0e4a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t4k8v92src0c.webp</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5068,20 +5068,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>INNO3D RTX5070 TWIN X2 OC 12GB GDDR7</t>
+          <t>ASUS TUF RTX5070 GAMING OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>37500</v>
+        <v>38600</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyToh5nx</t>
+          <t>https://s.shopee.co.th/5LA85CiMTv</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fqk2rbkneka7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3amujwk64if2.webp</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5113,20 +5113,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>INNO3D RTX5070 TWIN X2 12GB GDDR7 BLACK</t>
+          <t>GIGABYTE RTX5070 WINDFORCE SFF OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>32500</v>
+        <v>35500</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYHVhj8w</t>
+          <t>https://s.shopee.co.th/7prT3nYqPQ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t4k8v92src0c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8frlxq4oo3224.webp</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5158,20 +5158,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ASUS TUF RTX5070 GAMING OC 12GB GDDR7</t>
+          <t>MSI RTX5070 VENTUS 2X OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>38600</v>
+        <v>29500</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA85CiMTv</t>
+          <t>https://s.shopee.co.th/7fY2rUZTkP</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3amujwk64if2.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8u1lrmsiteo80.webp</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5203,20 +5203,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 WINDFORCE SFF OC 12GB GDDR7</t>
+          <t>GIGABYTE RTX5070 GAMING OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>35500</v>
+        <v>36500</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prT3nYqPQ</t>
+          <t>https://s.shopee.co.th/7VEcfBa75O</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8frlxq4oo3224.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8fr2ccuzg5855.webp</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5248,20 +5248,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MSI RTX5070 VENTUS 2X OC 12GB GDDR7</t>
+          <t>MSI RTX5070 GAMING TRIO 12GB GDDR7</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>29500</v>
+        <v>43600</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2rUZTkP</t>
+          <t>https://s.shopee.co.th/7KvCSsakQN</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8u1lrmsiteo80.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t79lqa4x7caf.webp</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5293,20 +5293,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 GAMING OC 12GB GDDR7</t>
+          <t>คอมพิวเตอร์ประกอบ MSI SUPRIM GAMING X BLACK EDITION i7-10700 +32GB    + RTX 3070 / VENTUS RTX5070 3X</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>36500</v>
+        <v>27500</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcfBa75O</t>
+          <t>https://s.shopee.co.th/7AbmGZbNlM</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8fr2ccuzg5855.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7r98y-lyvt0wibg8fd67.webp</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>MSI RTX5070 GAMING TRIO 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5070 SOLID OC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>43600</v>
+        <v>26800</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCSsakQN</t>
+          <t>https://s.shopee.co.th/70IM4Gc16L</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t79lqa4x7caf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mm1mzdmzk4qo34.webp</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>M.B Computer Store</t>
         </is>
       </c>
     </row>
@@ -5383,20 +5383,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ MSI SUPRIM GAMING X BLACK EDITION i7-10700 +32GB    + RTX 3070 / VENTUS RTX5070 3X</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5070 Twin Edge OC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>27500</v>
+        <v>25600</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmGZbNlM</t>
+          <t>https://s.shopee.co.th/6pyvrxceRK</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7r98y-lyvt0wibg8fd67.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mm1mwhbo2kg438.webp</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>M.B Computer Store</t>
         </is>
       </c>
     </row>
@@ -5428,20 +5428,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5070 SOLID OC</t>
+          <t>Nextcomputer CORE ULTRA 9 285K RAM 32GB I M2 1024GB I RTX5070 หรือ VGA เลือกได้</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>26800</v>
+        <v>66900</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70IM4Gc16L</t>
+          <t>https://s.shopee.co.th/6ffVfedHmJ</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mm1mzdmzk4qo34.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mki994u99atha7.webp</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5451,8 +5451,11 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>M.B Computer Store</t>
-        </is>
+          <t>Nextcomputer</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="108">
@@ -5473,20 +5476,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5070 Twin Edge OC</t>
+          <t>Nextcomputer Hight End I9 14900F I RAM 32G I RTX5070 I POWER 750W</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>25600</v>
+        <v>89900</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvrxceRK</t>
+          <t>https://s.shopee.co.th/3qLKIRo4Wm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mm1mwhbo2kg438.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mkic1lczkqva5e.webp</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5496,7 +5499,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>M.B Computer Store</t>
+          <t>Nextcomputer</t>
         </is>
       </c>
     </row>
@@ -5518,20 +5521,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Nextcomputer CORE ULTRA 9 285K RAM 32GB I M2 1024GB I RTX5070 หรือ VGA เลือกได้</t>
+          <t>Nextcomputer RTX5070 l I5 14400f l RAM 32GB I B760M DDR5</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>66900</v>
+        <v>54900</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVfedHmJ</t>
+          <t>https://s.shopee.co.th/3g1u68ohrl</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mki994u99atha7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasf-m8vbh6rczv2hde.webp</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5543,9 +5546,6 @@
         <is>
           <t>Nextcomputer</t>
         </is>
-      </c>
-      <c r="L109" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="110">
@@ -5566,20 +5566,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Nextcomputer Hight End I9 14900F I RAM 32G I RTX5070 I POWER 750W</t>
+          <t>Asus TUF Gaming A16 (FA608UP-QT024W) Ryzen 7 260/16GB/512GB M.2 SSD/GeForce RTX 5070 8GB/16" WQXGA/Windows 11 Home/Jaege</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>89900</v>
+        <v>71700</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKIRo4Wm</t>
+          <t>https://s.shopee.co.th/3ViTtppLCk</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mkic1lczkqva5e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-moryg8c7hh5958.webp</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Nextcomputer</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -5611,20 +5611,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Nextcomputer RTX5070 l I5 14400f l RAM 32GB I B760M DDR5</t>
+          <t>Predator Helios Neo 16S AI PHN16S-71-95J9_Abyssal black  U9-275HX 32G 1TB RTX5070 W11 BK (Game Pass) (AI)</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>54900</v>
+        <v>84000</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1u68ohrl</t>
+          <t>https://s.shopee.co.th/3LP3hWpyXj</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasf-m8vbh6rczv2hde.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mgvzdc0r48p4eb.webp</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Nextcomputer</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -5656,20 +5656,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Asus TUF Gaming A16 (FA608UP-QT024W) Ryzen 7 260/16GB/512GB M.2 SSD/GeForce RTX 5070 8GB/16" WQXGA/Windows 11 Home/Jaege</t>
+          <t>Asus ROG Strix G16 (G614PP-TS138W) Ryzen 9 8940HX /16GB/1TB M.2 SSD/GeForce RTX 5070 8GB/16"/Windows 11 Home/Eclipse Gr</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>71700</v>
+        <v>86900</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTtppLCk</t>
+          <t>https://s.shopee.co.th/3B5dVDqbsi</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-moryg8c7hh5958.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mos4vczzwg0cec.webp</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5696,25 +5696,25 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Predator Helios Neo 16S AI PHN16S-71-95J9_Abyssal black  U9-275HX 32G 1TB RTX5070 W11 BK (Game Pass) (AI)</t>
+          <t>VGA การ์ดจอ PNY GeForce RTX 5080 16GB ARGB Overclocked Triple Fan DLSS 4 GDDR7</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>84000</v>
+        <v>51900</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3hWpyXj</t>
+          <t>https://s.shopee.co.th/9fJ7913vKx</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mgvzdc0r48p4eb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mo4863r6po1v3b.webp</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5724,8 +5724,11 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>NOTEBOOK  CORP</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -5741,25 +5744,25 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Asus ROG Strix G16 (G614PP-TS138W) Ryzen 9 8940HX /16GB/1TB M.2 SSD/GeForce RTX 5070 8GB/16"/Windows 11 Home/Eclipse Gr</t>
+          <t>GBT GF RTX 5080 GAMING OC 16G (Rev1.0)	GV-N5080GAMOC-16GD</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>86900</v>
+        <v>57600</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5dVDqbsi</t>
+          <t>https://s.shopee.co.th/6AjEyaHFRI</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mos4vczzwg0cec.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-mazph6oiow1i7d.webp</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5769,7 +5772,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>NOTEBOOK  CORP</t>
+          <t>Hp_by_iqink</t>
         </is>
       </c>
     </row>
@@ -5791,20 +5794,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ PNY GeForce RTX 5080 16GB ARGB Overclocked Triple Fan DLSS 4 GDDR7</t>
+          <t>ZOTAC GAMING GEFORCE RTX5080 SOLID CORE OC 16GB 256BIT GDDR7(P288-1N765-300Z8)</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>51900</v>
+        <v>56000</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7913vKx</t>
+          <t>https://s.shopee.co.th/60PomHHsmH</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mo4863r6po1v3b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8a9twwj7iemf8.webp</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5814,11 +5817,11 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>TECHNOCOM.OFFICIAL</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
@@ -5839,20 +5842,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>GBT GF RTX 5080 GAMING OC 16G (Rev1.0)	GV-N5080GAMOC-16GD</t>
+          <t>ASUS PRIME GEFORCE RTX5080 OC 16G GDDR7 (90YV0LX0-M0NA00)</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>57600</v>
+        <v>63000</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjEyaHFRI</t>
+          <t>https://s.shopee.co.th/6VM5NCFylO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-mazph6oiow1i7d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m846xz01ff8u95.webp</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5862,8 +5865,11 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Hp_by_iqink</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="117">
@@ -5884,20 +5890,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING GEFORCE RTX5080 SOLID CORE OC 16GB 256BIT GDDR7(P288-1N765-300Z8)</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>56000</v>
+        <v>52900</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PomHHsmH</t>
+          <t>https://s.shopee.co.th/6L2fAtGc6N</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8a9twwj7iemf8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmv7butau96u14.webp</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5907,11 +5913,8 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
-        </is>
-      </c>
-      <c r="L117" t="n">
-        <v>4</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -5932,20 +5935,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ASUS PRIME GEFORCE RTX5080 OC 16G GDDR7 (90YV0LX0-M0NA00)</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G GAMING TRIO OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>63000</v>
+        <v>62600</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5NCFylO</t>
+          <t>https://s.shopee.co.th/5VTYBMJmnE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m846xz01ff8u95.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-moy490f3fuofce.webp</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5955,11 +5958,8 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
-        </is>
-      </c>
-      <c r="L118" t="n">
-        <v>9</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -5980,20 +5980,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7 +  PSU ASUS 1200W ROG THOR 1200P3 80+PLATINUM MIKU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>52900</v>
+        <v>111000</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fAtGc6N</t>
+          <t>https://s.shopee.co.th/5LA7z3KQ8D</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmv7butau96u14.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mmjrx4g2i8zn0b.webp</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>D.P COMPUTER Hi End</t>
         </is>
       </c>
     </row>
@@ -6025,20 +6025,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G GAMING TRIO OC - 16GB GDDR7</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>62600</v>
+        <v>89900</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYBMJmnE</t>
+          <t>https://s.shopee.co.th/5q6OZyIW7K</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-moy490f3fuofce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mpkfshwxt3ij71.webp</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>D.P COMPUTER Hi End</t>
         </is>
       </c>
     </row>
@@ -6070,20 +6070,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7 +  PSU ASUS 1200W ROG THOR 1200P3 80+PLATINUM MIKU</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5080 SOLID CORE OC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>111000</v>
+        <v>52200</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA7z3KQ8D</t>
+          <t>https://s.shopee.co.th/5fmyNfJ9SJ</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mmjrx4g2i8zn0b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mm1mtsp7op3402.webp</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>D.P COMPUTER Hi End</t>
+          <t>M.B Computer Store</t>
         </is>
       </c>
     </row>
@@ -6115,20 +6115,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 X3 OC - 16GB GDDR7 - A0182764</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>89900</v>
+        <v>56500</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6OZyIW7K</t>
+          <t>https://s.shopee.co.th/7VEcZ2CAjg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mpkfshwxt3ij71.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpukkz1kncp821.webp</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>D.P COMPUTER Hi End</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6160,20 +6160,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5080 SOLID CORE OC</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL FROSTBITE OC - 16GB GDDR7 - A0182767</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>52200</v>
+        <v>71700</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyNfJ9SJ</t>
+          <t>https://s.shopee.co.th/7KvCMjCo4f</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mm1mtsp7op3402.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mpukedl8v8ch88.webp</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>M.B Computer Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6205,20 +6205,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 X3 OC - 16GB GDDR7 - A0182764</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 WINDFORCE OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>56500</v>
+        <v>52900</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcZ2CAjg</t>
+          <t>https://s.shopee.co.th/7prSxeAu3m</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpukkz1kncp821.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkd8n452amth61.webp</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6228,8 +6228,11 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="125">
@@ -6250,20 +6253,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL FROSTBITE OC - 16GB GDDR7 - A0182767</t>
+          <t>VGA การ์ดจอ ZOTAC GAMING GeForce RTX 5080 GAMING SOLID CORE OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>71700</v>
+        <v>52400</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCMjCo4f</t>
+          <t>https://s.shopee.co.th/7fY2lLBXOl</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mpukedl8v8ch88.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mki0hzdcdlvk9a.webp</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6273,8 +6276,11 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="126">
@@ -6295,20 +6301,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 WINDFORCE OC SFF 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 (PRIME-RTX5080-16G)</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>52900</v>
+        <v>67600</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prSxeAu3m</t>
+          <t>https://s.shopee.co.th/6pyvloEi5c</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkd8n452amth61.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4j8l8twxuce.webp</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6318,11 +6324,8 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
-      </c>
-      <c r="L126" t="n">
-        <v>10</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -6343,20 +6346,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ ZOTAC GAMING GeForce RTX 5080 GAMING SOLID CORE OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>52400</v>
+        <v>55900</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2lLBXOl</t>
+          <t>https://s.shopee.co.th/6ffVZVFLQb</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mki0hzdcdlvk9a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mmv7325j5mgxbb.webp</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6366,11 +6369,8 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
-        <v>4</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -6391,20 +6391,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 (PRIME-RTX5080-16G)</t>
+          <t>ASUS ROG ASTRAL RTX5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>67600</v>
+        <v>113000</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvloEi5c</t>
+          <t>https://s.shopee.co.th/7AbmAQDRPi</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4j8l8twxuce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mjxxy5kvxjied7.webp</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6436,20 +6436,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>55900</v>
+        <v>71900</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVZVFLQb</t>
+          <t>https://s.shopee.co.th/70ILy7E4kh</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mmv7325j5mgxbb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mjjcxbr8kqo03d.webp</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6481,20 +6481,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC - 16GB GDDR7 (N50803-16D7X-17603930)</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>113000</v>
+        <v>59000</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmAQDRPi</t>
+          <t>https://s.shopee.co.th/3ViTngROr2</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mjxxy5kvxjied7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbdla2gs3l9wca.webp</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6504,8 +6504,11 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -6526,20 +6529,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 EX GAMER 16GB GDDR7</t>
+          <t>MSI VGA GEFORCE RTX 5080 SHADOW 3X OC - 16GB GDDR7 - A0167047</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>71900</v>
+        <v>58000</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70ILy7E4kh</t>
+          <t>https://s.shopee.co.th/3LP3bNS2C1</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mjjcxbr8kqo03d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rask-m9r5cxk7f42o1c.webp</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6549,7 +6552,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6571,20 +6574,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC - 16GB GDDR7 (N50803-16D7X-17603930)</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 XTREME WATERFORCE - 16GB GDDR7 (REV. 1.0) - A0166365</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>59000</v>
+        <v>74200</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTngROr2</t>
+          <t>https://s.shopee.co.th/3qLKCIQ8B8</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbdla2gs3l9wca.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-mai21hqfq6icd6.webp</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6594,11 +6597,8 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
-        <v>1</v>
+          <t>Advice Official Shop</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -6619,20 +6619,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>MSI VGA GEFORCE RTX 5080 SHADOW 3X OC - 16GB GDDR7 - A0167047</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 AORUS MASTER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>58000</v>
+        <v>60700</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3bNS2C1</t>
+          <t>https://s.shopee.co.th/3g1tzzQlW7</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rask-m9r5cxk7f42o1c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mky5qpeaknwi66.webp</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -6664,20 +6664,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 XTREME WATERFORCE - 16GB GDDR7 (REV. 1.0) - A0166365</t>
+          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>74200</v>
+        <v>9000</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKCIQ8B8</t>
+          <t>https://s.shopee.co.th/2qSn0STwCy</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-mai21hqfq6icd6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6687,8 +6687,11 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>EZGGTECH</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -6709,20 +6712,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 AORUS MASTER 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>60700</v>
+        <v>67900</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1tzzQlW7</t>
+          <t>https://s.shopee.co.th/2g9Mo9UZXx</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mky5qpeaknwi66.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4xoa7sr9r50.webp</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6732,7 +6735,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -6754,20 +6757,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC WHITE - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>9000</v>
+        <v>55900</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSn0STwCy</t>
+          <t>https://s.shopee.co.th/3B5dP4SfX4</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mqbi0037km4r5f.webp</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6777,11 +6780,8 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>1</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -6802,20 +6802,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7</t>
+          <t>GALAX RTX5080 HOF GAMING BLACK EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>67900</v>
+        <v>87000</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9Mo9UZXx</t>
+          <t>https://s.shopee.co.th/30mDClTIs3</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4xoa7sr9r50.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mi2smox3b8qo49.webp</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6847,20 +6847,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC WHITE - 16GB GDDR7</t>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>55900</v>
+        <v>69500</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5dP4SfX4</t>
+          <t>https://s.shopee.co.th/4qDrO8MK9Q</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mqbi0037km4r5f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9pqc1bk39ipd8.webp</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6892,20 +6892,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 HOF GAMING BLACK EDITION 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G VENTUS 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>87000</v>
+        <v>64100</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30mDClTIs3</t>
+          <t>https://s.shopee.co.th/4fuRBpMxUP</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mi2smox3b8qo49.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmjx8u2c385h1b.webp</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -6937,20 +6937,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 AERO OC - 16GB GDDR7 (REV. 1.0) - A0166362</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>69500</v>
+        <v>66200</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDrO8MK9Q</t>
+          <t>https://s.shopee.co.th/5AqhmkL3TW</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9pqc1bk39ipd8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m9r5fxjheinlbf.webp</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6960,8 +6960,11 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -6982,20 +6985,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G VENTUS 3X OC - 16GB GDDR7</t>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 AORUS MASTER - 16GB GDDR7 (REV. 1.0) - A0166364</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>64100</v>
+        <v>70500</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuRBpMxUP</t>
+          <t>https://s.shopee.co.th/50XHaRLgoV</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmjx8u2c385h1b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e59iq7j2a769.webp</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7005,7 +7008,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -7027,20 +7030,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 AERO OC - 16GB GDDR7 (REV. 1.0) - A0166362</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 WHITE OC EDITION</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>66200</v>
+        <v>79900</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqhmkL3TW</t>
+          <t>https://s.shopee.co.th/4AyAauOrVM</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m9r5fxjheinlbf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlljzbvrqccib8.webp</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7050,11 +7053,8 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>3</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -7075,20 +7075,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VGA GIGABYTE GEFORCE RTX 5080 AORUS MASTER - 16GB GDDR7 (REV. 1.0) - A0166364</t>
+          <t>(มีโค้ดลด2000฿) RTX 5060 5060Ti 5060 ti 2060Super 3060 3060Ti 3070 3070Ti 4060 4060Ti 4070 4070Ti 4080 4090 5080 5090</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>70500</v>
+        <v>5000</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XHaRLgoV</t>
+          <t>https://s.shopee.co.th/40ekObPUqL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e59iq7j2a769.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7098,8 +7098,11 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>EZGGTECH</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="144">
@@ -7120,20 +7123,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 WHITE OC EDITION</t>
+          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>79900</v>
+        <v>21400</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4AyAauOrVM</t>
+          <t>https://s.shopee.co.th/4Vb0zWNapS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlljzbvrqccib8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7143,7 +7146,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>3CCamera.th</t>
         </is>
       </c>
     </row>
@@ -7165,20 +7168,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(มีโค้ดลด2000฿) RTX 5060 5060Ti 5060 ti 2060Super 3060 3060Ti 3070 3070Ti 4060 4060Ti 4070 4070Ti 4080 4090 5080 5090</t>
+          <t>คอมประกอบพรีเมียม / 4K | Intel Core Ultra 9 285K + RTX 5080 | DDR5 64GB 6400MHz / SSD 2TB | โทนขาว / ชุดแต่ง Lian Li</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5000</v>
+        <v>155700</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40ekObPUqL</t>
+          <t>https://s.shopee.co.th/4LHanDOEAR</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfkgr2oabvux4c.webp</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7188,11 +7191,8 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
-        </is>
-      </c>
-      <c r="L145" t="n">
-        <v>23</v>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -7213,20 +7213,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
+          <t>GIGABYTE RTX5080 AORUS XTREME WATERFORECE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>21400</v>
+        <v>89500</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vb0zWNapS</t>
+          <t>https://s.shopee.co.th/qhicmbYGm</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prhvzpau3yd2.webp</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>3CCamera.th</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Intel Core Ultra 9 285K + RTX 5080 | DDR5 64GB 6400MHz / SSD 2TB | โทนขาว / ชุดแต่ง Lian Li</t>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>155700</v>
+        <v>66900</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHanDOEAR</t>
+          <t>https://s.shopee.co.th/gOIQTcBbl</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfkgr2oabvux4c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9pqq1xfnr3i22.webp</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7303,20 +7303,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 AORUS XTREME WATERFORECE 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>89500</v>
+        <v>75300</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhicmbYGm</t>
+          <t>https://s.shopee.co.th/1BKZ1OaHas</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prhvzpau3yd2.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mmwzh1437egx8f.webp</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -7348,20 +7348,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7 WHITE</t>
+          <t>MSI VGA GEFORCE RTX 5080 VENTUS 3X OC - 16GB GDDR7 - A0167046</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>66900</v>
+        <v>60500</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gOIQTcBbl</t>
+          <t>https://s.shopee.co.th/1118p5auvr</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9pqq1xfnr3i22.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasf-m9r4yrpdj75afe.webp</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -7393,20 +7393,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 GAMING OC - 16GB GDDR7 (REV. 1.0) - A0166361</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>75300</v>
+        <v>65500</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKZ1OaHas</t>
+          <t>https://s.shopee.co.th/BS1pYe5ci</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mmwzh1437egx8f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9e55v65yvbda7.webp</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -7438,20 +7438,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MSI VGA GEFORCE RTX 5080 VENTUS 3X OC - 16GB GDDR7 - A0167046</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 ICHILL X3 V2 - 16GB GDDR7 C50803-16D7X-176069R</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>60500</v>
+        <v>64900</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1118p5auvr</t>
+          <t>https://s.shopee.co.th/18bdFeixh</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasf-m9r4yrpdj75afe.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-modebjzln30gb5.webp</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -7483,20 +7483,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VGA GIGABYTE GEFORCE RTX 5080 GAMING OC - 16GB GDDR7 (REV. 1.0) - A0166361</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | RAM 64GB 6400MHz / SSD 2TB | โทนขาว / HYTE Y70 Touch</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>65500</v>
+        <v>145900</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BS1pYe5ci</t>
+          <t>https://s.shopee.co.th/W4sEAcowo</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9e55v65yvbda7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq8r6vopg3rg36.webp</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -7528,20 +7528,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 ICHILL X3 V2 - 16GB GDDR7 C50803-16D7X-176069R</t>
+          <t>ROG Zephyrus G18 G815LW-S9112W Asus U9-275HX32 G 1TB RTX5080 W11 3YOSS</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>64900</v>
+        <v>125000</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18bdFeixh</t>
+          <t>https://s.shopee.co.th/LlS1rdSHn</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-modebjzln30gb5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-me5o4gxp31mrb5.webp</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -7573,20 +7573,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | RAM 64GB 6400MHz / SSD 2TB | โทนขาว / HYTE Y70 Touch</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>145900</v>
+        <v>130900</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4sEAcowo</t>
+          <t>https://s.shopee.co.th/2BD6DEWTZA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq8r6vopg3rg36.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq90ma8arc3x60.webp</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7618,20 +7618,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ROG Zephyrus G18 G815LW-S9112W Asus U9-275HX32 G 1TB RTX5080 W11 3YOSS</t>
+          <t>MSI RTX5080 SHADOW 3X OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>125000</v>
+        <v>67800</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlS1rdSHn</t>
+          <t>https://s.shopee.co.th/20tg0vX6u9</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-me5o4gxp31mrb5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9prwjnh3cy749.webp</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>NOTEBOOK  CORP</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7663,20 +7663,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>GIGABYTE RTX5080 WINFOREC OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>130900</v>
+        <v>68500</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD6DEWTZA</t>
+          <t>https://s.shopee.co.th/2VpwbqVCtG</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq90ma8arc3x60.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prnu5bv9wxb3.webp</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7708,20 +7708,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>MSI RTX5080 SHADOW 3X OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 MASTER 16G - 16GB GDDR7 (GV-N5080AORUS M-16GD)</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>67800</v>
+        <v>67900</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20tg0vX6u9</t>
+          <t>https://s.shopee.co.th/2LWWPXVqEF</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9prwjnh3cy749.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbbxwlx4z7uc43.webp</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -7753,20 +7753,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 WINFOREC OC SFF 16GB GDDR7</t>
+          <t>GALAX VGA GEFORCE RTX 5080 HOF GAMING BLACK - 16GB GDDR7 - A0172861</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>68500</v>
+        <v>68400</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2VpwbqVCtG</t>
+          <t>https://s.shopee.co.th/1VxPQ0Z0v6</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prnu5bv9wxb3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-824je-me9vcwg1o3cw45.webp</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -7798,20 +7798,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 MASTER 16G - 16GB GDDR7 (GV-N5080AORUS M-16GD)</t>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO OC - 16GB GDDR7 - A0180200</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>67900</v>
+        <v>55500</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2LWWPXVqEF</t>
+          <t>https://s.shopee.co.th/1LdzDhZeG5</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbbxwlx4z7uc43.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-82609-mmd4ly6nd341a5.webp</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -7843,20 +7843,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>GALAX VGA GEFORCE RTX 5080 HOF GAMING BLACK - 16GB GDDR7 - A0172861</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 XTREME WATERFORCE 16G - 16GB GDDR7 (GV-N5080AORUSX W-16GD)</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>68400</v>
+        <v>73800</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxPQ0Z0v6</t>
+          <t>https://s.shopee.co.th/1qaFocXkFC</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134275-824je-me9vcwg1o3cw45.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mbbxc0wleh6p7b.webp</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -7888,20 +7888,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO OC - 16GB GDDR7 - A0180200</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 16GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>55500</v>
+        <v>130900</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LdzDhZeG5</t>
+          <t>https://s.shopee.co.th/1gGpcJYNaB</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134275-82609-mmd4ly6nd341a5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mq8stcq5cx6of7.webp</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -7933,20 +7933,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 XTREME WATERFORCE 16G - 16GB GDDR7 (GV-N5080AORUSX W-16GD)</t>
+          <t>MSI STEALTH A16 AI PLUS Ryzen AI 9 HX 370/RTX 5080 RAM64/2TB - ID26060441</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>73800</v>
+        <v>113400</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaFocXkFC</t>
+          <t>https://s.shopee.co.th/8fQZxB7jNY</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mbbxc0wleh6p7b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpuc7ehxc9ho8a.webp</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>10X Store</t>
         </is>
       </c>
     </row>
@@ -7978,20 +7978,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 16GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>Original 380W 20V 19A อะแดปเตอร์ชาร์จสําหรับ ASUS ROG Strix scar 16 2025 G635LW RTX5080 ADP-380AB B</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>130900</v>
+        <v>6400</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGpcJYNaB</t>
+          <t>https://s.shopee.co.th/8pk09U762b</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mq8stcq5cx6of7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824jc-mep4jcmcgnphd5.webp</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8001,8 +8001,11 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
+          <t>junyue999.th</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -8023,20 +8026,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>MSI STEALTH A16 AI PLUS Ryzen AI 9 HX 370/RTX 5080 RAM64/2TB - ID26060441</t>
+          <t>GIGABYTE RTX5080 AORUS MASTER ICE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>113400</v>
+        <v>82500</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fQZxB7jNY</t>
+          <t>https://s.shopee.co.th/903QLn6She</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpuc7ehxc9ho8a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-map4vxrow1ao8a.webp</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8046,8 +8049,11 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>10X Store</t>
-        </is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -8068,20 +8074,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Original 380W 20V 19A อะแดปเตอร์ชาร์จสําหรับ ASUS ROG Strix scar 16 2025 G635LW RTX5080 ADP-380AB B</t>
+          <t>INNO3D RTX5080 X3 OC 16GB BLACK GDDR7</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6400</v>
+        <v>66900</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pk09U762b</t>
+          <t>https://s.shopee.co.th/9AMqY65pMh</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824jc-mep4jcmcgnphd5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8d39ntj3z7289.webp</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8091,11 +8097,8 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>junyue999.th</t>
-        </is>
-      </c>
-      <c r="L165" t="n">
-        <v>3</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -8116,20 +8119,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 AORUS MASTER ICE 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC WHITE - 16GB GDDR7 (N50803-16D7X-17605211)</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>82500</v>
+        <v>59000</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/903QLn6She</t>
+          <t>https://s.shopee.co.th/80At9xAGjU</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-map4vxrow1ao8a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbdmsesr8qk199.webp</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8139,11 +8142,8 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L166" t="n">
-        <v>1</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -8164,20 +8164,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>INNO3D RTX5080 X3 OC 16GB BLACK GDDR7</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL X3 V2 OC - 16GB GDDR7 - A0182766</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>66900</v>
+        <v>61800</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AMqY65pMh</t>
+          <t>https://s.shopee.co.th/8AUJMG9dOX</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8d39ntj3z7289.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mpujxufur8y4aa.webp</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -8209,20 +8209,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC WHITE - 16GB GDDR7 (N50803-16D7X-17605211)</t>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7 - A0166369</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>59000</v>
+        <v>55500</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/80At9xAGjU</t>
+          <t>https://s.shopee.co.th/8KnjYZ903a</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbdmsesr8qk199.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0k-mc7mmx5y9omf72.webp</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8232,8 +8232,11 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -8254,20 +8257,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL X3 V2 OC - 16GB GDDR7 - A0182766</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>61800</v>
+        <v>78500</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8AUJMG9dOX</t>
+          <t>https://s.shopee.co.th/8V79ks8Mid</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mpujxufur8y4aa.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-me6x1j4ufmyqba.webp</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8277,8 +8280,11 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -8299,20 +8305,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7 - A0166369</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 WINDFORCE OC - 16GB GDDR7 (REV. 1.0) - A0166360</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>55500</v>
+        <v>60300</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8KnjYZ903a</t>
+          <t>https://s.shopee.co.th/9zvxXd2efw</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0k-mc7mmx5y9omf72.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7ras8-m9r4yq4hudlb71.webp</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8326,7 +8332,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -8347,20 +8353,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>78500</v>
+        <v>69200</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8V79ks8Mid</t>
+          <t>https://s.shopee.co.th/AAFNjw21Kz</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-me6x1j4ufmyqba.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9pqwzx9tkvi06.webp</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8370,11 +8376,8 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L171" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -8395,20 +8398,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 WINDFORCE OC - 16GB GDDR7 (REV. 1.0) - A0166360</t>
+          <t>GIGABYTE GAMING RTX5080 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>60300</v>
+        <v>75900</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9zvxXd2efw</t>
+          <t>https://s.shopee.co.th/AKYnwF1O02</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7ras8-m9r4yq4hudlb71.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5zvhd595sc69a.webp</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8418,11 +8421,8 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L172" t="n">
-        <v>2</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -8443,20 +8443,20 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 EX GAMER 16GB GDDR7 WHITE</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 WINDFORCE OC SFF 16G - 16GB GDDR7 (GV-N5080WF3OC-16GD)</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>69200</v>
+        <v>58800</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAFNjw21Kz</t>
+          <t>https://s.shopee.co.th/AUsE8Y0kf5</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9pqwzx9tkvi06.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbc1uyc222bab6.webp</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -8488,20 +8488,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>GIGABYTE GAMING RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] MSI GAMING TRIO RTX5080 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>75900</v>
+        <v>72900</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKYnwF1O02</t>
+          <t>https://s.shopee.co.th/9KgGkP5C1s</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5zvhd595sc69a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m5qng58cco0t25.webp</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8513,6 +8513,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -8533,20 +8536,20 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 WINDFORCE OC SFF 16G - 16GB GDDR7 (GV-N5080WF3OC-16GD)</t>
+          <t>RTX5080/16GB GALAX 1-CLICK (OC/D7) - A0166352</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>58800</v>
+        <v>59600</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AUsE8Y0kf5</t>
+          <t>https://s.shopee.co.th/9Uzgwi4Ygv</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbc1uyc222bab6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m81gt7mb1w4u18.webp</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8556,8 +8559,11 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="176">
@@ -8578,20 +8584,20 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] MSI GAMING TRIO RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 HOF GAMING BLACK EDITION - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>72900</v>
+        <v>70600</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9KgGkP5C1s</t>
+          <t>https://s.shopee.co.th/9fJ7913vLy</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m5qng58cco0t25.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdpq3ctyx2ta3e.webp</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8601,11 +8607,8 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L176" t="n">
-        <v>1</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -8626,20 +8629,20 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>RTX5080/16GB GALAX 1-CLICK (OC/D7) - A0166352</t>
+          <t>ASUS ROG ASTRAL RTX5080 OC WHITE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>59600</v>
+        <v>89500</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9Uzgwi4Ygv</t>
+          <t>https://s.shopee.co.th/9pcXLK3I11</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m81gt7mb1w4u18.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-misduj582yo30b.webp</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8649,11 +8652,8 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L177" t="n">
-        <v>11</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -8674,20 +8674,20 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 HOF GAMING BLACK EDITION - 16GB GDDR7</t>
+          <t>ZOTAC RTX5080 SOLID GAMING OC 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>70600</v>
+        <v>64900</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7913vLy</t>
+          <t>https://s.shopee.co.th/60PomHHsnI</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdpq3ctyx2ta3e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-mapdn0hs6q9gfb.webp</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -8719,20 +8719,20 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5080 OC WHITE 16GB GDDR7</t>
+          <t>GALAX RTX5080 HOF GAMING 16GB GDDR7</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>89500</v>
+        <v>87000</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9pcXLK3I11</t>
+          <t>https://s.shopee.co.th/6AjEyaHFSL</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-misduj582yo30b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mi2scd35wirsed.webp</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8764,20 +8764,20 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5080 SOLID GAMING OC 16GB GDDR7 WHITE</t>
+          <t>GIGABYTE AERO RTX5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>64900</v>
+        <v>78500</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PomHHsnI</t>
+          <t>https://s.shopee.co.th/6L2fAtGc7O</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-mapdn0hs6q9gfb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mki1wyjsh14yd6.webp</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8789,6 +8789,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -8809,20 +8812,20 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 HOF GAMING 16GB GDDR7</t>
+          <t>ZOTAC GAMING RTX5080 SOLID CORE OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>87000</v>
+        <v>62500</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjEyaHFSL</t>
+          <t>https://s.shopee.co.th/6VM5NCFymR</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mi2scd35wirsed.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mloguv0dy97323.webp</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8854,20 +8857,20 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>GIGABYTE AERO RTX5080 16GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5080 SOLID CORE OC - 16GB GDDR7 (ZT-B50800J2-10P)</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>78500</v>
+        <v>59000</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fAtGc7O</t>
+          <t>https://s.shopee.co.th/5LA7z3KQ9E</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mki1wyjsh14yd6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbvy43nc50gsdd.webp</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8877,11 +8880,8 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L182" t="n">
-        <v>1</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -8902,20 +8902,20 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5080 SOLID CORE OC 16GB GDDR7</t>
+          <t>ASUS TUF RTX5080 GAMING OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>62500</v>
+        <v>81000</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5NCFymR</t>
+          <t>https://s.shopee.co.th/5VTYBMJmoH</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mloguv0dy97323.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m9pk6xb8lmjk47.webp</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8947,20 +8947,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5080 SOLID CORE OC - 16GB GDDR7 (ZT-B50800J2-10P)</t>
+          <t>INNO3D RTX5080 X3 OC WHITE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>59000</v>
+        <v>68300</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA7z3KQ9E</t>
+          <t>https://s.shopee.co.th/5fmyNfJ9TK</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbvy43nc50gsdd.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8d2yz7814ax90.webp</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -8992,20 +8992,20 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ASUS TUF RTX5080 GAMING OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7 (GV-N5080AERO OC-16GD)</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>81000</v>
+        <v>67000</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYBMJmoH</t>
+          <t>https://s.shopee.co.th/5q6OZyIW8N</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m9pk6xb8lmjk47.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbbyjj2rglflce.webp</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -9037,20 +9037,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>INNO3D RTX5080 X3 OC WHITE 16GB GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE AORUS RTX5080 MASTER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>68300</v>
+        <v>80900</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyNfJ9TK</t>
+          <t>https://s.shopee.co.th/7KvCMjCo5g</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8d2yz7814ax90.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml4sii5ubnym20.webp</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9062,6 +9062,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L186" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -9082,20 +9085,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7 (GV-N5080AERO OC-16GD)</t>
+          <t>ROG ASTRAL RTX5080 16GB OC GDDR7 BLACK</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>67000</v>
+        <v>85500</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6OZyIW8N</t>
+          <t>https://s.shopee.co.th/7VEcZ2CAkj</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbbyjj2rglflce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq632jnzevwuf9.webp</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9105,7 +9108,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9127,20 +9130,20 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE AORUS RTX5080 MASTER 16GB GDDR7</t>
+          <t>ROG ASTRAL RTX5080 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>80900</v>
+        <v>88500</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCMjCo5g</t>
+          <t>https://s.shopee.co.th/7fY2lLBXPm</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml4sii5ubnym20.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5p939h7ybw69b.webp</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9175,20 +9178,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5080 16GB OC GDDR7 BLACK</t>
+          <t>MSI RTX5080 VENTUS X3 OC PLUS 16GB GDDR7</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>85500</v>
+        <v>63000</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcZ2CAkj</t>
+          <t>https://s.shopee.co.th/7prSxeAu4p</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq632jnzevwuf9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mnkzq2y21x51b3.webp</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9220,20 +9223,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>ASUS PRIME RTX5080 OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>88500</v>
+        <v>74300</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2lLBXPm</t>
+          <t>https://s.shopee.co.th/6ffVZVFLRc</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5p939h7ybw69b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9pl3a6dymlq34.webp</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9245,9 +9248,6 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L190" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -9268,20 +9268,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>MSI RTX5080 VENTUS X3 OC PLUS 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G SHADOW 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>63000</v>
+        <v>60500</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prSxeAu4p</t>
+          <t>https://s.shopee.co.th/6pyvloEi6f</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mnkzq2y21x51b3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m807f87tz7xq68.webp</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9291,8 +9291,11 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -9313,20 +9316,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ASUS PRIME RTX5080 OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 GAMING OC 16G - 16GB GDDR7 (GV-N5080GAMING OC-16GD)</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>74300</v>
+        <v>63500</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVZVFLRc</t>
+          <t>https://s.shopee.co.th/70ILy7E4li</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9pl3a6dymlq34.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0o-mbbz0v0mfsdt28.webp</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9336,7 +9339,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -9358,20 +9361,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G SHADOW 3X OC - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>60500</v>
+        <v>61400</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvloEi6f</t>
+          <t>https://s.shopee.co.th/7AbmAQDRQl</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m807f87tz7xq68.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0g-mb65w0t41ai927.webp</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9383,9 +9386,6 @@
         <is>
           <t>JIB Official Store</t>
         </is>
-      </c>
-      <c r="L193" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -9406,20 +9406,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 GAMING OC 16G - 16GB GDDR7 (GV-N5080GAMING OC-16GD)</t>
+          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5080 16GB GDDR7 OC EDITION (TUF-RTX5080-O16G-GAMING)</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>63500</v>
+        <v>71700</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70ILy7E4li</t>
+          <t>https://s.shopee.co.th/3LP3bNS2D2</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0o-mbbz0v0mfsdt28.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mb7lu03gdf7ace.webp</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9451,20 +9451,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>61400</v>
+        <v>63900</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmAQDRQl</t>
+          <t>https://s.shopee.co.th/3ViTngROs5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0g-mb65w0t41ai927.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9qqhz75s2cu0e.webp</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9476,6 +9476,9 @@
         <is>
           <t>JIB Official Store</t>
         </is>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -9496,20 +9499,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5080 16GB GDDR7 OC EDITION (TUF-RTX5080-O16G-GAMING)</t>
+          <t>คอมพิวเตอร์ประกอบ HYTE Y40 RTX5080 BLACK/WHITE</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>71700</v>
+        <v>155900</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3bNS2D2</t>
+          <t>https://s.shopee.co.th/3g1tzzQlX8</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mb7lu03gdf7ace.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m5v66xgrzeuv7b.webp</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9519,7 +9522,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9541,20 +9544,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+          <t>คอมพิวเตอร์ประกอบ HTYE Y60 RTX5080 OC GDDR7 BLACK</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>63900</v>
+        <v>159000</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTngROs5</t>
+          <t>https://s.shopee.co.th/3qLKCIQ8CB</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9qqhz75s2cu0e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m63p4ze31cil46.webp</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9564,11 +9567,8 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L197" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -9584,25 +9584,25 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ HYTE Y40 RTX5080 BLACK/WHITE</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>155900</v>
+        <v>169700</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1tzzQlX8</t>
+          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m5v66xgrzeuv7b.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9612,8 +9612,11 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -9629,25 +9632,25 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ HTYE Y60 RTX5080 OC GDDR7 BLACK</t>
+          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>159000</v>
+        <v>301100</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKCIQ8CB</t>
+          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m63p4ze31cil46.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9657,7 +9660,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -9679,20 +9682,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>169700</v>
+        <v>236900</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
+          <t>https://s.shopee.co.th/1qaAsBag8T</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9702,11 +9705,8 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L200" t="n">
-        <v>1</v>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -9727,20 +9727,20 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
+          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>301100</v>
+        <v>288900</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
+          <t>https://s.shopee.co.th/1LduHGca9O</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9772,20 +9772,20 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>236900</v>
+        <v>195500</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaAsBag8T</t>
+          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9795,8 +9795,11 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -9817,20 +9820,20 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>288900</v>
+        <v>180700</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LduHGca9O</t>
+          <t>https://s.shopee.co.th/1113sedqpM</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -9840,7 +9843,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -9862,20 +9865,20 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>195500</v>
+        <v>180000</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
+          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -9885,11 +9888,11 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>TECHNOCOM.OFFICIAL</t>
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -9910,20 +9913,20 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
+          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>180700</v>
+        <v>337700</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1113sedqpM</t>
+          <t>https://s.shopee.co.th/gODU2f7VK</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -9933,8 +9936,11 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>I KNOW YOU</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -9955,20 +9961,20 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>180000</v>
+        <v>204900</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
+          <t>https://s.shopee.co.th/qhdgLeUAN</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -9978,11 +9984,8 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
-        </is>
-      </c>
-      <c r="L206" t="n">
-        <v>2</v>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -10003,20 +10006,20 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>337700</v>
+        <v>193900</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gODU2f7VK</t>
+          <t>https://s.shopee.co.th/LlN5QgOBI</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10026,11 +10029,8 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>I KNOW YOU</t>
-        </is>
-      </c>
-      <c r="L207" t="n">
-        <v>1</v>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -10051,20 +10051,20 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>204900</v>
+        <v>205600</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhdgLeUAN</t>
+          <t>https://s.shopee.co.th/W4nHjfkqL</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -10096,20 +10096,20 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>193900</v>
+        <v>193400</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlN5QgOBI</t>
+          <t>https://s.shopee.co.th/18WgoherG</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10141,20 +10141,20 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
+          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>205600</v>
+        <v>189900</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4nHjfkqL</t>
+          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -10186,20 +10186,20 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>193400</v>
+        <v>198500</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18WgoherG</t>
+          <t>https://s.shopee.co.th/50XCe0OciG</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -10231,20 +10231,20 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
+          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>189900</v>
+        <v>189000</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
+          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10276,20 +10276,20 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
+          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>198500</v>
+        <v>192900</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XCe0OciG</t>
+          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10321,20 +10321,20 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
+          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>189000</v>
+        <v>187900</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
+          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10366,20 +10366,20 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>192900</v>
+        <v>198500</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
+          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10391,6 +10391,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L215" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="216">
@@ -10411,20 +10414,20 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
+          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>187900</v>
+        <v>195500</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
+          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10456,20 +10459,20 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
+          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>198500</v>
+        <v>459500</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
+          <t>https://s.shopee.co.th/40efSASQkA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10481,9 +10484,6 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L217" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="218">
@@ -10504,20 +10504,20 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
+          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>195500</v>
+        <v>186900</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
+          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10549,20 +10549,20 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
+          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>459500</v>
+        <v>186900</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40efSASQkA</t>
+          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10594,20 +10594,20 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>186900</v>
+        <v>185500</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
+          <t>https://s.shopee.co.th/3qLFFrT45B</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -10639,20 +10639,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
+          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>186900</v>
+        <v>269500</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
+          <t>https://s.shopee.co.th/3LOyewUy66</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -10684,20 +10684,20 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
+          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>185500</v>
+        <v>195000</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLFFrT45B</t>
+          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -10729,20 +10729,20 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
+          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>269500</v>
+        <v>195500</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOyewUy66</t>
+          <t>https://s.shopee.co.th/30m8GKWEm4</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -10774,20 +10774,20 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
+          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>195000</v>
+        <v>179900</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
+          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -10819,20 +10819,20 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>195500</v>
+        <v>185500</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8GKWEm4</t>
+          <t>https://s.shopee.co.th/2g9HriXVS2</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -10864,20 +10864,20 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>179900</v>
+        <v>198500</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
+          <t>https://s.shopee.co.th/2qSi41Ws75</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -10909,20 +10909,20 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
+          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>185500</v>
+        <v>192900</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+          <t>https://s.shopee.co.th/7fXxouETJ2</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -10954,20 +10954,20 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
+          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>198500</v>
+        <v>188500</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSi41Ws75</t>
+          <t>https://s.shopee.co.th/7prO1DDpy5</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -10999,20 +10999,20 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
+          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>192900</v>
+        <v>215000</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXxouETJ2</t>
+          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11044,20 +11044,20 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>188500</v>
+        <v>228800</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prO1DDpy5</t>
+          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -11089,20 +11089,20 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
+          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>215000</v>
+        <v>209000</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
+          <t>https://s.shopee.co.th/70IH1gH0ey</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11112,14 +11112,14 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>shoppingpc dotnet</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ai_calculator</t>
+          <t>ai_calculator_cpu</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -11129,25 +11129,25 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>r9_7950x</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
+          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>228800</v>
+        <v>22700</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
+          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11157,14 +11157,17 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>mcwinner</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ai_calculator</t>
+          <t>ai_calculator_cpu</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -11174,25 +11177,25 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>r9_7950x</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>209000</v>
+        <v>26500</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70IH1gH0ey</t>
+          <t>https://s.shopee.co.th/2g9IIXOei9</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11202,8 +11205,11 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>shoppingpc dotnet</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="234">
@@ -11224,20 +11230,20 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
+          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>22700</v>
+        <v>10500</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
+          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11247,11 +11253,11 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>mcwinner</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
       <c r="L234" t="n">
-        <v>19</v>
+        <v>382</v>
       </c>
     </row>
     <row r="235">
@@ -11272,20 +11278,20 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>26500</v>
+        <v>33000</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9IIXOei9</t>
+          <t>https://s.shopee.co.th/30m8h9NO2F</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11320,20 +11326,20 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>10500</v>
+        <v>29900</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11343,11 +11349,11 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>atSine Tech</t>
         </is>
       </c>
       <c r="L236" t="n">
-        <v>382</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -11368,20 +11374,20 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>33000</v>
+        <v>24200</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11391,11 +11397,11 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
       <c r="L237" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="238">
@@ -11416,20 +11422,20 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+          <t>CPU AMD AM5 RYZEN 9 9950X3D (NEXT) - A0168684</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>29900</v>
+        <v>32200</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+          <t>https://s.shopee.co.th/3qLFggKDLS</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11439,106 +11445,10 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>atSine Tech</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
       <c r="L238" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>ai_calculator_cpu</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>r9_7950x</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
-        </is>
-      </c>
-      <c r="E239" t="n">
-        <v>24200</v>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L239" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>ai_calculator_cpu</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>r9_7950x</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>CPU AMD AM5 RYZEN 9 9950X3D (NEXT) - A0168684</t>
-        </is>
-      </c>
-      <c r="E240" t="n">
-        <v>32200</v>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/3qLFggKDLS</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L240" t="n">
         <v>11</v>
       </c>
     </row>

--- a/data/affiliate/picks.xlsx
+++ b/data/affiliate/picks.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N238"/>
+  <dimension ref="A1:N242"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1348,20 +1348,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
+          <t>VGA ZOTAC GAMING GEFORCE RTX 5070 SOLID OC 12GB GDDR7 (ZT-B50700J-10P) (รับประกัน3ปี)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9000</v>
+        <v>26200</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pk0FdV2MF</t>
+          <t>https://s.shopee.co.th/7VEciEtBZu</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-me8br9vvoe11c5.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1371,11 +1371,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
+          <t>pansonics</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1396,20 +1396,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(15,990฿) GALAX RTX 5070 12G RGB🌈 ของใหม่ มือ1</t>
+          <t>VGA GALAX GEFORCE RTX 5070 EX Gamer 1-Click OC 12GB GDDR7 192-bit (รับประกัน3ปี)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9600</v>
+        <v>28900</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8KnjeiWwNA</t>
+          <t>https://s.shopee.co.th/7KvCVvtout</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mfcwvayul2x892.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mkknnqo1ueww40.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1419,11 +1419,11 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>การ์ดจอมือสอง อุปกรณ์คอม</t>
+          <t>pansonics</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1444,20 +1444,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VGA ZOTAC GAMING GEFORCE RTX 5070 SOLID OC 12GB GDDR7 (ZT-B50700J-10P) (รับประกัน3ปี)</t>
+          <t>VGA ASUS PRIME GEFORCE RTX 5070 WHITE OC  EDITION 12GB GDDR7 (รับประกัน3ปี)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>26200</v>
+        <v>31500</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8V79r1WJ2D</t>
+          <t>https://s.shopee.co.th/5q6OjAzWxc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-me8br9vvoe11c5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfupu0o5b7kf65.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>217</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -1492,20 +1492,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VGA GALAX GEFORCE RTX 5070 EX Gamer 1-Click OC 12GB GDDR7 192-bit (รับประกัน3ปี)</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G SHADOW 3X OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>28900</v>
+        <v>23900</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/80AtG6YD38</t>
+          <t>https://s.shopee.co.th/5fmyWs0AIb</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mkknnqo1ueww40.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mlygum4567er09.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1515,11 +1515,11 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>pansonics</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1540,20 +1540,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VGA ASUS PRIME GEFORCE RTX 5070 WHITE OC  EDITION 12GB GDDR7 (รับประกัน3ปี)</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 GAMING OC 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>31500</v>
+        <v>28500</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8AUJSPXZiB</t>
+          <t>https://s.shopee.co.th/5VTYKZ0nda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfupu0o5b7kf65.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mhgh1lfdj6de72.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1563,11 +1563,8 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>pansonics</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>17</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1588,20 +1585,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G SHADOW 3X OC - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 12GB GDDR7 (PRIME-RTX5070-12G)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>23900</v>
+        <v>27500</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKYo2OPKJc</t>
+          <t>https://s.shopee.co.th/5LA88G1QyZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mlygum4567er09.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mhgdx8jz03cwa4.webp</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1613,9 +1610,6 @@
         <is>
           <t>แอดบอล คอมพิวเตอร์</t>
         </is>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1636,20 +1630,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS DUAL GEFORCE RTX 5070 12GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 12GB GDDR7 OC EDITION (PRIME-RTX5070-O12G)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>23900</v>
+        <v>28900</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AUsEEhOgyf</t>
+          <t>https://s.shopee.co.th/6VM5WOwzbo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlj56pbe4c1t6c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mm74uk247pc1bd.webp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1681,20 +1675,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 12GB GDDR7 (PRIME-RTX5070-12G)</t>
+          <t>VGA (การ์ดแสดงผล) PNY GEFORCE RTX 5070 ARGB EPIC-X RGB OVERCLOCKED TRIPLE FAN - 12GB GDDR7 VCG507012TFXXPB1-O</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>27500</v>
+        <v>29000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9zvxdmQaza</t>
+          <t>https://s.shopee.co.th/6L2fK5xcwn</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mhgdx8jz03cwa4.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mkgpazghoefa01.webp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1726,20 +1720,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 12GB GDDR7 OC EDITION (PRIME-RTX5070-O12G)</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5070 GAMINGPRO - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>28900</v>
+        <v>25900</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAFNq5Pxed</t>
+          <t>https://s.shopee.co.th/6AjF7myGHm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mm74uk247pc1bd.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mm73lr6fcc8wde.webp</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1771,20 +1765,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) PNY GEFORCE RTX 5070 ARGB EPIC-X RGB OVERCLOCKED TRIPLE FAN - 12GB GDDR7 VCG507012TFXXPB1-O</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G GAMING TRIO OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>29000</v>
+        <v>34500</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7FARrfY</t>
+          <t>https://s.shopee.co.th/60PovTytcl</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mkgpazghoefa01.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mlj63he5z9j5eb.webp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1796,6 +1790,9 @@
         <is>
           <t>แอดบอล คอมพิวเตอร์</t>
         </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1816,20 +1813,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 TI 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 TWIN X2 OC WHITE - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>39000</v>
+        <v>27900</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9pcXRTREKb</t>
+          <t>https://s.shopee.co.th/9pcXUWkIqW</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mm1j7jihgoap88.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mm74le80axhg26.webp</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1861,20 +1858,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5070 GAMINGPRO - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G SHADOW 2X OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>25900</v>
+        <v>25500</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9KgGqYT8LW</t>
+          <t>https://s.shopee.co.th/9fJ7IDkwBV</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mm73lr6fcc8wde.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlyf8z1anrbc9a.webp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1906,20 +1903,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) VGA COLORFUL GEFORCE RTX 5070 TI BATTLE AX - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5070 12GB GDDR7 OC EDITION (TUF-RTX5070-O12G-GAMING)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>40000</v>
+        <v>29400</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9Uzh2rSV0Z</t>
+          <t>https://s.shopee.co.th/9Uzh5ulZWU</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mkgrq7veafpg48.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mhge8e0c0utj90.webp</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1951,20 +1948,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 GAMING OC 12G - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G VANGUARD SOC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>28500</v>
+        <v>29000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fH2eYQy</t>
+          <t>https://s.shopee.co.th/9KgGtbmCrT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mhgh1lfdj6de72.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mlj7htauark48d.webp</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1996,20 +1993,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G GAMING TRIO OC - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G INSPIRE 3X OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>34500</v>
+        <v>31900</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5TLdv61</t>
+          <t>https://s.shopee.co.th/AUsEHkhlUi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mlj63he5z9j5eb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mn33svflo9ok19.webp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2021,9 +2018,6 @@
         <is>
           <t>แอดบอล คอมพิวเตอร์</t>
         </is>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2044,20 +2038,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 TI X3 - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5070 INFINITY 3 - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>39900</v>
+        <v>24900</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PosQfp6w</t>
+          <t>https://s.shopee.co.th/AKYo5RiOph</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mnb3ffe2756p85.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlj6vysxk9vs85.webp</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2089,20 +2083,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 TWIN X2 OC WHITE - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS DUAL GEFORCE RTX 5070 12GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27900</v>
+        <v>23900</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjF4jfBlz</t>
+          <t>https://s.shopee.co.th/AAFNt8j2Ag</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mm74le80axhg26.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlj56pbe4c1t6c.webp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2134,20 +2128,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G SHADOW 2X OC - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 AERO OC 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>25500</v>
+        <v>28900</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyToh5mu</t>
+          <t>https://s.shopee.co.th/9zvxgpjfVf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlyf8z1anrbc9a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlj4jn7p52bn89.webp</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2179,20 +2173,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 TI EX GAMER 1-CLICK OC - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 WHITE OC EDITION 12GB GDDR7</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>39900</v>
+        <v>28000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6Og7gSRx</t>
+          <t>https://s.shopee.co.th/8V79u4pNYO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mn5rk2rprw1u22.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mlj8li0hw7pgca.webp</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2224,20 +2218,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5070 12GB GDDR7 OC EDITION (TUF-RTX5070-O12G-GAMING)</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 1-CLICK OC WHITE - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>29400</v>
+        <v>27500</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA85CiMSs</t>
+          <t>https://s.shopee.co.th/8Knjhlq0tN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mhge8e0c0utj90.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134201-81ztk-mhg4bj1gpse8cf.webp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2269,20 +2263,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G INSPIRE 3X OC - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 TWIN X2 - 12GB GDDR7 (N50702-12D7-195064N)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>31900</v>
+        <v>25500</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYHVhj7v</t>
+          <t>https://s.shopee.co.th/8AUJVSqeEM</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mn33svflo9ok19.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mlj48zqab1twc0.webp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2314,20 +2308,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 TI 16G SHADOW 3X OC - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 EAGLE OC ICE SFF 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>39900</v>
+        <v>29000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2rUZTjM</t>
+          <t>https://s.shopee.co.th/80AtJ9rHZL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mofl9m7g2m1bfe.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mlj6cvh6afpcfc.webp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2359,20 +2353,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 AERO OC 12G - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 EAGLE OC SFF 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>28900</v>
+        <v>24900</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prT3nYqOP</t>
+          <t>https://s.shopee.co.th/9AMqhImqCa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlj4jn7p52bn89.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mlj49goxj4sg7b.webp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2404,20 +2398,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5070 TI GAMINGPRO - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 EX GAMER 1-CLICK OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>40000</v>
+        <v>26500</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCSsakPK</t>
+          <t>https://s.shopee.co.th/903QUznTXZ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mn5s9hngkwzo32.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mhfxc8du1vkad3.webp</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2449,20 +2443,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 WHITE OC EDITION 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 WINDFORCE OC SFF 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>28000</v>
+        <v>27000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcfBa74N</t>
+          <t>https://s.shopee.co.th/8pk0Igo6sY</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mlj8li0hw7pgca.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mhgg3kczd3wj7a.webp</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2494,20 +2488,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 1-CLICK OC WHITE - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 EX GAMER 1-CLICK OC WHITE - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>27500</v>
+        <v>28600</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70IM4Gc15I</t>
+          <t>https://s.shopee.co.th/8fQa6NokDX</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134201-81ztk-mhg4bj1gpse8cf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mkgpmmnbvkee06.webp</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2539,20 +2533,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 TWIN X2 - 12GB GDDR7 (N50702-12D7-195064N)</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG STRIX GEFORCE RTX 5070 12GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>25500</v>
+        <v>34600</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmGZbNkL</t>
+          <t>https://s.shopee.co.th/1qaFxpEl5E</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mlj48zqab1twc0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mhgdehhugembdd.webp</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2584,20 +2578,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG STRIX GEFORCE RTX 5070 TI 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G VENTUS 2X OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>47500</v>
+        <v>27500</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVfedHlG</t>
+          <t>https://s.shopee.co.th/1gGplWFOQD</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mm748jdbevwgb8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zti-mkgs6ubokcg4e6.webp</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2629,20 +2623,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 EAGLE OC ICE SFF 12G - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 1-CLICK OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>29000</v>
+        <v>27900</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvrxceQJ</t>
+          <t>https://s.shopee.co.th/1VxPZDG1lC</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mlj6cvh6afpcfc.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mhfx1sjd3rpna9.webp</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2674,20 +2668,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 EAGLE OC SFF 12G - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5070 MASTER 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>24900</v>
+        <v>32900</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1u68ohqi</t>
+          <t>https://s.shopee.co.th/1LdzMuGf6B</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mlj49goxj4sg7b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mlj51w24z1u08f.webp</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2719,20 +2713,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 EX GAMER 1-CLICK OC - 12GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5070 TWIN EDGE - 12GB GDDR7 (ZT-B50700E-10P)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>26500</v>
+        <v>22000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKIRo4Vl</t>
+          <t>https://s.shopee.co.th/2Vpwl3CDjQ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mhfxc8du1vkad3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mhggp8eo347a7a.webp</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2764,20 +2758,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 TI 16G VENTUS 3X OC - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 X3 OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>39900</v>
+        <v>25500</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3hWpyWg</t>
+          <t>https://s.shopee.co.th/2LWWYkCr4P</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkgq0zywyzgk9b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlj485n39xcf69.webp</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2809,20 +2803,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5070 TWIN EDGE - 12GB GDDR7 (ZT-B50700E-10P)</t>
+          <t>BOSSPC / INTEL CORE ULTRA 5 225F / 32GB DDR5 BUS6000 RGB / RTX 5070 12GB / M.2 1TB</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22000</v>
+        <v>77500</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTtppLBj</t>
+          <t>https://s.shopee.co.th/2BD6MRDUPO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mhggp8eo347a7a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mnnrlzy11m9v63.webp</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2832,7 +2826,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>BOSSPC</t>
         </is>
       </c>
     </row>
@@ -2854,20 +2848,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 TI 1-CLICK OC 2X - 16GB GDDR7</t>
+          <t>VGA ZOTAC GEFORCE RTX 5070 GAMING TWIN EDGE OC - 12GB GDDR7 มือสอง</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>39900</v>
+        <v>24600</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30mDIurFCe</t>
+          <t>https://s.shopee.co.th/20tgA8E7kN</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mjqqmfpm9fd0ef.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mq00fruhkkxs6b.webp</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2877,11 +2871,8 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
+          <t>M&amp;N Computer</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -2902,20 +2893,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 EX GAMER 1-CLICK OC WHITE - 12GB GDDR7</t>
+          <t>Geforce RTX 5070 OC 12GB GDDR7 Snow Fox DLSS 4 Esports Design Live AI กราฟิกการ์ดสําหรับเล่นเกมอิสระ</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>28600</v>
+        <v>90500</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5dVDqbrh</t>
+          <t>https://s.shopee.co.th/W4sNNJpn6</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mkgpmmnbvkee06.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7renx-m8d3bdfuxnswe8.webp</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2925,7 +2916,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>PC Accessories Shop</t>
         </is>
       </c>
     </row>
@@ -2947,20 +2938,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 WINDFORCE OC SFF 12G - 12GB GDDR7</t>
+          <t>คอมประกอบครบชุด SPCOMZING RYZEN5 5600 / M.2 500GB / RTX 5070 12GB / B550M / 32GB DDR4 / จอ 24นิ้ว</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>27000</v>
+        <v>26700</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9MuIsVsc</t>
+          <t>https://s.shopee.co.th/LlSB4KT85</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mhgg3kczd3wj7a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mp20d8fdwykh66.webp</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2970,7 +2961,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>SPCOMZING</t>
         </is>
       </c>
     </row>
@@ -2992,20 +2983,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG STRIX GEFORCE RTX 5070 12GB GDDR7 OC EDITION</t>
+          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT VOID OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>34600</v>
+        <v>46000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSn6brsXf</t>
+          <t>https://s.shopee.co.th/BS1ylL6T4</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mhgdehhugembdd.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mln8wxv1kao1df.webp</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3015,7 +3006,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3037,20 +3028,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G VANGUARD SOC - 12GB GDDR7</t>
+          <t>GALAX RTX5070 EX GAMER 12GB GDDR7</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>29000</v>
+        <v>35000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XHgajd96</t>
+          <t>https://s.shopee.co.th/18bmSLjo3</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mlj7htauark48d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-ml3do6g159fm84.webp</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3060,7 +3051,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3082,20 +3073,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5070 INFINITY 3 - 12GB GDDR7</t>
+          <t>GIGABYTE RTX5070 AERO OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>24900</v>
+        <v>37900</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5Aqhstizo9</t>
+          <t>https://s.shopee.co.th/1BKZAbHIRI</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlj6vysxk9vs85.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-ml3b0ujyyigw9f.webp</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3105,7 +3096,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3127,20 +3118,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 TI GAMING OC 16G - 16GB GDDR7</t>
+          <t>ZOTAC GAMING RTX5070 TWIN EDGE 12GB GDDR7</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>38900</v>
+        <v>31000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuRHyktp4</t>
+          <t>https://s.shopee.co.th/1118yIHvmH</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-merzaz171ts0c9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-ma9clcgr2jrn46.webp</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3150,11 +3141,8 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3175,20 +3163,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 1-CLICK OC - 12GB GDDR7</t>
+          <t>INNO3D RTX5070 TWIN X2 OC 12GB WHITE GDDR7</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>27900</v>
+        <v>33600</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDrUHkGU7</t>
+          <t>https://s.shopee.co.th/qhilzIZ7G</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mhfx1sjd3rpna9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8fpz7z7z3m167.webp</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3198,7 +3186,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3220,20 +3208,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5070 12G VENTUS 2X OC - 12GB GDDR7</t>
+          <t>MSI RTX5070 GAMING TRIO OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>27500</v>
+        <v>36300</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHatMmAV2</t>
+          <t>https://s.shopee.co.th/gOIZgJCSF</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zti-mkgs6ubokcg4e6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8fplkpwu26459.webp</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3243,7 +3231,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3265,20 +3253,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5070 MASTER 12G - 12GB GDDR7</t>
+          <t>GALAX RTX5070 1-CLICK 12GB OC GDDR7</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>32900</v>
+        <v>32800</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vb15flXA5</t>
+          <t>https://s.shopee.co.th/4Vb18j4bg0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mlj51w24z1u08f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m7t43sao8g0oc9.webp</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3288,7 +3276,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3310,20 +3298,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5070 X3 OC - 12GB GDDR7</t>
+          <t>MSI RTX5070 VANGUARD SOC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>25500</v>
+        <v>42900</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40ekUknRB0</t>
+          <t>https://s.shopee.co.th/4LHawQ5F0z</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlj485n39xcf69.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m7t7pn5x4rli2a.webp</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3333,7 +3321,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3355,20 +3343,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5070 TI OC EDITION 16GB GDDR7</t>
+          <t>ASUS PRIME RTX5070 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>41500</v>
+        <v>34900</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4AyAh3mnq3</t>
+          <t>https://s.shopee.co.th/4AyAk75sLy</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mn5rzhzup53a0c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fw1olmz4kue9.webp</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3378,7 +3366,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3400,20 +3388,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 TI HOF GAMING - 16GB GDDR7</t>
+          <t>ZOTAC RTX5070 SOLID GAMING OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>48500</v>
+        <v>32500</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1118vEyrGS</t>
+          <t>https://s.shopee.co.th/40ekXo6Vgx</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlygemsgbev722.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fob1nq1jpl67.webp</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3423,7 +3411,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3445,20 +3433,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ AMD Ryzen 7 7800X3D 5.0GHz/B650M/DDR5 32GB (16X2) 5200/M.2 512GB/PSU750W/ RTX 5070</t>
+          <t>MSI RTX5070 SHADOW 2X OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>65700</v>
+        <v>29500</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKZ7XyDvV</t>
+          <t>https://s.shopee.co.th/5Aqhvx24KC</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mp9d847uhgjm80.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8u1tn79jysufe.webp</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3468,7 +3456,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3490,20 +3478,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ AMD Ryzen 7 7900X3D 5.6GHz/B650M/DDR5 32GB (16X2) 5200/M.2 512GB/PSU750W/ RTX 5070</t>
+          <t>GALAX RTX5070 1-Click OC 12GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>65700</v>
+        <v>33000</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gOIWd07wQ</t>
+          <t>https://s.shopee.co.th/50XHje2hfB</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mpgo7nupupzj78.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fuipfj90xad4.webp</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3513,7 +3501,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3535,20 +3523,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ INTEL CORE I7 12700KF 5.0 GHz/B760M/DDR4 32GB (16X2) 3200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
+          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT LIGHT OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>47400</v>
+        <v>46000</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhiivzUbT</t>
+          <t>https://s.shopee.co.th/4qDrXL3L0A</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mp11k4bg9bt924.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlnatrpoxouad3.webp</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3558,7 +3546,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3580,20 +3568,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ AMD RYZEN 5 7500F 5.0 GHz/A620M/DDR5 32GB (16X2) 5200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
+          <t>GIGABYTE RTX5070 EAGLE OC ICE SFF 12GB GDDR7</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>52000</v>
+        <v>34900</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlS811OcO</t>
+          <t>https://s.shopee.co.th/4fuRL23yL9</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mpaacvrbqh36c5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8frvyv07ej3f1.webp</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3603,7 +3591,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3625,20 +3613,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ INTEL CORE I7 12700 4.9 GHz/B660M/DDR4 32GB (16X2) 3200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
+          <t>ASUS DUAL RTX5070 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>52700</v>
+        <v>35500</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4sKK0lHR</t>
+          <t>https://s.shopee.co.th/3B5dYH9gNs</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mq8m96d4luyz2c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mk0r90rueww2f6.webp</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3648,7 +3636,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3670,20 +3658,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ INTEL I7 14700K 5.6 GHz/B760M /DDR4 32GB (16X2) BUS 3200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
+          <t>ASUS PRIME RTX5070 OC 12GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>62500</v>
+        <v>38600</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18bjP2fIM</t>
+          <t>https://s.shopee.co.th/30mDLyAJir</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mpdp2grbr4su76.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3a2dz58n4028.webp</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3693,7 +3681,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3715,20 +3703,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ INTEL I7 14700F 5.4 GHz/B760M WIFI/DDR5 32GB (16X2) BUS 6000/M.2 1TB/850W/เลือกเคสได้ RTX 5070</t>
+          <t>MSI VENTUS 3X RTX5070 12GB OC GDDR7</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>62900</v>
+        <v>41000</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BS1vi21xP</t>
+          <t>https://s.shopee.co.th/2qSn9fAx3q</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mkkgsvb7j4ee42.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mj41n0bwbe2qfb.webp</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3738,7 +3726,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3760,20 +3748,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ AMD Ryzen 7 5800X 4.7 GHz/B550/DDR4 32GB (16X2) 3200/M.2 512GB/750W/เลือกเคสได้ RTX 5070</t>
+          <t>ZOTAC RTX5070 AMP WHITE 12GB GDDR7</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>54800</v>
+        <v>35800</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2LWWVgtmYq</t>
+          <t>https://s.shopee.co.th/2g9MxMBaOp</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mpvht7ozql1pdf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml3ci5g59l3998.webp</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3783,7 +3771,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3805,20 +3793,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ INTEL CORE I5 14500 5.0 GHz/B760M/DDR4 32GB (16X2) 3200/M.2 1TB/750W/เลือกเคสได้ RTX 5070</t>
+          <t>GIGABYTE RTX5070 AORUS MASTER 12GB GDDR7</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>48400</v>
+        <v>40800</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2Vpwhzt9Dt</t>
+          <t>https://s.shopee.co.th/3qLKLV7924</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mp0mdj79btoi6a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m8u12jihcu0e4a.webp</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3828,7 +3816,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3850,20 +3838,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ชุดคอมประกอบ INTEL CORE I5 13500 4.8 GHz/B760M/DDR4 32GB (16X2) 3200/M.2 1TB/750W/เลือกเคสได้ RTX 5070</t>
+          <t>INNO3D RTX5070 TWIN X2 OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>47000</v>
+        <v>37500</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20tg74v3Eo</t>
+          <t>https://s.shopee.co.th/3g1u9C7mN3</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mp0jaoe0uznk6b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fqk2rbkneka7.webp</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3873,7 +3861,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3895,20 +3883,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BOSSPC / INTEL CORE ULTRA 5 225F / 32GB DDR5 BUS6000 RGB / RTX 5070 12GB / M.2 1TB</t>
+          <t>INNO3D RTX5070 TWIN X2 12GB GDDR7 BLACK</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>77500</v>
+        <v>32500</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD6JNuPtr</t>
+          <t>https://s.shopee.co.th/3ViTwt8Pi2</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mnnrlzy11m9v63.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t4k8v92src0c.webp</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3918,7 +3906,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>BOSSPC</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -3940,20 +3928,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TwithIT การ์ดจอ VGA Graphic Card GPU GTX 1060/1050Ti/1650 RTX 3050/3060/4060/5060/5060Ti/5070</t>
+          <t>ASUS TUF RTX5070 GAMING OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3500</v>
+        <v>38600</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGpiSwJum</t>
+          <t>https://s.shopee.co.th/3LP3ka9331</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mpzcowidfwnf22.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3amujwk64if2.webp</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3963,11 +3951,8 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>TwithTech</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -3988,20 +3973,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VGA ZOTAC GEFORCE RTX 5070 GAMING TWIN EDGE OC - 12GB GDDR7 มือสอง</t>
+          <t>GIGABYTE RTX5070 WINDFORCE SFF OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>24600</v>
+        <v>35500</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxPW9wxFn</t>
+          <t>https://s.shopee.co.th/70IM7Jv5bk</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mq00fruhkkxs6b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8frlxq4oo3224.webp</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4011,7 +3996,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>M&amp;N Computer</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -4033,20 +4018,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Geforce RTX 5070 OC 12GB GDDR7 Snow Fox DLSS 4 Esports Design Live AI กราฟิกการ์ดสําหรับเล่นเกมอิสระ</t>
+          <t>MSI RTX5070 VENTUS 2X OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>90500</v>
+        <v>29500</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AMqeFTlhI</t>
+          <t>https://s.shopee.co.th/7AbmJcuSGn</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7renx-m8d3bdfuxnswe8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8u1lrmsiteo80.webp</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4056,7 +4041,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>PC Accessories Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -4078,20 +4063,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>คอมประกอบครบชุด SPCOMZING RYZEN5 5600 / M.2 500GB / RTX 5070 12GB / B550M / 32GB DDR4 / จอ 24นิ้ว</t>
+          <t>GIGABYTE RTX5070 GAMING OC 12GB GDDR7</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>26700</v>
+        <v>36500</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/903QRwUP2H</t>
+          <t>https://s.shopee.co.th/6ffVihwMHi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mp20d8fdwykh66.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8fr2ccuzg5855.webp</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4101,7 +4086,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>SPCOMZING</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -4123,20 +4108,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT VOID OC 12GB GDDR7</t>
+          <t>MSI RTX5070 GAMING TRIO 12GB GDDR7</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>46000</v>
+        <v>43600</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pk0FdV2NG</t>
+          <t>https://s.shopee.co.th/6pyvv0viwl</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mln8wxv1kao1df.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t79lqa4x7caf.webp</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4168,20 +4153,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GALAX RTX5070 EX GAMER 12GB GDDR7</t>
+          <t>Predator Helios Neo 18 AI PHN18-72-945W  U9-275HX 32G 1TB RTX 5070 Ti 12GB W11</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>35000</v>
+        <v>91900</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fQa3KVfiF</t>
+          <t>https://s.shopee.co.th/7fY2uXsYFw</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-ml3do6g159fm84.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0r-md5pk3fk0w9ydf.webp</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4191,8 +4176,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>NOTEBOOK  CORP</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4213,20 +4201,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 AERO OC 12GB GDDR7</t>
+          <t>คอมประกอบเล่นเกม 2K | Ryzen 5 9600X + RTX 5070 | DDR5 32GB / SSD 1TB | ชุดน้ำจอ LCD / Wi-Fi / Bluetooth</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>37900</v>
+        <v>72900</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8V79r1WJ3E</t>
+          <t>https://s.shopee.co.th/7prT6qruuz</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-ml3b0ujyyigw9f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mq8v3mga639d7d.webp</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4236,8 +4224,11 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -4258,20 +4249,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5070 TWIN EDGE 12GB GDDR7</t>
+          <t>คอมประกอบเล่นเกม 2K | Ryzen 5 7500F + RTX 5070 | DDR5 32GB / SSD 1TB | โทนขาว / ชุดน้ำจอ LCD</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>31000</v>
+        <v>69900</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8KnjeiWwOD</t>
+          <t>https://s.shopee.co.th/7KvCVvtovu</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-ma9clcgr2jrn46.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mq8u8uglvua3a6.webp</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4281,8 +4272,11 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -4303,20 +4297,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>INNO3D RTX5070 TWIN X2 OC 12GB WHITE GDDR7</t>
+          <t>คอมประกอบเล่นเกม 2K | Intel Core i5-14400F + RTX 5070 | DDR5 12GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>33600</v>
+        <v>66900</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8AUJSPXZjC</t>
+          <t>https://s.shopee.co.th/7VEciEtBax</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8fpz7z7z3m167.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mq8uwloys1e452.webp</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4326,8 +4320,11 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -4348,20 +4345,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MSI RTX5070 GAMING TRIO OC 12GB GDDR7</t>
+          <t>คอมประกอบเล่นเกม 2K | Ryzen 7 9800X3D + RTX 5070 | RAM 32GB / SSD 1TB | โทนขาว / ชุดแต่ง Lian Li</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>36300</v>
+        <v>99900</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/80AtG6YD4B</t>
+          <t>https://s.shopee.co.th/5fmyWs0AJc</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8fplkpwu26459.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mq8t9m68lrt997.webp</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4371,7 +4368,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -4393,20 +4390,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GALAX RTX5070 1-CLICK 12GB OC GDDR7</t>
+          <t>คอมประกอบ INTEL Core i9-14900K / RTX 5070 12GB | DDR5 32GB 6000MHz | SSD 1TB | ชุดน้ำปิด 3 ตอน | - monkey etc.</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>32800</v>
+        <v>104100</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AUsEEhOgzg</t>
+          <t>https://s.shopee.co.th/5q6OjAzWyf</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m7t43sao8g0oc9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mffzlmr9924ubc.webp</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4416,7 +4413,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -4438,20 +4435,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MSI RTX5070 VANGUARD SOC 12GB GDDR7</t>
+          <t>คอมประกอบเล่นเกม 2K | Intel Core i5-14400F + RTX 5070 | DDR5 32GB / SSD 1TB | เคสเลือกสีได้ / เคสตู้ปลา | รุ่น B</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>42900</v>
+        <v>72900</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKYo2OPKKf</t>
+          <t>https://s.shopee.co.th/5LA88G1Qza</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m7t7pn5x4rli2a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mqbn4gsdyyha53.webp</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4461,8 +4458,11 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -4483,20 +4483,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ASUS PRIME RTX5070 OC 12GB GDDR7</t>
+          <t>คอมประกอบเล่นเกม 2K | Intel Core i5-14400F + RTX 5070 | DDR5 32GB / SSD 1TB | เคสเลือกสีได้ / ชุดน้ำจอ LCD</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>34900</v>
+        <v>74900</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAFNq5Pxfe</t>
+          <t>https://s.shopee.co.th/5VTYKZ0ned</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fw1olmz4kue9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mqblivji9xj594.webp</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4506,8 +4506,11 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -4528,20 +4531,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5070 SOLID GAMING OC 12GB GDDR7</t>
+          <t>คอมประกอบเล่นเกม 2K | Ryzen 5 7500F + RTX 5070 | DDR5 32GB / SSD 1TB | เคสเลือกสีได้ / เคสตู้ปลา</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>32500</v>
+        <v>67100</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9zvxdmQb0d</t>
+          <t>https://s.shopee.co.th/6L2fK5xcxo</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fob1nq1jpl67.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mpxdw3kn0r2jec.webp</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4551,7 +4554,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -4573,20 +4576,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MSI RTX5070 SHADOW 2X OC 12GB GDDR7</t>
+          <t>คอมประกอบเล่นเกม 2K | Intel Core Ultra 7 265KF + RTX 5070 | DDR5 32GB / SSD 1TB | เคสเลือกสีได้ / เคสตู้ปลา</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>29500</v>
+        <v>77900</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9pcXRTRELc</t>
+          <t>https://s.shopee.co.th/6VM5WOwzcr</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8u1tn79jysufe.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mqbnzvh30sn506.webp</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4596,8 +4599,11 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -4618,20 +4624,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>GALAX RTX5070 1-Click OC 12GB GDDR7 WHITE</t>
+          <t>คอมประกอบเล่นเกม 2K | Intel Core i5-14600K + RTX 5070 | DDR5 32GB / SSD 1TB | ชุดน้ำจอ LCD / Wi-Fi / Bluetooth</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>33000</v>
+        <v>74500</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7FARrgb</t>
+          <t>https://s.shopee.co.th/60PovTytdm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8fuipfj90xad4.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mpx9de1uhez010.webp</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4641,8 +4647,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4663,20 +4672,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MSI RTX5070 WORLD OF WARCRAFT MIDNIGHT LIGHT OC 12GB GDDR7</t>
+          <t>COLORFUL VGA GEFORCE RTX 5070 ULTRA W OC - 12GB GDDR7 - A0169636</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>46000</v>
+        <v>30000</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9Uzh2rSV1a</t>
+          <t>https://s.shopee.co.th/6AjF7myGIp</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mlnatrpoxouad3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rash-mai21nkh6t8444.webp</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4686,8 +4695,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="91">
@@ -4708,20 +4720,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 EAGLE OC ICE SFF 12GB GDDR7</t>
+          <t>VGA GIGABYTE GEFORCE RTX 5070 WINDFORCE OC - 12GB GDDR7 (REV. 1.0) - A0167333</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>34900</v>
+        <v>28900</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9KgGqYT8MZ</t>
+          <t>https://s.shopee.co.th/9fJ7IDkwCW</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8frvyv07ej3f1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e5kzgzgage9f.webp</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4731,8 +4743,11 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>172</v>
       </c>
     </row>
     <row r="92">
@@ -4753,20 +4768,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ASUS DUAL RTX5070 OC 12GB GDDR7</t>
+          <t>INNO3D VGA GEFORCE RTX 5070 ICHILL X3 WHITE OC - 12GB GDDR7 - A0182763</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>35500</v>
+        <v>30600</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5TLdv72</t>
+          <t>https://s.shopee.co.th/9pcXUWkIrZ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mk0r90rueww2f6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zti-mpn8ztxa1eype5.webp</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4776,8 +4791,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4798,20 +4816,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ASUS PRIME RTX5070 OC 12GB GDDR7 WHITE</t>
+          <t>GIGABYTE RTX5070/12GB GAMING (OC/D7) - A0167704</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>38600</v>
+        <v>31000</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fH2eYS1</t>
+          <t>https://s.shopee.co.th/9KgGtbmCsU</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3a2dz58n4028.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m7t4s6bzc33q4e.webp</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4821,8 +4839,11 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="94">
@@ -4843,20 +4864,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>MSI VENTUS 3X RTX5070 12GB OC GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5070 WINDFORCE - 12GB GDDR7 (REV. 1.0) - A0168507</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>41000</v>
+        <v>28900</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjF4jfBn0</t>
+          <t>https://s.shopee.co.th/9Uzh5ulZXX</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mj41n0bwbe2qfb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasd-m9shjy3jzhm975.webp</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4866,8 +4887,11 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -4888,20 +4912,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5070 AMP WHITE 12GB GDDR7</t>
+          <t>MSI VGA GEFORCE RTX 5070 SHADOW 2X OC - 12GB GDDR7 - A0167334</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>35800</v>
+        <v>27800</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PosQfp7z</t>
+          <t>https://s.shopee.co.th/AKYo5RiOqi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml3ci5g59l3998.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m8vu18t6nqrz16.webp</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4911,8 +4935,11 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="96">
@@ -4933,20 +4960,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 AORUS MASTER 12GB GDDR7</t>
+          <t>COLORFUL VGA GEFORCE RTX 5070 IGAME ULTRA OC - 12GB GDDR7 - A0182693</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>40800</v>
+        <v>30000</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6Og7gSSy</t>
+          <t>https://s.shopee.co.th/AUsEHkhlVl</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m8u12jihcu0e4a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zti-mpn9epfga8zza7.webp</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4956,8 +4983,11 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4978,20 +5008,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>INNO3D RTX5070 TWIN X2 OC 12GB GDDR7</t>
+          <t>COLORFUL VGA GEFORCE RTX 5070 GAMING - 12GB GDDR7 - A0179155</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>37500</v>
+        <v>29000</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyToh5nx</t>
+          <t>https://s.shopee.co.th/9zvxgpjfWg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m8fqk2rbkneka7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-825zk-mkf6jmm2g8ara0.webp</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5001,7 +5031,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -5023,20 +5053,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>INNO3D RTX5070 TWIN X2 12GB GDDR7 BLACK</t>
+          <t>INNO3D VGA GEFORCE RTX 5070 TWIN X2 WHITE OC - 12GB GDDR7 - A0182761</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>32500</v>
+        <v>28200</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYHVhj8w</t>
+          <t>https://s.shopee.co.th/AAFNt8j2Bj</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t4k8v92src0c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mpuki3sjbvny01.webp</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5046,7 +5076,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -5068,20 +5098,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ASUS TUF RTX5070 GAMING OC 12GB GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5070 EAGLE OC - 12GB GDDR7 (REV. 1.0) - A0167332</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>38600</v>
+        <v>30000</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA85CiMTv</t>
+          <t>https://s.shopee.co.th/8Knjhlq0uO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-ml3amujwk64if2.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasb-m9r4ysvtt0lr65.webp</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5091,8 +5121,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="100">
@@ -5113,20 +5146,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 WINDFORCE SFF OC 12GB GDDR7</t>
+          <t>PALIT VGA GEFORCE RTX 5070 INFINITY3 - 12GB GDDR7 - A0169582</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>35500</v>
+        <v>28300</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prT3nYqPQ</t>
+          <t>https://s.shopee.co.th/8V79u4pNZR</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8frlxq4oo3224.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasm-mai21lnnzgr4e6.webp</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5136,8 +5169,11 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -5158,20 +5194,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>MSI RTX5070 VENTUS 2X OC 12GB GDDR7</t>
+          <t>VGA ZOTAC GEFORCE RTX 5070 GAMING TWIN EDGE OC - 12GB GDDR7 - A0168935</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>29500</v>
+        <v>27200</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2rUZTkP</t>
+          <t>https://s.shopee.co.th/80AtJ9rHaM</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8u1lrmsiteo80.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9r5llbx6iq743.webp</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5181,8 +5217,11 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="102">
@@ -5203,20 +5242,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5070 GAMING OC 12GB GDDR7</t>
+          <t>MSI VGA GEFORCE RTX 5070 SHADOW 3X OC - 12GB GDDR7 - A0167337</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>36500</v>
+        <v>29300</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcfBa75O</t>
+          <t>https://s.shopee.co.th/8AUJVSqeFP</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m8fr2ccuzg5855.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasb-m9r4yt0tlptda3.webp</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5226,8 +5265,11 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -5248,20 +5290,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MSI RTX5070 GAMING TRIO 12GB GDDR7</t>
+          <t>VGA MSI GEFORCE RTX 5070 VENTUS 2X OC - 12GB GDDR7 - A0167335</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>43600</v>
+        <v>28300</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCSsakQN</t>
+          <t>https://s.shopee.co.th/903QUznTYa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7t79lqa4x7caf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasf-m8fncy4sdmo953.webp</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5271,8 +5313,11 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="104">
@@ -5293,20 +5338,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ MSI SUPRIM GAMING X BLACK EDITION i7-10700 +32GB    + RTX 3070 / VENTUS RTX5070 3X</t>
+          <t>VGA GALAX GEFORCE RTX 5070 EX GAMER OC - 12GB GDDR7 - A0168937</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>27500</v>
+        <v>31000</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmGZbNlM</t>
+          <t>https://s.shopee.co.th/9AMqhImqDd</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7r98y-lyvt0wibg8fd67.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasc-m9e5itp39kyo9d.webp</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5316,8 +5361,11 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="105">
@@ -5338,20 +5386,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5070 SOLID OC</t>
+          <t>GALAX RTX5070/12GB 1-CLICK (OC/D7) - A0167407</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>26800</v>
+        <v>28500</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70IM4Gc16L</t>
+          <t>https://s.shopee.co.th/8fQa6NokEY</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mm1mzdmzk4qo34.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m7gdvr2cf4ts39.webp</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5361,8 +5409,11 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>M.B Computer Store</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="106">
@@ -5383,20 +5434,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5070 Twin Edge OC</t>
+          <t>ASUS VGA GEFORCE RTX 5070 DUAL O12G - 12GB GDDR7 - A0170023</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25600</v>
+        <v>26000</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvrxceRK</t>
+          <t>https://s.shopee.co.th/8pk0Igo6tb</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mm1mwhbo2kg438.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasi-maxvtnp96kj84f.webp</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5406,8 +5457,11 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>M.B Computer Store</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="107">
@@ -5428,20 +5482,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Nextcomputer CORE ULTRA 9 285K RAM 32GB I M2 1024GB I RTX5070 หรือ VGA เลือกได้</t>
+          <t>ASUS VGA GEFORCE RTX 5070 PRIME O12G - 12GB GDDR7 - A0167376</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>66900</v>
+        <v>32700</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVfedHmJ</t>
+          <t>https://s.shopee.co.th/1gGplWFORE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mki994u99atha7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m8wtzu5de1qn86.webp</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5451,11 +5505,11 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Nextcomputer</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108">
@@ -5476,20 +5530,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Nextcomputer Hight End I9 14900F I RAM 32G I RTX5070 I POWER 750W</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5070 EAGLE ICE OC - 12GB GDDR7 (REV. 1.0) - A0167331</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>89900</v>
+        <v>30300</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKIRo4Wm</t>
+          <t>https://s.shopee.co.th/1qaFxpEl6H</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mkic1lczkqva5e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasg-m9shjw1h2p8v39.webp</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5499,8 +5553,11 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Nextcomputer</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="109">
@@ -5521,20 +5578,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Nextcomputer RTX5070 l I5 14400f l RAM 32GB I B760M DDR5</t>
+          <t>ZOTAC VGA GEFORCE RTX 5070 GAMING SOLID OC - 12GB GDDR7 - A0167640</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>54900</v>
+        <v>28200</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1u68ohrl</t>
+          <t>https://s.shopee.co.th/1LdzMuGf7C</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasf-m8vbh6rczv2hde.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8wtlnocelov6c.webp</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5544,8 +5601,11 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Nextcomputer</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="110">
@@ -5566,20 +5626,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Asus TUF Gaming A16 (FA608UP-QT024W) Ryzen 7 260/16GB/512GB M.2 SSD/GeForce RTX 5070 8GB/16" WQXGA/Windows 11 Home/Jaege</t>
+          <t>GIGABYTEVGA  GEFORCE RTX 5070 AORUS MASTER - 12GB GDDR7 (REV. 1.0) - A0167329</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>71700</v>
+        <v>34100</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTtppLCk</t>
+          <t>https://s.shopee.co.th/1VxPZDG1mF</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-moryg8c7hh5958.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasd-m9r4ysv9vai63c.webp</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5589,8 +5649,11 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>NOTEBOOK  CORP</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -5611,20 +5674,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Predator Helios Neo 16S AI PHN16S-71-95J9_Abyssal black  U9-275HX 32G 1TB RTX5070 W11 BK (Game Pass) (AI)</t>
+          <t>GALAX VGA GEFORCE RTX 5070 EX GAMER WHITE OC - 12GB GDDR7 - A0168481</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>84000</v>
+        <v>31000</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3hWpyXj</t>
+          <t>https://s.shopee.co.th/2LWWYkCr5Q</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mgvzdc0r48p4eb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-m9r4yuoh6erza8.webp</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5634,8 +5697,11 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>NOTEBOOK  CORP</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -5656,20 +5722,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Asus ROG Strix G16 (G614PP-TS138W) Ryzen 9 8940HX /16GB/1TB M.2 SSD/GeForce RTX 5070 8GB/16"/Windows 11 Home/Eclipse Gr</t>
+          <t>ZOTAC VGA GEFORCE RTX 5070 GAMING TWIN EDGE WHITE OC - 12GB GDDR7 - A0182849</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>86900</v>
+        <v>27400</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5dVDqbsi</t>
+          <t>https://s.shopee.co.th/2Vpwl3CDkT</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mos4vczzwg0cec.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mpn9g7p0j2mj31.webp</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5679,7 +5745,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>NOTEBOOK  CORP</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -5696,25 +5762,25 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ PNY GeForce RTX 5080 16GB ARGB Overclocked Triple Fan DLSS 4 GDDR7</t>
+          <t>INNO3D VGA GEFORCE RTX 5070 TWIN X2 - 12GB GDDR7 - A0183048</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>51900</v>
+        <v>27500</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7913vKx</t>
+          <t>https://s.shopee.co.th/20tgA8E7lO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mo4863r6po1v3b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mpn8y99sq2ob94.webp</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5724,11 +5790,8 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
-      </c>
-      <c r="L113" t="n">
-        <v>1</v>
+          <t>Advice Official Shop</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -5744,25 +5807,25 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>GBT GF RTX 5080 GAMING OC 16G (Rev1.0)	GV-N5080GAMOC-16GD</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5070 GAMING OC 12G - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>57600</v>
+        <v>32200</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjEyaHFRI</t>
+          <t>https://s.shopee.co.th/2BD6MRDUQR</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-mazph6oiow1i7d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbd9lju1nj9243.webp</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5772,8 +5835,11 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Hp_by_iqink</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -5789,25 +5855,25 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING GEFORCE RTX5080 SOLID CORE OC 16GB 256BIT GDDR7(P288-1N765-300Z8)</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5070 1-CLICK OC - 12GB GDDR7</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>56000</v>
+        <v>28800</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PomHHsmH</t>
+          <t>https://s.shopee.co.th/LlSB4KT96</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8a9twwj7iemf8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasf-mannnywv8nxy4d.webp</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5817,11 +5883,11 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -5837,25 +5903,25 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ASUS PRIME GEFORCE RTX5080 OC 16G GDDR7 (90YV0LX0-M0NA00)</t>
+          <t>ZOTAC GAMING GEFORCE RTX5070 TWIN EDGE OC WHITE EDITION 12GB 192BIT GDDR7 (P288-1N764-601Z8)</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>63000</v>
+        <v>28700</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5NCFylO</t>
+          <t>https://s.shopee.co.th/W4sNNJpo9</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m846xz01ff8u95.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zti-mpumvo62uepu7c.webp</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5867,9 +5933,6 @@
         <is>
           <t>TECHNOCOM.OFFICIAL</t>
         </is>
-      </c>
-      <c r="L116" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="117">
@@ -5890,20 +5953,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7</t>
+          <t>VGA การ์ดจอ PNY GeForce RTX 5080 16GB ARGB Overclocked Triple Fan DLSS 4 GDDR7</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>52900</v>
+        <v>51900</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fAtGc6N</t>
+          <t>https://s.shopee.co.th/9fJ7913vKx</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmv7butau96u14.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mo4863r6po1v3b.webp</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5913,8 +5976,11 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -5935,20 +6001,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G GAMING TRIO OC - 16GB GDDR7</t>
+          <t>GBT GF RTX 5080 GAMING OC 16G (Rev1.0)	GV-N5080GAMOC-16GD</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>62600</v>
+        <v>57600</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYBMJmnE</t>
+          <t>https://s.shopee.co.th/6AjEyaHFRI</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-moy490f3fuofce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-mazph6oiow1i7d.webp</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5958,7 +6024,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>Hp_by_iqink</t>
         </is>
       </c>
     </row>
@@ -5980,20 +6046,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7 +  PSU ASUS 1200W ROG THOR 1200P3 80+PLATINUM MIKU</t>
+          <t>ZOTAC GAMING GEFORCE RTX5080 SOLID CORE OC 16GB 256BIT GDDR7(P288-1N765-300Z8)</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>111000</v>
+        <v>56000</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA7z3KQ8D</t>
+          <t>https://s.shopee.co.th/60PomHHsmH</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mmjrx4g2i8zn0b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8a9twwj7iemf8.webp</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6003,8 +6069,11 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>D.P COMPUTER Hi End</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="120">
@@ -6025,20 +6094,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
+          <t>ASUS PRIME GEFORCE RTX5080 OC 16G GDDR7 (90YV0LX0-M0NA00)</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>89900</v>
+        <v>63000</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6OZyIW7K</t>
+          <t>https://s.shopee.co.th/6VM5NCFylO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mpkfshwxt3ij71.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m846xz01ff8u95.webp</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6048,8 +6117,11 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>D.P COMPUTER Hi End</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="121">
@@ -6070,20 +6142,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5080 SOLID CORE OC</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>52200</v>
+        <v>52900</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyNfJ9SJ</t>
+          <t>https://s.shopee.co.th/6L2fAtGc6N</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mm1mtsp7op3402.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmv7butau96u14.webp</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6093,7 +6165,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>M.B Computer Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -6115,20 +6187,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 X3 OC - 16GB GDDR7 - A0182764</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G GAMING TRIO OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>56500</v>
+        <v>62600</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcZ2CAjg</t>
+          <t>https://s.shopee.co.th/5VTYBMJmnE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpukkz1kncp821.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-moy490f3fuofce.webp</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6138,7 +6210,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -6160,20 +6232,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL FROSTBITE OC - 16GB GDDR7 - A0182767</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7 +  PSU ASUS 1200W ROG THOR 1200P3 80+PLATINUM MIKU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>71700</v>
+        <v>111000</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCMjCo4f</t>
+          <t>https://s.shopee.co.th/5LA7z3KQ8D</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mpukedl8v8ch88.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mmjrx4g2i8zn0b.webp</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6183,7 +6255,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>D.P COMPUTER Hi End</t>
         </is>
       </c>
     </row>
@@ -6205,20 +6277,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 WINDFORCE OC SFF 16GB GDDR7</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>52900</v>
+        <v>89900</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prSxeAu3m</t>
+          <t>https://s.shopee.co.th/5q6OZyIW7K</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkd8n452amth61.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mpkfshwxt3ij71.webp</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6228,11 +6300,8 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
-      </c>
-      <c r="L124" t="n">
-        <v>10</v>
+          <t>D.P COMPUTER Hi End</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -6253,20 +6322,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ ZOTAC GAMING GeForce RTX 5080 GAMING SOLID CORE OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5080 SOLID CORE OC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>52400</v>
+        <v>52200</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2lLBXOl</t>
+          <t>https://s.shopee.co.th/5fmyNfJ9SJ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mki0hzdcdlvk9a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mm1mtsp7op3402.webp</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6276,11 +6345,8 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
-      </c>
-      <c r="L125" t="n">
-        <v>4</v>
+          <t>M.B Computer Store</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -6301,20 +6367,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 (PRIME-RTX5080-16G)</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 X3 OC - 16GB GDDR7 - A0182764</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>67600</v>
+        <v>56500</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvloEi5c</t>
+          <t>https://s.shopee.co.th/7VEcZ2CAjg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4j8l8twxuce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpukkz1kncp821.webp</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6324,7 +6390,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6346,20 +6412,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL FROSTBITE OC - 16GB GDDR7 - A0182767</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>55900</v>
+        <v>71700</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVZVFLQb</t>
+          <t>https://s.shopee.co.th/7KvCMjCo4f</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mmv7325j5mgxbb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mpukedl8v8ch88.webp</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6369,7 +6435,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6391,20 +6457,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 WINDFORCE OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>113000</v>
+        <v>52900</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmAQDRPi</t>
+          <t>https://s.shopee.co.th/7prSxeAu3m</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mjxxy5kvxjied7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkd8n452amth61.webp</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6414,8 +6480,11 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="129">
@@ -6436,20 +6505,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 EX GAMER 16GB GDDR7</t>
+          <t>VGA การ์ดจอ ZOTAC GAMING GeForce RTX 5080 GAMING SOLID CORE OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>71900</v>
+        <v>52400</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70ILy7E4kh</t>
+          <t>https://s.shopee.co.th/7fY2lLBXOl</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mjjcxbr8kqo03d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mki0hzdcdlvk9a.webp</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6459,8 +6528,11 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="130">
@@ -6481,20 +6553,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC - 16GB GDDR7 (N50803-16D7X-17603930)</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 (PRIME-RTX5080-16G)</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>59000</v>
+        <v>67600</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTngROr2</t>
+          <t>https://s.shopee.co.th/6pyvloEi5c</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbdla2gs3l9wca.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4j8l8twxuce.webp</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6504,11 +6576,8 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>1</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -6529,20 +6598,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MSI VGA GEFORCE RTX 5080 SHADOW 3X OC - 16GB GDDR7 - A0167047</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>58000</v>
+        <v>55900</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3bNS2C1</t>
+          <t>https://s.shopee.co.th/6ffVZVFLQb</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rask-m9r5cxk7f42o1c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mmv7325j5mgxbb.webp</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6552,7 +6621,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -6574,20 +6643,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 XTREME WATERFORCE - 16GB GDDR7 (REV. 1.0) - A0166365</t>
+          <t>ASUS ROG ASTRAL RTX5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>74200</v>
+        <v>113000</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKCIQ8B8</t>
+          <t>https://s.shopee.co.th/7AbmAQDRPi</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-mai21hqfq6icd6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mjxxy5kvxjied7.webp</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6597,7 +6666,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6619,20 +6688,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 AORUS MASTER 16GB GDDR7</t>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>60700</v>
+        <v>71900</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1tzzQlW7</t>
+          <t>https://s.shopee.co.th/70ILy7E4kh</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mky5qpeaknwi66.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mjjcxbr8kqo03d.webp</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6642,7 +6711,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6664,20 +6733,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC - 16GB GDDR7 (N50803-16D7X-17603930)</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>9000</v>
+        <v>59000</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSn0STwCy</t>
+          <t>https://s.shopee.co.th/3ViTngROr2</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbdla2gs3l9wca.webp</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6687,7 +6756,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -6712,20 +6781,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7</t>
+          <t>MSI VGA GEFORCE RTX 5080 SHADOW 3X OC - 16GB GDDR7 - A0167047</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>67900</v>
+        <v>58000</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9Mo9UZXx</t>
+          <t>https://s.shopee.co.th/3LP3bNS2C1</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4xoa7sr9r50.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rask-m9r5cxk7f42o1c.webp</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6735,7 +6804,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6757,20 +6826,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC WHITE - 16GB GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 XTREME WATERFORCE - 16GB GDDR7 (REV. 1.0) - A0166365</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>55900</v>
+        <v>74200</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5dP4SfX4</t>
+          <t>https://s.shopee.co.th/3qLKCIQ8B8</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mqbi0037km4r5f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-mai21hqfq6icd6.webp</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6780,7 +6849,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6802,20 +6871,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 HOF GAMING BLACK EDITION 16GB GDDR7</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 AORUS MASTER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>87000</v>
+        <v>60700</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30mDClTIs3</t>
+          <t>https://s.shopee.co.th/3g1tzzQlW7</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mi2smox3b8qo49.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mky5qpeaknwi66.webp</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6825,7 +6894,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -6847,20 +6916,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7</t>
+          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>69500</v>
+        <v>9000</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDrO8MK9Q</t>
+          <t>https://s.shopee.co.th/2qSn0STwCy</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9pqc1bk39ipd8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6870,8 +6939,11 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>EZGGTECH</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -6892,20 +6964,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G VENTUS 3X OC - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>64100</v>
+        <v>67900</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuRBpMxUP</t>
+          <t>https://s.shopee.co.th/2g9Mo9UZXx</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmjx8u2c385h1b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4xoa7sr9r50.webp</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6915,7 +6987,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -6937,20 +7009,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 AERO OC - 16GB GDDR7 (REV. 1.0) - A0166362</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC WHITE - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>66200</v>
+        <v>55900</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqhmkL3TW</t>
+          <t>https://s.shopee.co.th/3B5dP4SfX4</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m9r5fxjheinlbf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mqbi0037km4r5f.webp</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6960,11 +7032,8 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>3</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -6985,20 +7054,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VGA GIGABYTE GEFORCE RTX 5080 AORUS MASTER - 16GB GDDR7 (REV. 1.0) - A0166364</t>
+          <t>GALAX RTX5080 HOF GAMING BLACK EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>70500</v>
+        <v>87000</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XHaRLgoV</t>
+          <t>https://s.shopee.co.th/30mDClTIs3</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e59iq7j2a769.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mi2smox3b8qo49.webp</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7008,7 +7077,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7030,20 +7099,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 WHITE OC EDITION</t>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>79900</v>
+        <v>69500</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4AyAauOrVM</t>
+          <t>https://s.shopee.co.th/4qDrO8MK9Q</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlljzbvrqccib8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9pqc1bk39ipd8.webp</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7053,7 +7122,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7075,20 +7144,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(มีโค้ดลด2000฿) RTX 5060 5060Ti 5060 ti 2060Super 3060 3060Ti 3070 3070Ti 4060 4060Ti 4070 4070Ti 4080 4090 5080 5090</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G VENTUS 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5000</v>
+        <v>64100</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40ekObPUqL</t>
+          <t>https://s.shopee.co.th/4fuRBpMxUP</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmjx8u2c385h1b.webp</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7098,11 +7167,8 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
-        <v>23</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -7123,20 +7189,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 AERO OC - 16GB GDDR7 (REV. 1.0) - A0166362</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>21400</v>
+        <v>66200</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vb0zWNapS</t>
+          <t>https://s.shopee.co.th/5AqhmkL3TW</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m9r5fxjheinlbf.webp</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7146,8 +7212,11 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>3CCamera.th</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -7168,20 +7237,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Intel Core Ultra 9 285K + RTX 5080 | DDR5 64GB 6400MHz / SSD 2TB | โทนขาว / ชุดแต่ง Lian Li</t>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 AORUS MASTER - 16GB GDDR7 (REV. 1.0) - A0166364</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>155700</v>
+        <v>70500</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHanDOEAR</t>
+          <t>https://s.shopee.co.th/50XHaRLgoV</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfkgr2oabvux4c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e59iq7j2a769.webp</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7191,7 +7260,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -7213,20 +7282,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 AORUS XTREME WATERFORECE 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 WHITE OC EDITION</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>89500</v>
+        <v>79900</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhicmbYGm</t>
+          <t>https://s.shopee.co.th/4AyAauOrVM</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prhvzpau3yd2.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlljzbvrqccib8.webp</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7236,7 +7305,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7327,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7 WHITE</t>
+          <t>(มีโค้ดลด2000฿) RTX 5060 5060Ti 5060 ti 2060Super 3060 3060Ti 3070 3070Ti 4060 4060Ti 4070 4070Ti 4080 4090 5080 5090</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>66900</v>
+        <v>5000</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gOIQTcBbl</t>
+          <t>https://s.shopee.co.th/40ekObPUqL</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9pqq1xfnr3i22.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7281,8 +7350,11 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>EZGGTECH</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="148">
@@ -7303,20 +7375,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>75300</v>
+        <v>21400</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKZ1OaHas</t>
+          <t>https://s.shopee.co.th/4Vb0zWNapS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mmwzh1437egx8f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7326,7 +7398,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>3CCamera.th</t>
         </is>
       </c>
     </row>
@@ -7348,20 +7420,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MSI VGA GEFORCE RTX 5080 VENTUS 3X OC - 16GB GDDR7 - A0167046</t>
+          <t>คอมประกอบพรีเมียม / 4K | Intel Core Ultra 9 285K + RTX 5080 | DDR5 64GB 6400MHz / SSD 2TB | โทนขาว / ชุดแต่ง Lian Li</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>60500</v>
+        <v>155700</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1118p5auvr</t>
+          <t>https://s.shopee.co.th/4LHanDOEAR</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasf-m9r4yrpdj75afe.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfkgr2oabvux4c.webp</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7371,7 +7443,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -7393,20 +7465,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VGA GIGABYTE GEFORCE RTX 5080 GAMING OC - 16GB GDDR7 (REV. 1.0) - A0166361</t>
+          <t>GIGABYTE RTX5080 AORUS XTREME WATERFORECE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>65500</v>
+        <v>89500</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BS1pYe5ci</t>
+          <t>https://s.shopee.co.th/qhicmbYGm</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9e55v65yvbda7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prhvzpau3yd2.webp</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7416,7 +7488,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7438,20 +7510,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 ICHILL X3 V2 - 16GB GDDR7 C50803-16D7X-176069R</t>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>64900</v>
+        <v>66900</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18bdFeixh</t>
+          <t>https://s.shopee.co.th/gOIQTcBbl</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-modebjzln30gb5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9pqq1xfnr3i22.webp</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7461,7 +7533,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7483,20 +7555,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | RAM 64GB 6400MHz / SSD 2TB | โทนขาว / HYTE Y70 Touch</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>145900</v>
+        <v>75300</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4sEAcowo</t>
+          <t>https://s.shopee.co.th/1BKZ1OaHas</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq8r6vopg3rg36.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mmwzh1437egx8f.webp</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7506,7 +7578,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -7528,20 +7600,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ROG Zephyrus G18 G815LW-S9112W Asus U9-275HX32 G 1TB RTX5080 W11 3YOSS</t>
+          <t>MSI VGA GEFORCE RTX 5080 VENTUS 3X OC - 16GB GDDR7 - A0167046</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>125000</v>
+        <v>60500</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlS1rdSHn</t>
+          <t>https://s.shopee.co.th/1118p5auvr</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-me5o4gxp31mrb5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasf-m9r4yrpdj75afe.webp</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7551,7 +7623,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>NOTEBOOK  CORP</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -7573,20 +7645,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 GAMING OC - 16GB GDDR7 (REV. 1.0) - A0166361</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>130900</v>
+        <v>65500</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD6DEWTZA</t>
+          <t>https://s.shopee.co.th/BS1pYe5ci</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq90ma8arc3x60.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9e55v65yvbda7.webp</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7596,7 +7668,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -7618,20 +7690,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>MSI RTX5080 SHADOW 3X OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 ICHILL X3 V2 - 16GB GDDR7 C50803-16D7X-176069R</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>67800</v>
+        <v>64900</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20tg0vX6u9</t>
+          <t>https://s.shopee.co.th/18bdFeixh</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9prwjnh3cy749.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-modebjzln30gb5.webp</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7641,7 +7713,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -7663,20 +7735,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 WINFOREC OC SFF 16GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | RAM 64GB 6400MHz / SSD 2TB | โทนขาว / HYTE Y70 Touch</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>68500</v>
+        <v>145900</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2VpwbqVCtG</t>
+          <t>https://s.shopee.co.th/W4sEAcowo</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prnu5bv9wxb3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq8r6vopg3rg36.webp</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7686,7 +7758,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -7708,20 +7780,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 MASTER 16G - 16GB GDDR7 (GV-N5080AORUS M-16GD)</t>
+          <t>ROG Zephyrus G18 G815LW-S9112W Asus U9-275HX32 G 1TB RTX5080 W11 3YOSS</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>67900</v>
+        <v>125000</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2LWWPXVqEF</t>
+          <t>https://s.shopee.co.th/LlS1rdSHn</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbbxwlx4z7uc43.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-me5o4gxp31mrb5.webp</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7731,7 +7803,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -7753,20 +7825,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>GALAX VGA GEFORCE RTX 5080 HOF GAMING BLACK - 16GB GDDR7 - A0172861</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>68400</v>
+        <v>130900</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxPQ0Z0v6</t>
+          <t>https://s.shopee.co.th/2BD6DEWTZA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134275-824je-me9vcwg1o3cw45.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq90ma8arc3x60.webp</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7776,7 +7848,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -7798,20 +7870,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO OC - 16GB GDDR7 - A0180200</t>
+          <t>MSI RTX5080 SHADOW 3X OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>55500</v>
+        <v>67800</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LdzDhZeG5</t>
+          <t>https://s.shopee.co.th/20tg0vX6u9</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134275-82609-mmd4ly6nd341a5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9prwjnh3cy749.webp</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7821,7 +7893,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7843,20 +7915,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 XTREME WATERFORCE 16G - 16GB GDDR7 (GV-N5080AORUSX W-16GD)</t>
+          <t>GIGABYTE RTX5080 WINFOREC OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>73800</v>
+        <v>68500</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaFocXkFC</t>
+          <t>https://s.shopee.co.th/2VpwbqVCtG</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mbbxc0wleh6p7b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prnu5bv9wxb3.webp</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7866,7 +7938,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7888,20 +7960,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 16GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 MASTER 16G - 16GB GDDR7 (GV-N5080AORUS M-16GD)</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>130900</v>
+        <v>67900</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGpcJYNaB</t>
+          <t>https://s.shopee.co.th/2LWWPXVqEF</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mq8stcq5cx6of7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbbxwlx4z7uc43.webp</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7911,7 +7983,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -7933,20 +8005,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>MSI STEALTH A16 AI PLUS Ryzen AI 9 HX 370/RTX 5080 RAM64/2TB - ID26060441</t>
+          <t>GALAX VGA GEFORCE RTX 5080 HOF GAMING BLACK - 16GB GDDR7 - A0172861</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>113400</v>
+        <v>68400</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fQZxB7jNY</t>
+          <t>https://s.shopee.co.th/1VxPQ0Z0v6</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpuc7ehxc9ho8a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-824je-me9vcwg1o3cw45.webp</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7956,7 +8028,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>10X Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -7978,20 +8050,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Original 380W 20V 19A อะแดปเตอร์ชาร์จสําหรับ ASUS ROG Strix scar 16 2025 G635LW RTX5080 ADP-380AB B</t>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO OC - 16GB GDDR7 - A0180200</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6400</v>
+        <v>55500</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pk09U762b</t>
+          <t>https://s.shopee.co.th/1LdzDhZeG5</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824jc-mep4jcmcgnphd5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-82609-mmd4ly6nd341a5.webp</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8001,11 +8073,8 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>junyue999.th</t>
-        </is>
-      </c>
-      <c r="L163" t="n">
-        <v>3</v>
+          <t>Advice Official Shop</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -8026,20 +8095,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 AORUS MASTER ICE 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 XTREME WATERFORCE 16G - 16GB GDDR7 (GV-N5080AORUSX W-16GD)</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>82500</v>
+        <v>73800</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/903QLn6She</t>
+          <t>https://s.shopee.co.th/1qaFocXkFC</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-map4vxrow1ao8a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mbbxc0wleh6p7b.webp</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8049,11 +8118,8 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L164" t="n">
-        <v>1</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -8074,20 +8140,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>INNO3D RTX5080 X3 OC 16GB BLACK GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 16GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>66900</v>
+        <v>130900</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AMqY65pMh</t>
+          <t>https://s.shopee.co.th/1gGpcJYNaB</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8d39ntj3z7289.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mq8stcq5cx6of7.webp</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8097,7 +8163,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -8119,20 +8185,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC WHITE - 16GB GDDR7 (N50803-16D7X-17605211)</t>
+          <t>MSI STEALTH A16 AI PLUS Ryzen AI 9 HX 370/RTX 5080 RAM64/2TB - ID26060441</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>59000</v>
+        <v>113400</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/80At9xAGjU</t>
+          <t>https://s.shopee.co.th/8fQZxB7jNY</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbdmsesr8qk199.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpuc7ehxc9ho8a.webp</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8142,7 +8208,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>10X Store</t>
         </is>
       </c>
     </row>
@@ -8164,20 +8230,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL X3 V2 OC - 16GB GDDR7 - A0182766</t>
+          <t>Original 380W 20V 19A อะแดปเตอร์ชาร์จสําหรับ ASUS ROG Strix scar 16 2025 G635LW RTX5080 ADP-380AB B</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>61800</v>
+        <v>6400</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8AUJMG9dOX</t>
+          <t>https://s.shopee.co.th/8pk09U762b</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mpujxufur8y4aa.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824jc-mep4jcmcgnphd5.webp</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8187,8 +8253,11 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>junyue999.th</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -8209,20 +8278,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7 - A0166369</t>
+          <t>GIGABYTE RTX5080 AORUS MASTER ICE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>55500</v>
+        <v>82500</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8KnjYZ903a</t>
+          <t>https://s.shopee.co.th/903QLn6She</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0k-mc7mmx5y9omf72.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-map4vxrow1ao8a.webp</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8232,11 +8301,11 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -8257,20 +8326,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+          <t>INNO3D RTX5080 X3 OC 16GB BLACK GDDR7</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>78500</v>
+        <v>66900</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8V79ks8Mid</t>
+          <t>https://s.shopee.co.th/9AMqY65pMh</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-me6x1j4ufmyqba.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8d39ntj3z7289.webp</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8280,11 +8349,8 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L169" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -8305,20 +8371,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 WINDFORCE OC - 16GB GDDR7 (REV. 1.0) - A0166360</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC WHITE - 16GB GDDR7 (N50803-16D7X-17605211)</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>60300</v>
+        <v>59000</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9zvxXd2efw</t>
+          <t>https://s.shopee.co.th/80At9xAGjU</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7ras8-m9r4yq4hudlb71.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbdmsesr8qk199.webp</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8328,11 +8394,8 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L170" t="n">
-        <v>2</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -8353,20 +8416,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 EX GAMER 16GB GDDR7 WHITE</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL X3 V2 OC - 16GB GDDR7 - A0182766</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>69200</v>
+        <v>61800</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAFNjw21Kz</t>
+          <t>https://s.shopee.co.th/8AUJMG9dOX</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9pqwzx9tkvi06.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mpujxufur8y4aa.webp</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8376,7 +8439,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -8398,20 +8461,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>GIGABYTE GAMING RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7 - A0166369</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>75900</v>
+        <v>55500</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKYnwF1O02</t>
+          <t>https://s.shopee.co.th/8KnjYZ903a</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5zvhd595sc69a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0k-mc7mmx5y9omf72.webp</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8421,8 +8484,11 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -8443,20 +8509,20 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 WINDFORCE OC SFF 16G - 16GB GDDR7 (GV-N5080WF3OC-16GD)</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>58800</v>
+        <v>78500</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AUsE8Y0kf5</t>
+          <t>https://s.shopee.co.th/8V79ks8Mid</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbc1uyc222bab6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-me6x1j4ufmyqba.webp</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8468,6 +8534,9 @@
         <is>
           <t>JIB Official Store</t>
         </is>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -8488,20 +8557,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] MSI GAMING TRIO RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 WINDFORCE OC - 16GB GDDR7 (REV. 1.0) - A0166360</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>72900</v>
+        <v>60300</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9KgGkP5C1s</t>
+          <t>https://s.shopee.co.th/9zvxXd2efw</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m5qng58cco0t25.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7ras8-m9r4yq4hudlb71.webp</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8511,11 +8580,11 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -8536,20 +8605,20 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>RTX5080/16GB GALAX 1-CLICK (OC/D7) - A0166352</t>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>59600</v>
+        <v>69200</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9Uzgwi4Ygv</t>
+          <t>https://s.shopee.co.th/AAFNjw21Kz</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m81gt7mb1w4u18.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9pqwzx9tkvi06.webp</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8559,11 +8628,8 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L175" t="n">
-        <v>11</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -8584,20 +8650,20 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 HOF GAMING BLACK EDITION - 16GB GDDR7</t>
+          <t>GIGABYTE GAMING RTX5080 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>70600</v>
+        <v>75900</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7913vLy</t>
+          <t>https://s.shopee.co.th/AKYnwF1O02</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdpq3ctyx2ta3e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5zvhd595sc69a.webp</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8607,7 +8673,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -8629,20 +8695,20 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5080 OC WHITE 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 WINDFORCE OC SFF 16G - 16GB GDDR7 (GV-N5080WF3OC-16GD)</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>89500</v>
+        <v>58800</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9pcXLK3I11</t>
+          <t>https://s.shopee.co.th/AUsE8Y0kf5</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-misduj582yo30b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbc1uyc222bab6.webp</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8652,7 +8718,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -8674,20 +8740,20 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5080 SOLID GAMING OC 16GB GDDR7 WHITE</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] MSI GAMING TRIO RTX5080 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>64900</v>
+        <v>72900</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PomHHsnI</t>
+          <t>https://s.shopee.co.th/9KgGkP5C1s</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-mapdn0hs6q9gfb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m5qng58cco0t25.webp</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8699,6 +8765,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -8719,20 +8788,20 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 HOF GAMING 16GB GDDR7</t>
+          <t>RTX5080/16GB GALAX 1-CLICK (OC/D7) - A0166352</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>87000</v>
+        <v>59600</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjEyaHFSL</t>
+          <t>https://s.shopee.co.th/9Uzgwi4Ygv</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mi2scd35wirsed.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m81gt7mb1w4u18.webp</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8742,8 +8811,11 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="180">
@@ -8764,20 +8836,20 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>GIGABYTE AERO RTX5080 16GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 HOF GAMING BLACK EDITION - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>78500</v>
+        <v>70600</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fAtGc7O</t>
+          <t>https://s.shopee.co.th/9fJ7913vLy</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mki1wyjsh14yd6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdpq3ctyx2ta3e.webp</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8787,11 +8859,8 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L180" t="n">
-        <v>1</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -8812,20 +8881,20 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5080 SOLID CORE OC 16GB GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5080 OC WHITE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>62500</v>
+        <v>89500</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5NCFymR</t>
+          <t>https://s.shopee.co.th/9pcXLK3I11</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mloguv0dy97323.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-misduj582yo30b.webp</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8857,20 +8926,20 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5080 SOLID CORE OC - 16GB GDDR7 (ZT-B50800J2-10P)</t>
+          <t>ZOTAC RTX5080 SOLID GAMING OC 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>59000</v>
+        <v>64900</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA7z3KQ9E</t>
+          <t>https://s.shopee.co.th/60PomHHsnI</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbvy43nc50gsdd.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-mapdn0hs6q9gfb.webp</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8880,7 +8949,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -8902,20 +8971,20 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ASUS TUF RTX5080 GAMING OC 16GB GDDR7</t>
+          <t>GALAX RTX5080 HOF GAMING 16GB GDDR7</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>81000</v>
+        <v>87000</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYBMJmoH</t>
+          <t>https://s.shopee.co.th/6AjEyaHFSL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m9pk6xb8lmjk47.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mi2scd35wirsed.webp</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8947,20 +9016,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>INNO3D RTX5080 X3 OC WHITE 16GB GDDR7</t>
+          <t>GIGABYTE AERO RTX5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>68300</v>
+        <v>78500</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyNfJ9TK</t>
+          <t>https://s.shopee.co.th/6L2fAtGc7O</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8d2yz7814ax90.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mki1wyjsh14yd6.webp</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8972,6 +9041,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -8992,20 +9064,20 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7 (GV-N5080AERO OC-16GD)</t>
+          <t>ZOTAC GAMING RTX5080 SOLID CORE OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>67000</v>
+        <v>62500</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6OZyIW8N</t>
+          <t>https://s.shopee.co.th/6VM5NCFymR</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbbyjj2rglflce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mloguv0dy97323.webp</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9015,7 +9087,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9037,20 +9109,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE AORUS RTX5080 MASTER 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5080 SOLID CORE OC - 16GB GDDR7 (ZT-B50800J2-10P)</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>80900</v>
+        <v>59000</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCMjCo5g</t>
+          <t>https://s.shopee.co.th/5LA7z3KQ9E</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml4sii5ubnym20.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbvy43nc50gsdd.webp</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9060,11 +9132,8 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L186" t="n">
-        <v>1</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -9085,20 +9154,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5080 16GB OC GDDR7 BLACK</t>
+          <t>ASUS TUF RTX5080 GAMING OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>85500</v>
+        <v>81000</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcZ2CAkj</t>
+          <t>https://s.shopee.co.th/5VTYBMJmoH</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq632jnzevwuf9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m9pk6xb8lmjk47.webp</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9130,20 +9199,20 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>INNO3D RTX5080 X3 OC WHITE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>88500</v>
+        <v>68300</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2lLBXPm</t>
+          <t>https://s.shopee.co.th/5fmyNfJ9TK</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5p939h7ybw69b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8d2yz7814ax90.webp</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9155,9 +9224,6 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L188" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -9178,20 +9244,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>MSI RTX5080 VENTUS X3 OC PLUS 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7 (GV-N5080AERO OC-16GD)</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>63000</v>
+        <v>67000</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prSxeAu4p</t>
+          <t>https://s.shopee.co.th/5q6OZyIW8N</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mnkzq2y21x51b3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbbyjj2rglflce.webp</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9201,7 +9267,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -9223,20 +9289,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ASUS PRIME RTX5080 OC 16GB GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE AORUS RTX5080 MASTER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>74300</v>
+        <v>80900</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVZVFLRc</t>
+          <t>https://s.shopee.co.th/7KvCMjCo5g</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9pl3a6dymlq34.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml4sii5ubnym20.webp</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9248,6 +9314,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -9268,20 +9337,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G SHADOW 3X OC - 16GB GDDR7</t>
+          <t>ROG ASTRAL RTX5080 16GB OC GDDR7 BLACK</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>60500</v>
+        <v>85500</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvloEi6f</t>
+          <t>https://s.shopee.co.th/7VEcZ2CAkj</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m807f87tz7xq68.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq632jnzevwuf9.webp</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9291,11 +9360,8 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L191" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -9316,20 +9382,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 GAMING OC 16G - 16GB GDDR7 (GV-N5080GAMING OC-16GD)</t>
+          <t>ROG ASTRAL RTX5080 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>63500</v>
+        <v>88500</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70ILy7E4li</t>
+          <t>https://s.shopee.co.th/7fY2lLBXPm</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0o-mbbz0v0mfsdt28.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5p939h7ybw69b.webp</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9339,8 +9405,11 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -9361,20 +9430,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC - 16GB GDDR7</t>
+          <t>MSI RTX5080 VENTUS X3 OC PLUS 16GB GDDR7</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>61400</v>
+        <v>63000</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmAQDRQl</t>
+          <t>https://s.shopee.co.th/7prSxeAu4p</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0g-mb65w0t41ai927.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mnkzq2y21x51b3.webp</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9384,7 +9453,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9406,20 +9475,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5080 16GB GDDR7 OC EDITION (TUF-RTX5080-O16G-GAMING)</t>
+          <t>ASUS PRIME RTX5080 OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>71700</v>
+        <v>74300</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3bNS2D2</t>
+          <t>https://s.shopee.co.th/6ffVZVFLRc</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mb7lu03gdf7ace.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9pl3a6dymlq34.webp</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9429,7 +9498,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9451,20 +9520,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G SHADOW 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>63900</v>
+        <v>60500</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTngROs5</t>
+          <t>https://s.shopee.co.th/6pyvloEi6f</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9qqhz75s2cu0e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m807f87tz7xq68.webp</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9499,20 +9568,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ HYTE Y40 RTX5080 BLACK/WHITE</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 GAMING OC 16G - 16GB GDDR7 (GV-N5080GAMING OC-16GD)</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>155900</v>
+        <v>63500</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1tzzQlX8</t>
+          <t>https://s.shopee.co.th/70ILy7E4li</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m5v66xgrzeuv7b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0o-mbbz0v0mfsdt28.webp</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9522,7 +9591,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -9544,20 +9613,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ HTYE Y60 RTX5080 OC GDDR7 BLACK</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>159000</v>
+        <v>61400</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKCIQ8CB</t>
+          <t>https://s.shopee.co.th/7AbmAQDRQl</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m63p4ze31cil46.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0g-mb65w0t41ai927.webp</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9567,7 +9636,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -9584,25 +9653,25 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5080 16GB GDDR7 OC EDITION (TUF-RTX5080-O16G-GAMING)</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>169700</v>
+        <v>71700</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
+          <t>https://s.shopee.co.th/3LP3bNS2D2</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mb7lu03gdf7ace.webp</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9614,9 +9683,6 @@
         <is>
           <t>JIB Official Store</t>
         </is>
-      </c>
-      <c r="L198" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -9632,25 +9698,25 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>301100</v>
+        <v>63900</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
+          <t>https://s.shopee.co.th/3ViTngROs5</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9qqhz75s2cu0e.webp</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9660,8 +9726,11 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -9677,25 +9746,25 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>คอมพิวเตอร์ประกอบ HYTE Y40 RTX5080 BLACK/WHITE</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>236900</v>
+        <v>155900</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaAsBag8T</t>
+          <t>https://s.shopee.co.th/3g1tzzQlX8</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m5v66xgrzeuv7b.webp</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9705,7 +9774,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9722,25 +9791,25 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
+          <t>คอมพิวเตอร์ประกอบ HTYE Y60 RTX5080 OC GDDR7 BLACK</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>288900</v>
+        <v>159000</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LduHGca9O</t>
+          <t>https://s.shopee.co.th/3qLKCIQ8CB</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m63p4ze31cil46.webp</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9772,20 +9841,20 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>195500</v>
+        <v>169700</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
+          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9795,7 +9864,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
       <c r="L202" t="n">
@@ -9820,20 +9889,20 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
+          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>180700</v>
+        <v>301100</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1113sedqpM</t>
+          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -9843,7 +9912,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -9865,20 +9934,20 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>180000</v>
+        <v>236900</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
+          <t>https://s.shopee.co.th/1qaAsBag8T</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -9888,11 +9957,8 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
-        </is>
-      </c>
-      <c r="L204" t="n">
-        <v>2</v>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -9913,20 +9979,20 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
+          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>337700</v>
+        <v>288900</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gODU2f7VK</t>
+          <t>https://s.shopee.co.th/1LduHGca9O</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -9936,11 +10002,8 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>I KNOW YOU</t>
-        </is>
-      </c>
-      <c r="L205" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -9961,20 +10024,20 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>204900</v>
+        <v>195500</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhdgLeUAN</t>
+          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -9984,8 +10047,11 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -10006,20 +10072,20 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>193900</v>
+        <v>180700</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlN5QgOBI</t>
+          <t>https://s.shopee.co.th/1113sedqpM</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10029,7 +10095,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -10051,20 +10117,20 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
+          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>205600</v>
+        <v>180000</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4nHjfkqL</t>
+          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10074,8 +10140,11 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -10096,20 +10165,20 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
+          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>193400</v>
+        <v>337700</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18WgoherG</t>
+          <t>https://s.shopee.co.th/gODU2f7VK</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10119,8 +10188,11 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
+          <t>I KNOW YOU</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -10141,20 +10213,20 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>189900</v>
+        <v>204900</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
+          <t>https://s.shopee.co.th/qhdgLeUAN</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10164,7 +10236,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -10186,20 +10258,20 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>198500</v>
+        <v>193900</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XCe0OciG</t>
+          <t>https://s.shopee.co.th/LlN5QgOBI</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10209,7 +10281,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -10231,20 +10303,20 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
+          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>189000</v>
+        <v>205600</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
+          <t>https://s.shopee.co.th/W4nHjfkqL</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10254,7 +10326,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -10276,20 +10348,20 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>192900</v>
+        <v>193400</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
+          <t>https://s.shopee.co.th/18WgoherG</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10299,7 +10371,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -10321,20 +10393,20 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
+          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>187900</v>
+        <v>189900</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
+          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10366,7 +10438,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -10374,12 +10446,12 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
+          <t>https://s.shopee.co.th/50XCe0OciG</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10391,9 +10463,6 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L215" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="216">
@@ -10414,20 +10483,20 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
+          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>195500</v>
+        <v>189000</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
+          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10459,20 +10528,20 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
+          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>459500</v>
+        <v>192900</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40efSASQkA</t>
+          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10504,20 +10573,20 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
+          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>186900</v>
+        <v>187900</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
+          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10549,20 +10618,20 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>186900</v>
+        <v>198500</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
+          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10574,6 +10643,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L219" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -10594,20 +10666,20 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
+          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>185500</v>
+        <v>195500</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLFFrT45B</t>
+          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -10639,20 +10711,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
+          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>269500</v>
+        <v>459500</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOyewUy66</t>
+          <t>https://s.shopee.co.th/40efSASQkA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -10684,20 +10756,20 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
+          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>195000</v>
+        <v>186900</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
+          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -10729,20 +10801,20 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
+          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>195500</v>
+        <v>186900</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8GKWEm4</t>
+          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -10774,20 +10846,20 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>179900</v>
+        <v>185500</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
+          <t>https://s.shopee.co.th/3qLFFrT45B</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -10819,20 +10891,20 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
+          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>185500</v>
+        <v>269500</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+          <t>https://s.shopee.co.th/3LOyewUy66</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -10864,20 +10936,20 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
+          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>198500</v>
+        <v>195000</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSi41Ws75</t>
+          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -10909,20 +10981,20 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
+          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>192900</v>
+        <v>195500</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXxouETJ2</t>
+          <t>https://s.shopee.co.th/30m8GKWEm4</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -10954,20 +11026,20 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
+          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>188500</v>
+        <v>179900</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prO1DDpy5</t>
+          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -10999,20 +11071,20 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>215000</v>
+        <v>185500</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
+          <t>https://s.shopee.co.th/2g9HriXVS2</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11044,20 +11116,20 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>228800</v>
+        <v>198500</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
+          <t>https://s.shopee.co.th/2qSi41Ws75</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11067,7 +11139,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -11089,20 +11161,20 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
+          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>209000</v>
+        <v>192900</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70IH1gH0ey</t>
+          <t>https://s.shopee.co.th/7fXxouETJ2</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11112,14 +11184,14 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>shoppingpc dotnet</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -11129,25 +11201,25 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
+          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>22700</v>
+        <v>188500</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
+          <t>https://s.shopee.co.th/7prO1DDpy5</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11157,17 +11229,14 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>mcwinner</t>
-        </is>
-      </c>
-      <c r="L232" t="n">
-        <v>19</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -11177,25 +11246,25 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>26500</v>
+        <v>215000</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9IIXOei9</t>
+          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11205,17 +11274,14 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L233" t="n">
-        <v>6</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -11225,25 +11291,25 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>10500</v>
+        <v>228800</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11255,15 +11321,12 @@
         <is>
           <t>JIB Official Store</t>
         </is>
-      </c>
-      <c r="L234" t="n">
-        <v>382</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -11273,25 +11336,25 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>33000</v>
+        <v>209000</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+          <t>https://s.shopee.co.th/70IH1gH0ey</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11301,11 +11364,8 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L235" t="n">
-        <v>6</v>
+          <t>shoppingpc dotnet</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -11326,20 +11386,20 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>29900</v>
+        <v>22700</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11349,11 +11409,11 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>atSine Tech</t>
+          <t>mcwinner</t>
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="237">
@@ -11374,20 +11434,20 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>24200</v>
+        <v>26500</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
+          <t>https://s.shopee.co.th/2g9IIXOei9</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11397,11 +11457,11 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
       <c r="L237" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="238">
@@ -11422,33 +11482,225 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
+          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>33000</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>29900</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>atSine Tech</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>24200</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
           <t>CPU AMD AM5 RYZEN 9 9950X3D (NEXT) - A0168684</t>
         </is>
       </c>
-      <c r="E238" t="n">
+      <c r="E242" t="n">
         <v>32200</v>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>https://s.shopee.co.th/3qLFggKDLS</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
+      <c r="H242" t="inlineStr">
         <is>
           <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
         <is>
           <t>Advice Official Shop</t>
         </is>
       </c>
-      <c r="L238" t="n">
+      <c r="L242" t="n">
         <v>11</v>
       </c>
     </row>

--- a/data/affiliate/picks.xlsx
+++ b/data/affiliate/picks.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N242"/>
+  <dimension ref="A1:N286"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5948,25 +5948,25 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ PNY GeForce RTX 5080 16GB ARGB Overclocked Triple Fan DLSS 4 GDDR7</t>
+          <t>ASUS PROART GEFORCE RTX5070TI-O16G (90YV0NR0-M0NA00)</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>51900</v>
+        <v>52000</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7913vKx</t>
+          <t>https://s.shopee.co.th/903S2OzxYy</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mo4863r6po1v3b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mmvian60wnphfc.webp</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5976,11 +5976,8 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
-      </c>
-      <c r="L117" t="n">
-        <v>1</v>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -5996,25 +5993,25 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GBT GF RTX 5080 GAMING OC 16G (Rev1.0)	GV-N5080GAMOC-16GD</t>
+          <t>ASUS PRIME GEFORCE RTX5070TI O16G OC GDDR7 (90YV0MF0-M0NA00)</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>57600</v>
+        <v>46000</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjEyaHFRI</t>
+          <t>https://s.shopee.co.th/9AMsEhzKE1</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-mazph6oiow1i7d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mm793mv5xj4551.webp</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6024,8 +6021,11 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Hp_by_iqink</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -6041,25 +6041,25 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING GEFORCE RTX5080 SOLID CORE OC 16GB 256BIT GDDR7(P288-1N765-300Z8)</t>
+          <t>GIGABYTE RTX5070TI/16GB EAGLE (OC/D7) - A0166986</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>56000</v>
+        <v>45200</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PomHHsmH</t>
+          <t>https://s.shopee.co.th/8fQbdn1EEw</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8a9twwj7iemf8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m7gdublfs1m86e.webp</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6069,11 +6069,8 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
-        </is>
-      </c>
-      <c r="L119" t="n">
-        <v>4</v>
+          <t>Advice Official Shop</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -6089,25 +6086,25 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ASUS PRIME GEFORCE RTX5080 OC 16G GDDR7 (90YV0LX0-M0NA00)</t>
+          <t>ASUS PRIME RTX5070Ti 16GB GDDR7</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>63000</v>
+        <v>52900</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5NCFylO</t>
+          <t>https://s.shopee.co.th/8pk1q60atz</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m846xz01ff8u95.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mjazn3fxov0h4d.webp</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6117,11 +6114,8 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
-        </is>
-      </c>
-      <c r="L120" t="n">
-        <v>9</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -6137,25 +6131,25 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7</t>
+          <t>ASUS PROART RTX5070Ti OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>52900</v>
+        <v>62600</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fAtGc6N</t>
+          <t>https://s.shopee.co.th/1qaHVERF6e</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmv7butau96u14.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mlls2kcn9yx474.webp</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6165,7 +6159,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6182,25 +6176,25 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G GAMING TRIO OC - 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5070 TI 16GB GDDR7 OC EDITION (TUF-RTX5070TI-O16G-GAMING)</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>62600</v>
+        <v>50500</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYBMJmnE</t>
+          <t>https://s.shopee.co.th/1gGrIvRsRd</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-moy490f3fuofce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mb7u0de0il4xd1.webp</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6210,8 +6204,11 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -6227,25 +6224,25 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7 +  PSU ASUS 1200W ROG THOR 1200P3 80+PLATINUM MIKU</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5070 TI 16GB GDDR7 OC EDITION (PRIME-RTX5070TI-O16G)</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>111000</v>
+        <v>47200</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA7z3KQ8D</t>
+          <t>https://s.shopee.co.th/1VxR6cSVmc</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mmjrx4g2i8zn0b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0q-mb7v1jaip2lt84.webp</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6255,8 +6252,11 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>D.P COMPUTER Hi End</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -6272,25 +6272,25 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
+          <t>คอมประกอบ Advice : Computer Set AMD #A282 RYZEN 7 9800X3D RTX5070TI 16GB ZOTAC GAMING SOLID SFF (OC/D7) - A0182231</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>89900</v>
+        <v>99100</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6OZyIW7K</t>
+          <t>https://s.shopee.co.th/1Le0uJT97b</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mpkfshwxt3ij71.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mqbs5qi4s8w280.webp</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>D.P COMPUTER Hi End</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -6317,25 +6317,25 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5080 SOLID CORE OC</t>
+          <t>ROG Strix G18 G815LR-S9149W  Asus U9-275HX 32G1TB RTX5070Ti W11 3YOSS</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>52200</v>
+        <v>101400</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyNfJ9SJ</t>
+          <t>https://s.shopee.co.th/2VpyISOhkq</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mm1mtsp7op3402.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbth02iajrcw39.webp</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>M.B Computer Store</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -6362,25 +6362,25 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 X3 OC - 16GB GDDR7 - A0182764</t>
+          <t>VGA (การ์ดจอ) ASUS TUF GAMING GEFORCE RTX5070TI O16G GDDR7 WHITE (90YV0MD3-M0NA00)</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>56500</v>
+        <v>51000</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcZ2CAjg</t>
+          <t>https://s.shopee.co.th/2LWY69PL5p</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpukkz1kncp821.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mmvihxk5qb5y12.webp</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>TECHNOCOM.OFFICIAL</t>
         </is>
       </c>
     </row>
@@ -6407,25 +6407,25 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL FROSTBITE OC - 16GB GDDR7 - A0182767</t>
+          <t>ZOTAC GAMING GEFORCE RTX5070TI APOCALYPSE OC 16GB 256BIT GDDR7 (P288-2N774-100Z8)</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>71700</v>
+        <v>45700</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCMjCo4f</t>
+          <t>https://s.shopee.co.th/2BD7tqPyQo</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mpukedl8v8ch88.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mqbs935dbhtsfc.webp</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>TECHNOCOM.OFFICIAL</t>
         </is>
       </c>
     </row>
@@ -6452,25 +6452,25 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 WINDFORCE OC SFF 16GB GDDR7</t>
+          <t>ACER PREDATOR HELIOS NEO 18 AI Core Ultra 9 275HX/RTX5070Ti RAM32/1TB - ID26060542</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>52900</v>
+        <v>85400</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prSxeAu3m</t>
+          <t>https://s.shopee.co.th/20thhXQbln</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkd8n452amth61.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq4naq4wmqks52.webp</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6480,11 +6480,8 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
-        <v>10</v>
+          <t>10X Store</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -6500,25 +6497,25 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ ZOTAC GAMING GeForce RTX 5080 GAMING SOLID CORE OC 16GB GDDR7</t>
+          <t>MSI RTX5070Ti 16GB FRIEREN EDITION OC GDDR7</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>52400</v>
+        <v>55800</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2lLBXOl</t>
+          <t>https://s.shopee.co.th/W4tumWJoW</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mki0hzdcdlvk9a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mo6nbxj8e0w228.webp</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6528,11 +6525,11 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -6548,25 +6545,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 (PRIME-RTX5080-16G)</t>
+          <t>ASUS PRIME RTX5070Ti OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>67600</v>
+        <v>55900</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvloEi5c</t>
+          <t>https://s.shopee.co.th/LlTiTWx9V</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4j8l8twxuce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mjazntpkuolddd.webp</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6576,7 +6573,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6593,25 +6590,25 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+          <t>ASUS ROG STRIX GEFORCE RTX5070TI 16G OC GDDR7 (90YV0M90-M0NA00)</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>55900</v>
+        <v>53400</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVZVFLQb</t>
+          <t>https://s.shopee.co.th/BS3WAXaUU</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mmv7325j5mgxbb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mp22s4bnftvz9f.webp</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6621,7 +6618,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>TECHNOCOM.OFFICIAL</t>
         </is>
       </c>
     </row>
@@ -6638,25 +6635,25 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
+          <t>ASUS PRIME GEFORCE RTX5070TI O16G GDDR7 (90YV0MF1-M0NA00)</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>113000</v>
+        <v>44000</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmAQDRPi</t>
+          <t>https://s.shopee.co.th/18dJrYDpT</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mjxxy5kvxjied7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mm794ac4o4cvc6.webp</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6666,7 +6663,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>TECHNOCOM.OFFICIAL</t>
         </is>
       </c>
     </row>
@@ -6683,25 +6680,25 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 EX GAMER 16GB GDDR7</t>
+          <t>ROG STRIX RTX5070TI 16GB GDDR7</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>71900</v>
+        <v>59000</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70ILy7E4kh</t>
+          <t>https://s.shopee.co.th/1BKai0TmSi</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mjjcxbr8kqo03d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlolyflr1l3842.webp</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6728,25 +6725,25 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC - 16GB GDDR7 (N50803-16D7X-17603930)</t>
+          <t>ASUS TUF RTX5070Ti 16GB GDDR7 OC EDITION WHITE</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>59000</v>
+        <v>58500</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTngROr2</t>
+          <t>https://s.shopee.co.th/111AVhUPnh</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbdla2gs3l9wca.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mj6i5ppe1x4yde.webp</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6756,11 +6753,8 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -6776,25 +6770,25 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>MSI VGA GEFORCE RTX 5080 SHADOW 3X OC - 16GB GDDR7 - A0167047</t>
+          <t>GIGABYTE  RTX5070Ti WINDFORCE OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>58000</v>
+        <v>52500</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3bNS2C1</t>
+          <t>https://s.shopee.co.th/qhkJOV38g</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rask-m9r5cxk7f42o1c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mjazzq70bfnp51.webp</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6804,7 +6798,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6821,25 +6815,25 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 XTREME WATERFORCE - 16GB GDDR7 (REV. 1.0) - A0166365</t>
+          <t>MSI RTX5070Ti SHADOW 3X OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>74200</v>
+        <v>48900</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKCIQ8B8</t>
+          <t>https://s.shopee.co.th/gOK75VgTf</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-mai21hqfq6icd6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mllsldlycs8y75.webp</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6849,7 +6843,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6866,25 +6860,25 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 AORUS MASTER 16GB GDDR7</t>
+          <t>GIGABYTE RTX5070TI EAGLE OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>60700</v>
+        <v>53000</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1tzzQlW7</t>
+          <t>https://s.shopee.co.th/4Vb2g8H5hQ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mky5qpeaknwi66.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zti-mipn37foe77s19.webp</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6894,7 +6888,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -6911,25 +6905,25 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
+          <t>GALAX RTX5070TI HOF GAMING 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>9000</v>
+        <v>58200</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSn0STwCy</t>
+          <t>https://s.shopee.co.th/4LHcTpHj2P</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0r-mdplixv8khri58.webp</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6939,11 +6933,8 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -6959,25 +6950,25 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7</t>
+          <t>ZOTAC GAMING RTX5070TI AMP EXTREME INFINITY 16GB GDDR7</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>67900</v>
+        <v>55000</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9Mo9UZXx</t>
+          <t>https://s.shopee.co.th/4AyCHWIMNO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4xoa7sr9r50.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5jpjeqp5o2y4d.webp</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6987,7 +6978,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7004,25 +6995,25 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC WHITE - 16GB GDDR7</t>
+          <t>GIGABYTE RTX5070TI WINDFORCE SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>55900</v>
+        <v>50900</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5dP4SfX4</t>
+          <t>https://s.shopee.co.th/40em5DIziN</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mqbi0037km4r5f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasb-m8ehv5m7ss1ae3.webp</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7032,7 +7023,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>แอดบอล คอมพิวเตอร์</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7049,25 +7040,25 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 HOF GAMING BLACK EDITION 16GB GDDR7</t>
+          <t>GALAX RTX5070TI 1-Click 16GB OC GDDR7</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>87000</v>
+        <v>53900</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30mDClTIs3</t>
+          <t>https://s.shopee.co.th/5AqjTMEYLc</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mi2smox3b8qo49.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasf-m8eh745gav494d.webp</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7094,25 +7085,25 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] AORUS MASTER RTX5070TI 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>69500</v>
+        <v>54500</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDrO8MK9Q</t>
+          <t>https://s.shopee.co.th/50XJH3FBgb</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9pqc1bk39ipd8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasf-m6ii6vufjlf314.webp</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7124,6 +7115,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L142" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -7139,25 +7133,25 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G VENTUS 3X OC - 16GB GDDR7</t>
+          <t>GIGABYTE RTX5070TI AERO OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>64100</v>
+        <v>55900</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuRBpMxUP</t>
+          <t>https://s.shopee.co.th/4qDt4kFp1a</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmjx8u2c385h1b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m8foo9zb1lksf6.webp</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7167,7 +7161,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7184,25 +7178,25 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 AERO OC - 16GB GDDR7 (REV. 1.0) - A0166362</t>
+          <t>INNO3D RTX5070TI X3 OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>66200</v>
+        <v>53000</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqhmkL3TW</t>
+          <t>https://s.shopee.co.th/4fuSsRGSMZ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m9r5fxjheinlbf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m8ebv72sw96k90.webp</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7212,11 +7206,8 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L144" t="n">
-        <v>3</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -7232,25 +7223,25 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VGA GIGABYTE GEFORCE RTX 5080 AORUS MASTER - 16GB GDDR7 (REV. 1.0) - A0166364</t>
+          <t>GALAX RTX5070Ti EX GAMER WHITE 16GB  GDDR7</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>70500</v>
+        <v>56300</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XHaRLgoV</t>
+          <t>https://s.shopee.co.th/3B5f5gMAPI</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e59iq7j2a769.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m8ecnbitb0fi14.webp</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7260,7 +7251,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7277,25 +7268,25 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 WHITE OC EDITION</t>
+          <t>GIGABYTE RTX5070TI GAMING OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>79900</v>
+        <v>48500</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4AyAauOrVM</t>
+          <t>https://s.shopee.co.th/30mEtNMnkH</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlljzbvrqccib8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m8eho3pfd7u69c.webp</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7305,7 +7296,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7322,25 +7313,25 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(มีโค้ดลด2000฿) RTX 5060 5060Ti 5060 ti 2060Super 3060 3060Ti 3070 3070Ti 4060 4060Ti 4070 4070Ti 4080 4090 5080 5090</t>
+          <t>ZOTAC RTX5070Ti SOLID SFF GAMING OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5000</v>
+        <v>53900</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40ekObPUqL</t>
+          <t>https://s.shopee.co.th/2qSoh4NR5G</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8u4pn1mw4m862.webp</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7350,11 +7341,8 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>EZGGTECH</t>
-        </is>
-      </c>
-      <c r="L147" t="n">
-        <v>23</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -7370,25 +7358,25 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
+          <t>ASUS ROG STRIX RTX5070TI OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>21400</v>
+        <v>62900</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vb0zWNapS</t>
+          <t>https://s.shopee.co.th/2g9OUlO4QF</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mcsx7iqm7yvy75.webp</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7398,7 +7386,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>3CCamera.th</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7415,25 +7403,25 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Intel Core Ultra 9 285K + RTX 5080 | DDR5 64GB 6400MHz / SSD 2TB | โทนขาว / ชุดแต่ง Lian Li</t>
+          <t>MSI RTX5070Ti 16GB GAMING TRIO OC WHITE</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>155700</v>
+        <v>55300</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHanDOEAR</t>
+          <t>https://s.shopee.co.th/3qLLsuJd3U</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfkgr2oabvux4c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdh7r43msg3i27.webp</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7443,7 +7431,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7460,25 +7448,25 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 AORUS XTREME WATERFORECE 16GB GDDR7</t>
+          <t>ASUS TUF RTX5070Ti GAMING OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>89500</v>
+        <v>56900</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhicmbYGm</t>
+          <t>https://s.shopee.co.th/3g1vgbKGOT</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prhvzpau3yd2.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m6hsrdaydm1s27.webp</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7505,25 +7493,25 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7 WHITE</t>
+          <t>GIGABYTE RTX5070TI EAGLE OC ICE SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>66900</v>
+        <v>53000</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gOIQTcBbl</t>
+          <t>https://s.shopee.co.th/3ViVUIKtjS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9pqq1xfnr3i22.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasg-m8ej6iuydq8944.webp</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7550,25 +7538,25 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+          <t>GALAX RTX5070TI 1-Click OC 16GB WHITE GDDR7</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>75300</v>
+        <v>55300</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKZ1OaHas</t>
+          <t>https://s.shopee.co.th/3LP5HzLX4R</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mmwzh1437egx8f.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m8efxvq7ay64b3.webp</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7578,7 +7566,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7595,25 +7583,25 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MSI VGA GEFORCE RTX 5080 VENTUS 3X OC - 16GB GDDR7 - A0167046</t>
+          <t>MSI RTX5070Ti 16GB MLG EDITION GDDR7</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>60500</v>
+        <v>52400</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1118p5auvr</t>
+          <t>https://s.shopee.co.th/7Abnr26wIC</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasf-m9r4yrpdj75afe.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mhhdqvg4unt15d.webp</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7623,7 +7611,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7640,25 +7628,25 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VGA GIGABYTE GEFORCE RTX 5080 GAMING OC - 16GB GDDR7 (REV. 1.0) - A0166361</t>
+          <t>MSI RTX5070Ti 16GB VENTUS 3X PZ OC GDDR7</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>65500</v>
+        <v>50900</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BS1pYe5ci</t>
+          <t>https://s.shopee.co.th/70INej7ZdB</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9e55v65yvbda7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mipmu163j95326.webp</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7668,7 +7656,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7685,25 +7673,25 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 ICHILL X3 V2 - 16GB GDDR7 C50803-16D7X-176069R</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] MSI RTX5070TI GAMING TRIO 16GB OC GDDR7</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>64900</v>
+        <v>55300</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18bdFeixh</t>
+          <t>https://s.shopee.co.th/6pyxSQ8CyA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-modebjzln30gb5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m6ihxs0haa5zcf.webp</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7713,7 +7701,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7730,25 +7718,25 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | RAM 64GB 6400MHz / SSD 2TB | โทนขาว / HYTE Y70 Touch</t>
+          <t>GALAX RTX5070Ti EX GAMER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>145900</v>
+        <v>55900</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4sEAcowo</t>
+          <t>https://s.shopee.co.th/6ffXG78qJ9</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq8r6vopg3rg36.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m6httcohdynp71.webp</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7758,7 +7746,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7775,25 +7763,25 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ROG Zephyrus G18 G815LW-S9112W Asus U9-275HX32 G 1TB RTX5080 W11 3YOSS</t>
+          <t>GIGABYTE RTX5070Ti AORUS MASTER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>125000</v>
+        <v>58500</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlS1rdSHn</t>
+          <t>https://s.shopee.co.th/7prUeG4OwO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-me5o4gxp31mrb5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mjb0hu1as0lgeb.webp</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7803,7 +7791,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>NOTEBOOK  CORP</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7820,25 +7808,25 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>INNO3D RTX5070Ti X3 OC WHITE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>130900</v>
+        <v>50900</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD6DEWTZA</t>
+          <t>https://s.shopee.co.th/7fY4Rx52HN</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq90ma8arc3x60.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mjb0szzu0qh108.webp</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7848,7 +7836,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -7865,25 +7853,25 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>MSI RTX5080 SHADOW 3X OC 16GB GDDR7</t>
+          <t>GALAX RTX5070TI HOF GAMING 16GB GDDR7 BLACK</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>67800</v>
+        <v>56600</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20tg0vX6u9</t>
+          <t>https://s.shopee.co.th/7VEeFe5fcM</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9prwjnh3cy749.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mdpkzbke5jzy84.webp</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7910,25 +7898,25 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070ti</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 WINFOREC OC SFF 16GB GDDR7</t>
+          <t>คอมพิวเตอร์ประกอบ JONSBO TK-2 TUF RTX5070TI GAMING OC GDDR7</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>68500</v>
+        <v>203000</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2VpwbqVCtG</t>
+          <t>https://s.shopee.co.th/7KvE3L6IxL</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prnu5bv9wxb3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mdvgos62o35w3d.webp</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7960,20 +7948,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 MASTER 16G - 16GB GDDR7 (GV-N5080AORUS M-16GD)</t>
+          <t>VGA การ์ดจอ PNY GeForce RTX 5080 16GB ARGB Overclocked Triple Fan DLSS 4 GDDR7</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>67900</v>
+        <v>51900</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2LWWPXVqEF</t>
+          <t>https://s.shopee.co.th/9fJ7913vKx</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbbxwlx4z7uc43.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mo4863r6po1v3b.webp</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7983,8 +7971,11 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -8005,20 +7996,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>GALAX VGA GEFORCE RTX 5080 HOF GAMING BLACK - 16GB GDDR7 - A0172861</t>
+          <t>GBT GF RTX 5080 GAMING OC 16G (Rev1.0)	GV-N5080GAMOC-16GD</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>68400</v>
+        <v>57600</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxPQ0Z0v6</t>
+          <t>https://s.shopee.co.th/6AjEyaHFRI</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134275-824je-me9vcwg1o3cw45.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-mazph6oiow1i7d.webp</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8028,7 +8019,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>Hp_by_iqink</t>
         </is>
       </c>
     </row>
@@ -8050,20 +8041,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO OC - 16GB GDDR7 - A0180200</t>
+          <t>ZOTAC GAMING GEFORCE RTX5080 SOLID CORE OC 16GB 256BIT GDDR7(P288-1N765-300Z8)</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>55500</v>
+        <v>56000</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LdzDhZeG5</t>
+          <t>https://s.shopee.co.th/60PomHHsmH</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134275-82609-mmd4ly6nd341a5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8a9twwj7iemf8.webp</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8073,8 +8064,11 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="164">
@@ -8095,20 +8089,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 XTREME WATERFORCE 16G - 16GB GDDR7 (GV-N5080AORUSX W-16GD)</t>
+          <t>ASUS PRIME GEFORCE RTX5080 OC 16G GDDR7 (90YV0LX0-M0NA00)</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>73800</v>
+        <v>63000</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaFocXkFC</t>
+          <t>https://s.shopee.co.th/6VM5NCFylO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mbbxc0wleh6p7b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m846xz01ff8u95.webp</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8118,8 +8112,11 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="165">
@@ -8140,20 +8137,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 16GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>VGA (การ์ดแสดงผล) PALIT GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>130900</v>
+        <v>52900</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGpcJYNaB</t>
+          <t>https://s.shopee.co.th/6L2fAtGc6N</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mq8stcq5cx6of7.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmv7butau96u14.webp</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8163,7 +8160,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -8185,20 +8182,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>MSI STEALTH A16 AI PLUS Ryzen AI 9 HX 370/RTX 5080 RAM64/2TB - ID26060441</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G GAMING TRIO OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>113400</v>
+        <v>62600</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fQZxB7jNY</t>
+          <t>https://s.shopee.co.th/5VTYBMJmnE</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpuc7ehxc9ho8a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-moy490f3fuofce.webp</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8208,7 +8205,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>10X Store</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -8230,20 +8227,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Original 380W 20V 19A อะแดปเตอร์ชาร์จสําหรับ ASUS ROG Strix scar 16 2025 G635LW RTX5080 ADP-380AB B</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7 +  PSU ASUS 1200W ROG THOR 1200P3 80+PLATINUM MIKU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6400</v>
+        <v>111000</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pk09U762b</t>
+          <t>https://s.shopee.co.th/5LA7z3KQ8D</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824jc-mep4jcmcgnphd5.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mmjrx4g2i8zn0b.webp</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8253,11 +8250,8 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>junyue999.th</t>
-        </is>
-      </c>
-      <c r="L167" t="n">
-        <v>3</v>
+          <t>D.P COMPUTER Hi End</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -8278,20 +8272,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5080 AORUS MASTER ICE 16GB GDDR7</t>
+          <t>ASUS ROG ASTRAL GEFORCE RTX 5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>82500</v>
+        <v>89900</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/903QLn6She</t>
+          <t>https://s.shopee.co.th/5q6OZyIW7K</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-map4vxrow1ao8a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mpkfshwxt3ij71.webp</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8301,11 +8295,8 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L168" t="n">
-        <v>1</v>
+          <t>D.P COMPUTER Hi End</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -8326,20 +8317,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>INNO3D RTX5080 X3 OC 16GB BLACK GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GeForce RTX 5080 SOLID CORE OC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>66900</v>
+        <v>52200</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AMqY65pMh</t>
+          <t>https://s.shopee.co.th/5fmyNfJ9SJ</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8d39ntj3z7289.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-mm1mtsp7op3402.webp</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8349,7 +8340,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>M.B Computer Store</t>
         </is>
       </c>
     </row>
@@ -8371,20 +8362,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC WHITE - 16GB GDDR7 (N50803-16D7X-17605211)</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 X3 OC - 16GB GDDR7 - A0182764</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>59000</v>
+        <v>56500</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/80At9xAGjU</t>
+          <t>https://s.shopee.co.th/7VEcZ2CAjg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbdmsesr8qk199.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpukkz1kncp821.webp</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8394,7 +8385,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -8416,20 +8407,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL X3 V2 OC - 16GB GDDR7 - A0182766</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL FROSTBITE OC - 16GB GDDR7 - A0182767</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>61800</v>
+        <v>71700</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8AUJMG9dOX</t>
+          <t>https://s.shopee.co.th/7KvCMjCo4f</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mpujxufur8y4aa.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mpukedl8v8ch88.webp</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8461,20 +8452,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7 - A0166369</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 WINDFORCE OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>55500</v>
+        <v>52900</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8KnjYZ903a</t>
+          <t>https://s.shopee.co.th/7prSxeAu3m</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0k-mc7mmx5y9omf72.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mkd8n452amth61.webp</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8484,11 +8475,11 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173">
@@ -8509,20 +8500,20 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
+          <t>VGA การ์ดจอ ZOTAC GAMING GeForce RTX 5080 GAMING SOLID CORE OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>78500</v>
+        <v>52400</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8V79ks8Mid</t>
+          <t>https://s.shopee.co.th/7fY2lLBXOl</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-me6x1j4ufmyqba.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mki0hzdcdlvk9a.webp</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8532,11 +8523,11 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174">
@@ -8557,20 +8548,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>GIGABYTE VGA GEFORCE RTX 5080 WINDFORCE OC - 16GB GDDR7 (REV. 1.0) - A0166360</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 (PRIME-RTX5080-16G)</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>60300</v>
+        <v>67600</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9zvxXd2efw</t>
+          <t>https://s.shopee.co.th/6pyvloEi5c</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134275-7ras8-m9r4yq4hudlb71.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4j8l8twxuce.webp</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8580,11 +8571,8 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L174" t="n">
-        <v>2</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -8605,20 +8593,20 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 EX GAMER 16GB GDDR7 WHITE</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>69200</v>
+        <v>55900</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAFNjw21Kz</t>
+          <t>https://s.shopee.co.th/6ffVZVFLQb</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9pqwzx9tkvi06.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mmv7325j5mgxbb.webp</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8628,7 +8616,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -8650,20 +8638,20 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>GIGABYTE GAMING RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>ASUS ROG ASTRAL RTX5080 OC HATSUNE MIKU EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>75900</v>
+        <v>113000</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKYnwF1O02</t>
+          <t>https://s.shopee.co.th/7AbmAQDRPi</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5zvhd595sc69a.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mjxxy5kvxjied7.webp</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8695,20 +8683,20 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 WINDFORCE OC SFF 16G - 16GB GDDR7 (GV-N5080WF3OC-16GD)</t>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>58800</v>
+        <v>71900</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AUsE8Y0kf5</t>
+          <t>https://s.shopee.co.th/70ILy7E4kh</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbc1uyc222bab6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mjjcxbr8kqo03d.webp</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8718,7 +8706,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -8740,20 +8728,20 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] MSI GAMING TRIO RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC - 16GB GDDR7 (N50803-16D7X-17603930)</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>72900</v>
+        <v>59000</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9KgGkP5C1s</t>
+          <t>https://s.shopee.co.th/3ViTngROr2</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m5qng58cco0t25.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0j-mbdla2gs3l9wca.webp</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8763,7 +8751,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -8788,20 +8776,20 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>RTX5080/16GB GALAX 1-CLICK (OC/D7) - A0166352</t>
+          <t>MSI VGA GEFORCE RTX 5080 SHADOW 3X OC - 16GB GDDR7 - A0167047</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>59600</v>
+        <v>58000</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9Uzgwi4Ygv</t>
+          <t>https://s.shopee.co.th/3LP3bNS2C1</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m81gt7mb1w4u18.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rask-m9r5cxk7f42o1c.webp</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8813,9 +8801,6 @@
         <is>
           <t>Advice Official Shop</t>
         </is>
-      </c>
-      <c r="L179" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="180">
@@ -8836,20 +8821,20 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 HOF GAMING BLACK EDITION - 16GB GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 XTREME WATERFORCE - 16GB GDDR7 (REV. 1.0) - A0166365</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>70600</v>
+        <v>74200</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJ7913vLy</t>
+          <t>https://s.shopee.co.th/3qLKCIQ8B8</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdpq3ctyx2ta3e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rask-mai21hqfq6icd6.webp</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8859,7 +8844,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -8881,20 +8866,20 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5080 OC WHITE 16GB GDDR7</t>
+          <t>VGA การ์ดจอ GIGABYTE GeForce RTX 5080 AORUS MASTER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>89500</v>
+        <v>60700</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9pcXLK3I11</t>
+          <t>https://s.shopee.co.th/3g1tzzQlW7</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-misduj582yo30b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mky5qpeaknwi66.webp</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8904,7 +8889,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -8926,20 +8911,20 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5080 SOLID GAMING OC 16GB GDDR7 WHITE</t>
+          <t>การ์ดจอ RTX 3060Ti 3060Ti 4060 4070 4080 5070 5080 5090</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>64900</v>
+        <v>9000</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60PomHHsnI</t>
+          <t>https://s.shopee.co.th/2qSn0STwCy</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-mapdn0hs6q9gfb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8949,8 +8934,11 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>EZGGTECH</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -8971,20 +8959,20 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>GALAX RTX5080 HOF GAMING 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>87000</v>
+        <v>67900</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AjEyaHFSL</t>
+          <t>https://s.shopee.co.th/2g9Mo9UZXx</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mi2scd35wirsed.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-moy4xoa7sr9r50.webp</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8994,7 +8982,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>แอดบอล คอมพิวเตอร์</t>
         </is>
       </c>
     </row>
@@ -9016,20 +9004,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>GIGABYTE AERO RTX5080 16GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC WHITE - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>78500</v>
+        <v>55900</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L2fAtGc7O</t>
+          <t>https://s.shopee.co.th/3B5dP4SfX4</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mki1wyjsh14yd6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mqbi0037km4r5f.webp</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9039,11 +9027,8 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L184" t="n">
-        <v>1</v>
+          <t>แอดบอล คอมพิวเตอร์</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -9064,20 +9049,20 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5080 SOLID CORE OC 16GB GDDR7</t>
+          <t>GALAX RTX5080 HOF GAMING BLACK EDITION 16GB GDDR7</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>62500</v>
+        <v>87000</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VM5NCFymR</t>
+          <t>https://s.shopee.co.th/30mDClTIs3</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mloguv0dy97323.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mi2smox3b8qo49.webp</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9109,20 +9094,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5080 SOLID CORE OC - 16GB GDDR7 (ZT-B50800J2-10P)</t>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>59000</v>
+        <v>69500</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LA7z3KQ9E</t>
+          <t>https://s.shopee.co.th/4qDrO8MK9Q</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbvy43nc50gsdd.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9pqc1bk39ipd8.webp</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9132,7 +9117,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9154,20 +9139,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ASUS TUF RTX5080 GAMING OC 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G VENTUS 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>81000</v>
+        <v>64100</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VTYBMJmoH</t>
+          <t>https://s.shopee.co.th/4fuRBpMxUP</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m9pk6xb8lmjk47.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztj-mmjx8u2c385h1b.webp</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9177,7 +9162,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -9199,20 +9184,20 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>INNO3D RTX5080 X3 OC WHITE 16GB GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 AERO OC - 16GB GDDR7 (REV. 1.0) - A0166362</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>68300</v>
+        <v>66200</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmyNfJ9TK</t>
+          <t>https://s.shopee.co.th/5AqhmkL3TW</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8d2yz7814ax90.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasm-m9r5fxjheinlbf.webp</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9222,8 +9207,11 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -9244,20 +9232,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7 (GV-N5080AERO OC-16GD)</t>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 AORUS MASTER - 16GB GDDR7 (REV. 1.0) - A0166364</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>67000</v>
+        <v>70500</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q6OZyIW8N</t>
+          <t>https://s.shopee.co.th/50XHaRLgoV</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbbyjj2rglflce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9e59iq7j2a769.webp</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9267,7 +9255,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -9289,20 +9277,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE AORUS RTX5080 MASTER 16GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 WHITE OC EDITION</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>80900</v>
+        <v>79900</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KvCMjCo5g</t>
+          <t>https://s.shopee.co.th/4AyAauOrVM</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml4sii5ubnym20.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-mlljzbvrqccib8.webp</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9312,11 +9300,8 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L190" t="n">
-        <v>1</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -9337,20 +9322,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5080 16GB OC GDDR7 BLACK</t>
+          <t>(มีโค้ดลด2000฿) RTX 5060 5060Ti 5060 ti 2060Super 3060 3060Ti 3070 3070Ti 4060 4060Ti 4070 4070Ti 4080 4090 5080 5090</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>85500</v>
+        <v>5000</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEcZ2CAkj</t>
+          <t>https://s.shopee.co.th/40ekObPUqL</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq632jnzevwuf9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m6deloele5jx0d.webp</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9360,8 +9345,11 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>EZGGTECH</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="192">
@@ -9382,20 +9370,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5080 16 GB GDDR7 OC EDITION</t>
+          <t>Alphacool Core Water Block Serve สําหรับ Inno3D Geforce RTX 5080 Reference (AIC),MSI GeForce 5080/5070 Ti VENTUS 3X OC การ์ด Cooler</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>88500</v>
+        <v>21400</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fY2lLBXPm</t>
+          <t>https://s.shopee.co.th/4Vb0zWNapS</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5p939h7ybw69b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134202-822yl-mhyxlw339sle8f.webp</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9405,11 +9393,8 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L192" t="n">
-        <v>1</v>
+          <t>3CCamera.th</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -9430,20 +9415,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>MSI RTX5080 VENTUS X3 OC PLUS 16GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Intel Core Ultra 9 285K + RTX 5080 | DDR5 64GB 6400MHz / SSD 2TB | โทนขาว / ชุดแต่ง Lian Li</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>63000</v>
+        <v>155700</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prSxeAu4p</t>
+          <t>https://s.shopee.co.th/4LHanDOEAR</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mnkzq2y21x51b3.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mfkgr2oabvux4c.webp</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9453,7 +9438,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -9475,20 +9460,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ASUS PRIME RTX5080 OC 16GB GDDR7</t>
+          <t>GIGABYTE RTX5080 AORUS XTREME WATERFORECE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>74300</v>
+        <v>89500</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6ffVZVFLRc</t>
+          <t>https://s.shopee.co.th/qhicmbYGm</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9pl3a6dymlq34.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prhvzpau3yd2.webp</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9520,20 +9505,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G SHADOW 3X OC - 16GB GDDR7</t>
+          <t>GALAX RTX5080 1-CLICK OC 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>60500</v>
+        <v>66900</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyvloEi6f</t>
+          <t>https://s.shopee.co.th/gOIQTcBbl</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m807f87tz7xq68.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9pqq1xfnr3i22.webp</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9543,11 +9528,8 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L195" t="n">
-        <v>1</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -9568,20 +9550,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 GAMING OC 16G - 16GB GDDR7 (GV-N5080GAMING OC-16GD)</t>
+          <t>VGA (การ์ดแสดงผล) ASUS PROART GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>63500</v>
+        <v>75300</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70ILy7E4li</t>
+          <t>https://s.shopee.co.th/1BKZ1OaHas</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0o-mbbz0v0mfsdt28.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-mmwzh1437egx8f.webp</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9613,20 +9595,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC - 16GB GDDR7</t>
+          <t>MSI VGA GEFORCE RTX 5080 VENTUS 3X OC - 16GB GDDR7 - A0167046</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>61400</v>
+        <v>60500</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7AbmAQDRQl</t>
+          <t>https://s.shopee.co.th/1118p5auvr</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0g-mb65w0t41ai927.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7rasf-m9r4yrpdj75afe.webp</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9636,7 +9618,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -9658,20 +9640,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5080 16GB GDDR7 OC EDITION (TUF-RTX5080-O16G-GAMING)</t>
+          <t>VGA GIGABYTE GEFORCE RTX 5080 GAMING OC - 16GB GDDR7 (REV. 1.0) - A0166361</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>71700</v>
+        <v>65500</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LP3bNS2D2</t>
+          <t>https://s.shopee.co.th/BS1pYe5ci</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mb7lu03gdf7ace.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rase-m9e55v65yvbda7.webp</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9681,7 +9663,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -9703,20 +9685,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 ICHILL X3 V2 - 16GB GDDR7 C50803-16D7X-176069R</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>63900</v>
+        <v>64900</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViTngROs5</t>
+          <t>https://s.shopee.co.th/18bdFeixh</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9qqhz75s2cu0e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-modebjzln30gb5.webp</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9728,9 +9710,6 @@
         <is>
           <t>JIB Official Store</t>
         </is>
-      </c>
-      <c r="L199" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -9751,20 +9730,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ HYTE Y40 RTX5080 BLACK/WHITE</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | RAM 64GB 6400MHz / SSD 2TB | โทนขาว / HYTE Y70 Touch</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>155900</v>
+        <v>145900</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1tzzQlX8</t>
+          <t>https://s.shopee.co.th/W4sEAcowo</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m5v66xgrzeuv7b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq8r6vopg3rg36.webp</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9774,7 +9753,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
         </is>
       </c>
     </row>
@@ -9796,20 +9775,20 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ HTYE Y60 RTX5080 OC GDDR7 BLACK</t>
+          <t>ROG Zephyrus G18 G815LW-S9112W Asus U9-275HX32 G 1TB RTX5080 W11 3YOSS</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>159000</v>
+        <v>125000</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLKCIQ8CB</t>
+          <t>https://s.shopee.co.th/LlS1rdSHn</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m63p4ze31cil46.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-me5o4gxp31mrb5.webp</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9819,7 +9798,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>NOTEBOOK  CORP</t>
         </is>
       </c>
     </row>
@@ -9836,25 +9815,25 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>169700</v>
+        <v>130900</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
+          <t>https://s.shopee.co.th/2BD6DEWTZA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq90ma8arc3x60.webp</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9864,11 +9843,8 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L202" t="n">
-        <v>1</v>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -9884,25 +9860,25 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
+          <t>MSI RTX5080 SHADOW 3X OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>301100</v>
+        <v>67800</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
+          <t>https://s.shopee.co.th/20tg0vX6u9</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rash-m9prwjnh3cy749.webp</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -9912,7 +9888,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9929,25 +9905,25 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+          <t>GIGABYTE RTX5080 WINFOREC OC SFF 16GB GDDR7</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>236900</v>
+        <v>68500</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaAsBag8T</t>
+          <t>https://s.shopee.co.th/2VpwbqVCtG</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m9prnu5bv9wxb3.webp</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -9957,7 +9933,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -9974,25 +9950,25 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 MASTER 16G - 16GB GDDR7 (GV-N5080AORUS M-16GD)</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>288900</v>
+        <v>67900</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LduHGca9O</t>
+          <t>https://s.shopee.co.th/2LWWPXVqEF</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbbxwlx4z7uc43.webp</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10002,7 +9978,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -10019,25 +9995,25 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
+          <t>GALAX VGA GEFORCE RTX 5080 HOF GAMING BLACK - 16GB GDDR7 - A0172861</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>195500</v>
+        <v>68400</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
+          <t>https://s.shopee.co.th/1VxPQ0Z0v6</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-824je-me9vcwg1o3cw45.webp</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10047,11 +10023,8 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L206" t="n">
-        <v>1</v>
+          <t>Advice Official Shop</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -10067,25 +10040,25 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO OC - 16GB GDDR7 - A0180200</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>180700</v>
+        <v>55500</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1113sedqpM</t>
+          <t>https://s.shopee.co.th/1LdzDhZeG5</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134275-82609-mmd4ly6nd341a5.webp</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10095,7 +10068,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -10112,25 +10085,25 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE AORUS GEFORCE RTX 5080 XTREME WATERFORCE 16G - 16GB GDDR7 (GV-N5080AORUSX W-16GD)</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>180000</v>
+        <v>73800</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
+          <t>https://s.shopee.co.th/1qaFocXkFC</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mbbxc0wleh6p7b.webp</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10140,11 +10113,8 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>TECHNOCOM.OFFICIAL</t>
-        </is>
-      </c>
-      <c r="L208" t="n">
-        <v>2</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -10160,25 +10130,25 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5080 16GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>337700</v>
+        <v>130900</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/gODU2f7VK</t>
+          <t>https://s.shopee.co.th/1gGpcJYNaB</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-mq8stcq5cx6of7.webp</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10188,11 +10158,8 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>I KNOW YOU</t>
-        </is>
-      </c>
-      <c r="L209" t="n">
-        <v>1</v>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -10208,25 +10175,25 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>MSI STEALTH A16 AI PLUS Ryzen AI 9 HX 370/RTX 5080 RAM64/2TB - ID26060441</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>204900</v>
+        <v>113400</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qhdgLeUAN</t>
+          <t>https://s.shopee.co.th/8fQZxB7jNY</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mpuc7ehxc9ho8a.webp</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10236,7 +10203,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>10X Store</t>
         </is>
       </c>
     </row>
@@ -10253,25 +10220,25 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+          <t>Original 380W 20V 19A อะแดปเตอร์ชาร์จสําหรับ ASUS ROG Strix scar 16 2025 G635LW RTX5080 ADP-380AB B</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>193900</v>
+        <v>6400</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LlN5QgOBI</t>
+          <t>https://s.shopee.co.th/8pk09U762b</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824jc-mep4jcmcgnphd5.webp</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10281,8 +10248,11 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
-        </is>
+          <t>junyue999.th</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="212">
@@ -10298,25 +10268,25 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
+          <t>GIGABYTE RTX5080 AORUS MASTER ICE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>205600</v>
+        <v>82500</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W4nHjfkqL</t>
+          <t>https://s.shopee.co.th/903QLn6She</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-map4vxrow1ao8a.webp</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10326,8 +10296,11 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -10343,25 +10316,25 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
+          <t>INNO3D RTX5080 X3 OC 16GB BLACK GDDR7</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>193400</v>
+        <v>66900</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/18WgoherG</t>
+          <t>https://s.shopee.co.th/9AMqY65pMh</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m8d39ntj3z7289.webp</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10371,7 +10344,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
@@ -10388,25 +10361,25 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) INNO3D GEFORCE RTX 5080 X3 OC WHITE - 16GB GDDR7 (N50803-16D7X-17605211)</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>189900</v>
+        <v>59000</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
+          <t>https://s.shopee.co.th/80At9xAGjU</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbdmsesr8qk199.webp</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10416,7 +10389,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -10433,25 +10406,25 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
+          <t>INNO3D VGA GEFORCE RTX 5080 ICHILL X3 V2 OC - 16GB GDDR7 - A0182766</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>198500</v>
+        <v>61800</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50XCe0OciG</t>
+          <t>https://s.shopee.co.th/8AUJMG9dOX</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztc-mpujxufur8y4aa.webp</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10461,7 +10434,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>Advice Official Shop</t>
         </is>
       </c>
     </row>
@@ -10478,25 +10451,25 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
+          <t>PALIT VGA GEFORCE RTX 5080 GAMINGPRO - 16GB GDDR7 - A0166369</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>189000</v>
+        <v>55500</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
+          <t>https://s.shopee.co.th/8KnjYZ903a</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0k-mc7mmx5y9omf72.webp</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10506,8 +10479,11 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -10523,25 +10499,25 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>192900</v>
+        <v>78500</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
+          <t>https://s.shopee.co.th/8V79ks8Mid</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztf-me6x1j4ufmyqba.webp</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10551,8 +10527,11 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -10568,25 +10547,25 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
+          <t>GIGABYTE VGA GEFORCE RTX 5080 WINDFORCE OC - 16GB GDDR7 (REV. 1.0) - A0166360</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>187900</v>
+        <v>60300</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
+          <t>https://s.shopee.co.th/9zvxXd2efw</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134275-7ras8-m9r4yq4hudlb71.webp</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10596,8 +10575,11 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="219">
@@ -10613,25 +10595,25 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
+          <t>GALAX RTX5080 EX GAMER 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>198500</v>
+        <v>69200</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
+          <t>https://s.shopee.co.th/AAFNjw21Kz</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9pqwzx9tkvi06.webp</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10643,9 +10625,6 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
-      </c>
-      <c r="L219" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -10661,25 +10640,25 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
+          <t>GIGABYTE GAMING RTX5080 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>195500</v>
+        <v>75900</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
+          <t>https://s.shopee.co.th/AKYnwF1O02</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5zvhd595sc69a.webp</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -10706,25 +10685,25 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 WINDFORCE OC SFF 16G - 16GB GDDR7 (GV-N5080WF3OC-16GD)</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>459500</v>
+        <v>58800</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40efSASQkA</t>
+          <t>https://s.shopee.co.th/AUsE8Y0kf5</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mbc1uyc222bab6.webp</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -10734,7 +10713,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -10751,25 +10730,25 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] MSI GAMING TRIO RTX5080 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>186900</v>
+        <v>72900</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
+          <t>https://s.shopee.co.th/9KgGkP5C1s</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m5qng58cco0t25.webp</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -10781,6 +10760,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -10796,25 +10778,25 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
+          <t>RTX5080/16GB GALAX 1-CLICK (OC/D7) - A0166352</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>186900</v>
+        <v>59600</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
+          <t>https://s.shopee.co.th/9Uzgwi4Ygv</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-m81gt7mb1w4u18.webp</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -10824,8 +10806,11 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
-        </is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="224">
@@ -10841,25 +10826,25 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 HOF GAMING BLACK EDITION - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>185500</v>
+        <v>70600</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qLFFrT45B</t>
+          <t>https://s.shopee.co.th/9fJ7913vLy</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0l-mdpq3ctyx2ta3e.webp</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -10869,7 +10854,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -10886,25 +10871,25 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
+          <t>ASUS ROG ASTRAL RTX5080 OC WHITE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>269500</v>
+        <v>89500</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOyewUy66</t>
+          <t>https://s.shopee.co.th/9pcXLK3I11</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztp-misduj582yo30b.webp</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -10931,25 +10916,25 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
+          <t>ZOTAC RTX5080 SOLID GAMING OC 16GB GDDR7 WHITE</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>195000</v>
+        <v>64900</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
+          <t>https://s.shopee.co.th/60PomHHsnI</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasa-mapdn0hs6q9gfb.webp</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -10976,25 +10961,25 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
+          <t>GALAX RTX5080 HOF GAMING 16GB GDDR7</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>195500</v>
+        <v>87000</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8GKWEm4</t>
+          <t>https://s.shopee.co.th/6AjEyaHFSL</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztn-mi2scd35wirsed.webp</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11021,25 +11006,25 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
+          <t>GIGABYTE AERO RTX5080 16GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>179900</v>
+        <v>78500</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
+          <t>https://s.shopee.co.th/6L2fAtGc7O</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztd-mki1wyjsh14yd6.webp</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11051,6 +11036,9 @@
         <is>
           <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
+      </c>
+      <c r="L228" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -11066,25 +11054,25 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
+          <t>ZOTAC GAMING RTX5080 SOLID CORE OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>185500</v>
+        <v>62500</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+          <t>https://s.shopee.co.th/6VM5NCFymR</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztm-mloguv0dy97323.webp</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11111,25 +11099,25 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) ZOTAC GAMING GEFORCE RTX 5080 SOLID CORE OC - 16GB GDDR7 (ZT-B50800J2-10P)</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>198500</v>
+        <v>59000</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSi41Ws75</t>
+          <t>https://s.shopee.co.th/5LA7z3KQ9E</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0n-mbvy43nc50gsdd.webp</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11139,7 +11127,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -11156,25 +11144,25 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
+          <t>ASUS TUF RTX5080 GAMING OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>192900</v>
+        <v>81000</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXxouETJ2</t>
+          <t>https://s.shopee.co.th/5VTYBMJmoH</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasj-m9pk6xb8lmjk47.webp</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11201,25 +11189,25 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
+          <t>INNO3D RTX5080 X3 OC WHITE 16GB GDDR7</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>188500</v>
+        <v>68300</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7prO1DDpy5</t>
+          <t>https://s.shopee.co.th/5fmyNfJ9TK</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m8d2yz7814ax90.webp</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11246,25 +11234,25 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 AERO OC SFF 16G - 16GB GDDR7 (GV-N5080AERO OC-16GD)</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>215000</v>
+        <v>67000</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
+          <t>https://s.shopee.co.th/5q6OZyIW8N</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0i-mbbyjj2rglflce.webp</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11274,7 +11262,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>EXPERT MINES COMPANY LIMITED</t>
+          <t>JIB Official Store</t>
         </is>
       </c>
     </row>
@@ -11291,25 +11279,25 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE AORUS RTX5080 MASTER 16GB GDDR7</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>228800</v>
+        <v>80900</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
+          <t>https://s.shopee.co.th/7KvCMjCo5g</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztk-ml4sii5ubnym20.webp</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11319,8 +11307,11 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="235">
@@ -11336,25 +11327,25 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
+          <t>ROG ASTRAL RTX5080 16GB OC GDDR7 BLACK</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>209000</v>
+        <v>85500</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70IH1gH0ey</t>
+          <t>https://s.shopee.co.th/7VEcZ2CAkj</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zto-mq632jnzevwuf9.webp</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11364,14 +11355,14 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>shoppingpc dotnet</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -11381,25 +11372,25 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
+          <t>ROG ASTRAL RTX5080 16 GB GDDR7 OC EDITION</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>22700</v>
+        <v>88500</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
+          <t>https://s.shopee.co.th/7fY2lLBXPm</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasi-m5p939h7ybw69b.webp</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11409,17 +11400,17 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>mcwinner</t>
+          <t>EXPERT MINES COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L236" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -11429,25 +11420,25 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>MSI RTX5080 VENTUS X3 OC PLUS 16GB GDDR7</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>26500</v>
+        <v>63000</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g9IIXOei9</t>
+          <t>https://s.shopee.co.th/7prSxeAu4p</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztl-mnkzq2y21x51b3.webp</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11457,17 +11448,14 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L237" t="n">
-        <v>6</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -11477,25 +11465,25 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>ASUS PRIME RTX5080 OC 16GB GDDR7</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>10500</v>
+        <v>74300</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+          <t>https://s.shopee.co.th/6ffVZVFLRc</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m9pl3a6dymlq34.webp</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11505,17 +11493,14 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>JIB Official Store</t>
-        </is>
-      </c>
-      <c r="L238" t="n">
-        <v>382</v>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -11525,25 +11510,25 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5080 16G SHADOW 3X OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>33000</v>
+        <v>60500</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+          <t>https://s.shopee.co.th/6pyvloEi6f</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras9-m807f87tz7xq68.webp</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11557,13 +11542,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -11573,25 +11558,25 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+          <t>VGA (การ์ดแสดงผล) GIGABYTE GEFORCE RTX 5080 GAMING OC 16G - 16GB GDDR7 (GV-N5080GAMING OC-16GD)</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>29900</v>
+        <v>63500</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+          <t>https://s.shopee.co.th/70ILy7E4li</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0o-mbbz0v0mfsdt28.webp</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -11601,17 +11586,14 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>atSine Tech</t>
-        </is>
-      </c>
-      <c r="L240" t="n">
-        <v>2</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ai_calculator_cpu</t>
+          <t>ai_calculator</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -11621,25 +11603,25 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>r9_7950x</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
+          <t>VGA (การ์ดแสดงผล) GALAX GEFORCE RTX 5080 1-CLICK OC - 16GB GDDR7</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>24200</v>
+        <v>61400</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
+          <t>https://s.shopee.co.th/7AbmAQDRQl</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0g-mb65w0t41ai927.webp</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -11649,58 +11631,2071 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Advice Official Shop</t>
-        </is>
-      </c>
-      <c r="L241" t="n">
-        <v>4</v>
+          <t>JIB Official Store</t>
+        </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS TUF GAMING GEFORCE RTX 5080 16GB GDDR7 OC EDITION (TUF-RTX5080-O16G-GAMING)</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>71700</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LP3bNS2D2</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ra0s-mb7lu03gdf7ace.webp</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS PRIME GEFORCE RTX 5080 16GB GDDR7 OC EDITION (PRIME-RTX5080-O16G)</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>63900</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViTngROs5</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasl-m9qqhz75s2cu0e.webp</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์ประกอบ HYTE Y40 RTX5080 BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>155900</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g1tzzQlX8</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7ras8-m5v66xgrzeuv7b.webp</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์ประกอบ HTYE Y60 RTX5080 OC GDDR7 BLACK</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>159000</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qLKCIQ8CB</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m63p4ze31cil46.webp</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G GAMING TRIO OC - 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>169700</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BD1GnZPSV</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-mbet1fh1hbnaa6.webp</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>คอมประกอบ GIGABYTE AITOP : Computer Set intel #i375 ULTRA 9 285K RTX5090 32GB GIGABYTE WINDFORCE (OC/D7) - A0172192</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>301100</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gGkfsbJTQ</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mq8t04g63tvx56.webp</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 | DDR5 12GB 6000MHz / SSD 1TB | ชุดน้ำปิด</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>236900</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qaAsBag8T</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134275-821eo-mh0e5nskf7k86e.webp</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 AORUS INFINITY 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>288900</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LduHGca9O</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mpeku3c4tngscb.webp</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 SUPRIM SOC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>195500</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VxKTZbwoR</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras8-m8fwept4cfgvaf.webp</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) ASUS ROG ASTRAL GEFORCE RTX 5090 32GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>180700</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1113sedqpM</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0u-mb7sojhocgfq48.webp</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL GAMING GEFORCE RTX5090 OC EDITION /32GB GDDR7 (90YV0LW0-M0NA00)</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BKU4xdDUP</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m847by4n5tkec6.webp</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>TECHNOCOM.OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L252" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ASUS RTX 5090 ระบบระบายความร้อนด้วยน้ำ Night God Wind Cooling Night God TUF ZTE PowerColor 5090 OC เวอร์ชันต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>337700</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gODU2f7VK</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/sg-11134201-8260c-mk0ukmy20v7p69.webp</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>I KNOW YOU</t>
+        </is>
+      </c>
+      <c r="L253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 9 9950X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>204900</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/qhdgLeUAN</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 32GB | DDR5 32GB / SSD 1TB | พร้อมใช้ ประกันไทย</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>193900</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LlN5QgOBI</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mpx5tygok26833.webp</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ASUS VGA GEFORCE RTX 5090 ROG ASTRAL O32G GAMING WHITE - 32GB GDDR7 - A0177699</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>205600</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W4nHjfkqL</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134275-825zz-mkf6jms5jdhgb4.webp</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>คอมประกอบพรีเมียม / 4K | Ryzen 7 9800X3D + RTX 5090 | DDR5 12GB / SSD 1TB | ชุดน้ำปิด</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>193400</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/18WgoherG</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mpxe9accfaq525.webp</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>บริษัท มังกี้ อีทีซี. จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 GAMING TRIO OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>189900</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/BRwt7h1WJ</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mipnxvm0gi69ef.webp</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC WHITE EDITION 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>198500</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50XCe0OciG</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mibay3dbo0lf65.webp</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>AORUS RTX5090 EXTREME WATERFORCE WB 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>189000</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AqcqJNzNJ</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf53ayfgm3nza4.webp</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ROG ASTRAL RTX5090 OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>192900</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4fuMFOPtOE</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mlolokuve51ra9.webp</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 WINDFORCE OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>187900</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qDmRhPG3H</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m8x6avrr1sztc8.webp</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5090 32GB OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>198500</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LHVqmRA4C</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m76f4vi99o1j85.webp</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L263" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 AORUS MASTER 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>195500</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vaw35QWjF</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x6kptwxcgf32.webp</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์ประกอบ THERMALTAKE TOWER 600 RTX5090 ASTRAL LC ULTRA 9 285K BLACK</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>459500</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40efSASQkA</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8vrk1wnfevde1.webp</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>ZOTAC RTX5090 SOLID GAMING OC WHITE 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>186900</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Ay5eTRnPD</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras8-m8eac2h34cnd54.webp</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>ZOTAC GAMING RTX5090 SOLID OC 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>186900</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g1p3YThQ8</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlogm2dcg5j558.webp</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] GIGABYTE GAMING RTX5090 32GB GDDR7 OC EDITION</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>185500</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qLFFrT45B</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m6r6xy11sncf25.webp</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 32G LIGHTNING Z GDDR7</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>269500</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOyewUy66</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mlisa7sidtdw15.webp</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>GIGABYTE AORUS RTX5090 STEALTH ICE 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>195000</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViOrFUKl9</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mczwcxljswclad.webp</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>GIGABYTE RTX5090 AORUS MASTER ICE GDDR7</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>195500</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30m8GKWEm4</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mdzlhtv1g2yo1b.webp</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>INNO3D RTX5090 ICHILL X3 32GB OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>179900</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5YSdVbR7</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8eajig8ywaxe9.webp</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>[สินค้าพร้อมจัดส่งในไทย] ASUS TUF GAMING RTX5090 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>185500</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g9HriXVS2</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m8x5qjjikva8b0.webp</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL RTX5090 GAMING OC BTF 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>198500</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qSi41Ws75</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnjoolkkmxoldd.webp</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>MSI RTX5090 32GB VENTUS 3X OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>192900</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXxouETJ2</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m8d2dtf6q4mm9d.webp</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ZOTAC RTX5090 AMP EXTREME INFINITY 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>188500</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7prO1DDpy5</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ASUS ROG ASTRAL LC RTX5090 32GB OC GDDR7</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>215000</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7Kv7QIFjz0</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m5js2fig00fea0.webp</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>EXPERT MINES COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>VGA (การ์ดแสดงผล) MSI GEFORCE RTX 5090 32G LIGHTNING Z - 32GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>228800</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VEXcbF6e3</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m7j5dkasn5qyce.webp</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ai_calculator</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>GIGABYTE GEFORCE RTX 5090 GAMING OC 32G – 32GB GDDR7 (GV-N5090GAMING OC-32GD) (ALI) (TBO-15 Days)</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>209000</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70IH1gH0ey</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mllhvztzby0w0e.webp</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>shoppingpc dotnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
           <t>ai_calculator_cpu</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
         <is>
           <t>r9_7950x</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 7950X 4.5 GHz (SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า) -3 YEARS</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>22700</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qSiUqO1NA</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8x801x6gycuda.webp</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>mcwinner</t>
+        </is>
+      </c>
+      <c r="L280" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X - 16C 32T 4.3-5.7GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>26500</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g9IIXOei9</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7r991-m08fblrkcqfsb1.webp</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L281" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 5 9600X - 6C 12T 3.9-5.4GHz (AMD SOCKET AM5) (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5YtSMkhG</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7ras8-m7agd6ph9f744c.webp</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L282" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>CPU (ซีพียู) AMD RYZEN 9 9950X3D - 16C 32T 4.3-5.7GHz AMD SOCKET AM5 (ระบบระบายความร้อนไม่รวมอยู่ในสินค้า)</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>33000</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30m8h9NO2F</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134207-7rasd-m8ylj449xemnd8.webp</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>JIB Official Store</t>
+        </is>
+      </c>
+      <c r="L283" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ซีพียู CPU: AMD - RYZEN 9 (9950X AM5)</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>29900</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3ViPI4LU1M</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasm-maw7h34vstcg33.webp</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>atSine Tech</t>
+        </is>
+      </c>
+      <c r="L284" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>CPU AMD AM5 RYZEN 9 9900X3D (NEXT) - A0169017</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>24200</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOz5lM7ML</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Advice Official Shop</t>
+        </is>
+      </c>
+      <c r="L285" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ai_calculator_cpu</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>r9_7950x</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
         <is>
           <t>CPU AMD AM5 RYZEN 9 9950X3D (NEXT) - A0168684</t>
         </is>
       </c>
-      <c r="E242" t="n">
+      <c r="E286" t="n">
         <v>32200</v>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G286" t="inlineStr">
         <is>
           <t>https://s.shopee.co.th/3qLFggKDLS</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
+      <c r="H286" t="inlineStr">
         <is>
           <t>https://down-ws-th.img.susercontent.com/th-11134275-7rasf-maw7gzrwpuo1b1.webp</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
         <is>
           <t>Advice Official Shop</t>
         </is>
       </c>
-      <c r="L242" t="n">
+      <c r="L286" t="n">
         <v>11</v>
       </c>
     </row>
